--- a/Hoàng/2025/T4/MÔI TRƯỜNG VIỆT TIẾN & LIÊN DOANH MÔI TRƯỜNG ĐA NĂNG (59 59.1 -2025)/ĐA NĂNG/BÁO GIÁ KSK CÔNG TY LIÊN DANH MÔI TRƯỜNG ĐA NĂNG.xlsx
+++ b/Hoàng/2025/T4/MÔI TRƯỜNG VIỆT TIẾN & LIÊN DOANH MÔI TRƯỜNG ĐA NĂNG (59 59.1 -2025)/ĐA NĂNG/BÁO GIÁ KSK CÔNG TY LIÊN DANH MÔI TRƯỜNG ĐA NĂNG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T4\MÔI TRƯỜNG VIỆT TIẾN &amp; LIÊN DOANH MÔI TRƯỜNG ĐA NĂNG (59 59.1 -2025)\ĐA NĂNG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430BC878-5CAE-4FF1-B267-C11CF583B53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A5A4B4-E2FA-4581-A12C-D1D11E5DEC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ĐA NĂNG'!$A$1:$G$249</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'VIỆT TIẾN'!$A$1:$G$249</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'VIỆT TIẾN'!$A$1:$H$256</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'ĐA NĂNG'!$60:$60</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'VIỆT TIẾN'!$60:$60</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'VIỆT TIẾN'!$61:$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="427">
   <si>
     <t>Ghi chú</t>
   </si>
@@ -1344,6 +1344,9 @@
   </si>
   <si>
     <t>Không khám</t>
+  </si>
+  <si>
+    <t>Gói nữ Nam (VND)</t>
   </si>
 </sst>
 </file>
@@ -1941,7 +1944,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2351,218 +2354,274 @@
     <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="2" xr:uid="{A328DFE0-4CF6-452C-850C-D71344C98BBE}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3014,7 +3073,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K249"/>
+  <dimension ref="A1:L256"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="9" bestFit="1" customWidth="1"/>
@@ -3024,56 +3083,57 @@
     <col min="5" max="5" width="18.5703125" style="17" customWidth="1"/>
     <col min="6" max="6" width="17" style="17" customWidth="1"/>
     <col min="7" max="7" width="20.7109375" style="18" customWidth="1"/>
-    <col min="8" max="8" width="32.140625" style="9" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="9"/>
+    <col min="8" max="8" width="18.85546875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" style="9" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="20"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
-      <c r="D1" s="179" t="s">
+      <c r="D1" s="158" t="s">
         <v>307</v>
       </c>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
-      <c r="D2" s="180"/>
-      <c r="E2" s="180"/>
-      <c r="F2" s="180"/>
-      <c r="G2" s="180"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
-      <c r="D3" s="180"/>
-      <c r="E3" s="180"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="180"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
-      <c r="D4" s="180"/>
-      <c r="E4" s="180"/>
-      <c r="F4" s="180"/>
-      <c r="G4" s="180"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
-      <c r="F5" s="180"/>
-      <c r="G5" s="180"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="21"/>
@@ -3085,15 +3145,15 @@
       <c r="G6" s="21"/>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="160" t="s">
         <v>409</v>
       </c>
-      <c r="B7" s="181"/>
-      <c r="C7" s="181"/>
-      <c r="D7" s="181"/>
-      <c r="E7" s="181"/>
-      <c r="F7" s="181"/>
-      <c r="G7" s="181"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -3114,41 +3174,41 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="26"/>
-      <c r="B9" s="182" t="s">
+      <c r="B9" s="161" t="s">
         <v>424</v>
       </c>
-      <c r="C9" s="182"/>
-      <c r="D9" s="182"/>
-      <c r="E9" s="182"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="182"/>
+      <c r="C9" s="161"/>
+      <c r="D9" s="161"/>
+      <c r="E9" s="161"/>
+      <c r="F9" s="161"/>
+      <c r="G9" s="161"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="183" t="s">
+      <c r="A10" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="184"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="184"/>
-      <c r="E10" s="184"/>
-      <c r="F10" s="184"/>
-      <c r="G10" s="185"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="163"/>
+      <c r="G10" s="164"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="186"/>
-      <c r="B11" s="187"/>
-      <c r="C11" s="187"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="187"/>
-      <c r="F11" s="187"/>
-      <c r="G11" s="188"/>
+      <c r="A11" s="165"/>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="167"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
@@ -3169,26 +3229,29 @@
       <c r="A13" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="B13" s="189" t="s">
+      <c r="B13" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="189"/>
+      <c r="C13" s="168"/>
       <c r="D13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="112" t="s">
+        <v>426</v>
+      </c>
+      <c r="F13" s="112" t="s">
         <v>416</v>
       </c>
-      <c r="F13" s="112" t="s">
+      <c r="G13" s="112" t="s">
         <v>415</v>
       </c>
-      <c r="G13" s="112" t="s">
+      <c r="H13" s="112" t="s">
         <v>418</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="I13" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="I13" s="113"/>
+      <c r="J13" s="113"/>
     </row>
     <row r="14" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31"/>
@@ -3200,106 +3263,117 @@
       <c r="E14" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="F14" s="115" t="s">
-        <v>413</v>
+      <c r="F14" s="145" t="s">
+        <v>425</v>
       </c>
       <c r="G14" s="115" t="s">
         <v>413</v>
       </c>
-      <c r="H14" s="141"/>
+      <c r="H14" s="115" t="s">
+        <v>413</v>
+      </c>
+      <c r="I14" s="141"/>
     </row>
     <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="190">
+      <c r="A15" s="153">
         <f>IF(LEN(C15)=0,"",COUNTA($C$15:C15))</f>
         <v>1</v>
       </c>
-      <c r="B15" s="177" t="s">
+      <c r="B15" s="154" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="191" t="s">
+      <c r="C15" s="155" t="s">
         <v>320</v>
       </c>
       <c r="D15" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="193">
+      <c r="E15" s="156">
         <v>150000</v>
       </c>
-      <c r="F15" s="198" t="s">
+      <c r="F15" s="156">
+        <v>150000</v>
+      </c>
+      <c r="G15" s="157" t="s">
         <v>425</v>
       </c>
-      <c r="G15" s="198" t="s">
+      <c r="H15" s="157" t="s">
         <v>425</v>
       </c>
-      <c r="H15" s="194"/>
-      <c r="I15" s="116"/>
+      <c r="I15" s="171"/>
+      <c r="J15" s="116"/>
     </row>
     <row r="16" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="190"/>
-      <c r="B16" s="177"/>
-      <c r="C16" s="191"/>
+      <c r="A16" s="153"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="155"/>
       <c r="D16" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="193"/>
-      <c r="F16" s="198"/>
-      <c r="G16" s="198"/>
-      <c r="H16" s="194"/>
-      <c r="I16" s="116"/>
-    </row>
-    <row r="17" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A17" s="190"/>
-      <c r="B17" s="177"/>
-      <c r="C17" s="191"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="171"/>
+      <c r="J16" s="116"/>
+    </row>
+    <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.25">
+      <c r="A17" s="153"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="155"/>
       <c r="D17" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="193"/>
-      <c r="F17" s="198"/>
-      <c r="G17" s="198"/>
-      <c r="H17" s="194"/>
-      <c r="I17" s="116"/>
-    </row>
-    <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="190"/>
-      <c r="B18" s="177"/>
-      <c r="C18" s="191"/>
+      <c r="E17" s="156"/>
+      <c r="F17" s="156"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="171"/>
+      <c r="J17" s="116"/>
+    </row>
+    <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="153"/>
+      <c r="B18" s="154"/>
+      <c r="C18" s="155"/>
       <c r="D18" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="193"/>
-      <c r="F18" s="198"/>
-      <c r="G18" s="198"/>
-      <c r="H18" s="194"/>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="190"/>
-      <c r="B19" s="177"/>
-      <c r="C19" s="191"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="157"/>
+      <c r="H18" s="157"/>
+      <c r="I18" s="171"/>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="153"/>
+      <c r="B19" s="154"/>
+      <c r="C19" s="155"/>
       <c r="D19" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="E19" s="193"/>
-      <c r="F19" s="198"/>
-      <c r="G19" s="198"/>
-      <c r="H19" s="194"/>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="190"/>
-      <c r="B20" s="177"/>
-      <c r="C20" s="191"/>
+      <c r="E19" s="156"/>
+      <c r="F19" s="156"/>
+      <c r="G19" s="157"/>
+      <c r="H19" s="157"/>
+      <c r="I19" s="171"/>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="153"/>
+      <c r="B20" s="154"/>
+      <c r="C20" s="155"/>
       <c r="D20" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="193"/>
-      <c r="F20" s="198"/>
-      <c r="G20" s="198"/>
-      <c r="H20" s="194"/>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="E20" s="156"/>
+      <c r="F20" s="156"/>
+      <c r="G20" s="157"/>
+      <c r="H20" s="157"/>
+      <c r="I20" s="171"/>
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A21" s="31">
         <f>IF(LEN(C21)=0,"",COUNTA($C$15:C21))</f>
         <v>2</v>
@@ -3316,16 +3390,19 @@
       <c r="E21" s="120">
         <v>86000</v>
       </c>
-      <c r="F21" s="145" t="s">
+      <c r="F21" s="120">
+        <v>86000</v>
+      </c>
+      <c r="G21" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="G21" s="120">
+      <c r="H21" s="120">
         <v>86000</v>
       </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="1:9" s="149" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="I21" s="34"/>
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" spans="1:10" s="149" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="146">
         <v>3</v>
       </c>
@@ -3345,10 +3422,13 @@
       <c r="G22" s="150">
         <v>70000</v>
       </c>
-      <c r="H22" s="147"/>
-      <c r="I22" s="148"/>
-    </row>
-    <row r="23" spans="1:9" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H22" s="150">
+        <v>70000</v>
+      </c>
+      <c r="I22" s="147"/>
+      <c r="J22" s="148"/>
+    </row>
+    <row r="23" spans="1:10" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="31">
         <f>IF(LEN(C23)=0,"",COUNTA($C$15:C23))</f>
         <v>4</v>
@@ -3371,10 +3451,13 @@
       <c r="G23" s="120">
         <v>50000</v>
       </c>
-      <c r="H23" s="34"/>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="24" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+      <c r="H23" s="120">
+        <v>50000</v>
+      </c>
+      <c r="I23" s="34"/>
+      <c r="J23" s="10"/>
+    </row>
+    <row r="24" spans="1:10" ht="66" x14ac:dyDescent="0.25">
       <c r="A24" s="31">
         <f>IF(LEN(C24)=0,"",COUNTA($C$15:C24))</f>
         <v>5</v>
@@ -3397,10 +3480,13 @@
       <c r="G24" s="120">
         <v>64000</v>
       </c>
-      <c r="H24" s="34"/>
-      <c r="I24" s="10"/>
-    </row>
-    <row r="25" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="H24" s="120">
+        <v>64000</v>
+      </c>
+      <c r="I24" s="34"/>
+      <c r="J24" s="10"/>
+    </row>
+    <row r="25" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="31">
         <f>IF(LEN(C25)=0,"",COUNTA($C$15:C25))</f>
         <v>6</v>
@@ -3423,15 +3509,18 @@
       <c r="G25" s="120">
         <v>22000</v>
       </c>
-      <c r="H25" s="34"/>
-      <c r="I25" s="10"/>
-    </row>
-    <row r="26" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H25" s="120">
+        <v>22000</v>
+      </c>
+      <c r="I25" s="34"/>
+      <c r="J25" s="10"/>
+    </row>
+    <row r="26" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="31">
         <f>IF(LEN(C26)=0,"",COUNTA($C$15:C26))</f>
         <v>7</v>
       </c>
-      <c r="B26" s="177" t="s">
+      <c r="B26" s="154" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="35" t="s">
@@ -3440,39 +3529,43 @@
       <c r="D26" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="195">
+      <c r="E26" s="172">
         <v>50000</v>
       </c>
-      <c r="F26" s="195">
+      <c r="F26" s="172">
         <v>50000</v>
       </c>
-      <c r="G26" s="195">
+      <c r="G26" s="172">
         <v>50000</v>
       </c>
-      <c r="H26" s="197" t="s">
+      <c r="H26" s="172">
+        <v>50000</v>
+      </c>
+      <c r="I26" s="174" t="s">
         <v>372</v>
       </c>
-      <c r="I26" s="10"/>
-    </row>
-    <row r="27" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="J26" s="10"/>
+    </row>
+    <row r="27" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="31">
         <f>IF(LEN(C27)=0,"",COUNTA($C$15:C27))</f>
         <v>8</v>
       </c>
-      <c r="B27" s="177"/>
+      <c r="B27" s="154"/>
       <c r="C27" s="35" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="196"/>
-      <c r="F27" s="196"/>
-      <c r="G27" s="196"/>
-      <c r="H27" s="197"/>
-      <c r="I27" s="10"/>
-    </row>
-    <row r="28" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="E27" s="173"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A28" s="31">
         <f>IF(LEN(C28)=0,"",COUNTA($C$15:C28))</f>
         <v>9</v>
@@ -3495,15 +3588,18 @@
       <c r="G28" s="121">
         <v>34000</v>
       </c>
-      <c r="H28" s="34"/>
-      <c r="I28" s="10"/>
-    </row>
-    <row r="29" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H28" s="121">
+        <v>34000</v>
+      </c>
+      <c r="I28" s="34"/>
+      <c r="J28" s="10"/>
+    </row>
+    <row r="29" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="31">
         <f>IF(LEN(C29)=0,"",COUNTA($C$15:C29))</f>
         <v>10</v>
       </c>
-      <c r="B29" s="192" t="s">
+      <c r="B29" s="175" t="s">
         <v>58</v>
       </c>
       <c r="C29" s="35" t="s">
@@ -3521,15 +3617,18 @@
       <c r="G29" s="121">
         <v>50000</v>
       </c>
-      <c r="H29" s="123"/>
-      <c r="I29" s="10"/>
-    </row>
-    <row r="30" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="H29" s="121">
+        <v>50000</v>
+      </c>
+      <c r="I29" s="123"/>
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="31">
         <f>IF(LEN(C30)=0,"",COUNTA($C$15:C30))</f>
         <v>11</v>
       </c>
-      <c r="B30" s="192"/>
+      <c r="B30" s="175"/>
       <c r="C30" s="38" t="s">
         <v>61</v>
       </c>
@@ -3545,15 +3644,18 @@
       <c r="G30" s="121">
         <v>50000</v>
       </c>
-      <c r="H30" s="123"/>
-      <c r="I30" s="10"/>
-    </row>
-    <row r="31" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="H30" s="121">
+        <v>50000</v>
+      </c>
+      <c r="I30" s="123"/>
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="31">
         <f>IF(LEN(C31)=0,"",COUNTA($C$15:C31))</f>
         <v>12</v>
       </c>
-      <c r="B31" s="192"/>
+      <c r="B31" s="175"/>
       <c r="C31" s="38" t="s">
         <v>65</v>
       </c>
@@ -3569,15 +3671,18 @@
       <c r="G31" s="121">
         <v>39000</v>
       </c>
-      <c r="H31" s="123"/>
-      <c r="I31" s="10"/>
-    </row>
-    <row r="32" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="H31" s="121">
+        <v>39000</v>
+      </c>
+      <c r="I31" s="123"/>
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A32" s="31">
         <f>IF(LEN(C32)=0,"",COUNTA($C$15:C32))</f>
         <v>13</v>
       </c>
-      <c r="B32" s="192"/>
+      <c r="B32" s="175"/>
       <c r="C32" s="38" t="s">
         <v>67</v>
       </c>
@@ -3593,10 +3698,13 @@
       <c r="G32" s="121">
         <v>34000</v>
       </c>
-      <c r="H32" s="123"/>
-      <c r="I32" s="10"/>
-    </row>
-    <row r="33" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H32" s="121">
+        <v>34000</v>
+      </c>
+      <c r="I32" s="123"/>
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="31">
         <f>IF(LEN(C33)=0,"",COUNTA($C$15:C33))</f>
         <v>14</v>
@@ -3608,19 +3716,22 @@
       <c r="D33" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="E33" s="121">
+      <c r="E33" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="F33" s="121">
         <v>60000</v>
-      </c>
-      <c r="F33" s="145" t="s">
-        <v>425</v>
       </c>
       <c r="G33" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="H33" s="123"/>
-      <c r="I33" s="10"/>
-    </row>
-    <row r="34" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H33" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="I33" s="123"/>
+      <c r="J33" s="10"/>
+    </row>
+    <row r="34" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="31">
         <f>IF(LEN(C34)=0,"",COUNTA($C$15:C34))</f>
         <v>15</v>
@@ -3641,15 +3752,18 @@
       <c r="G34" s="133">
         <v>109000</v>
       </c>
-      <c r="H34" s="123"/>
-      <c r="I34" s="10"/>
-    </row>
-    <row r="35" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="H34" s="133">
+        <v>109000</v>
+      </c>
+      <c r="I34" s="123"/>
+      <c r="J34" s="10"/>
+    </row>
+    <row r="35" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A35" s="31">
         <f>IF(LEN(C35)=0,"",COUNTA($C$15:C35))</f>
         <v>16</v>
       </c>
-      <c r="B35" s="177" t="s">
+      <c r="B35" s="154" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="38" t="s">
@@ -3658,47 +3772,53 @@
       <c r="D35" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="E35" s="145" t="s">
+      <c r="E35" s="121">
+        <v>34000</v>
+      </c>
+      <c r="F35" s="145" t="s">
         <v>425</v>
-      </c>
-      <c r="F35" s="121">
-        <v>34000</v>
       </c>
       <c r="G35" s="121">
         <v>34000</v>
       </c>
-      <c r="H35" s="99" t="s">
+      <c r="H35" s="121">
+        <v>34000</v>
+      </c>
+      <c r="I35" s="99" t="s">
         <v>369</v>
       </c>
-      <c r="I35" s="10"/>
-    </row>
-    <row r="36" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="J35" s="10"/>
+    </row>
+    <row r="36" spans="1:12" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="31">
         <f>IF(LEN(C36)=0,"",COUNTA($C$15:C36))</f>
         <v>17</v>
       </c>
-      <c r="B36" s="177"/>
+      <c r="B36" s="154"/>
       <c r="C36" s="38" t="s">
         <v>269</v>
       </c>
       <c r="D36" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="E36" s="145" t="s">
+      <c r="E36" s="121">
+        <v>34000</v>
+      </c>
+      <c r="F36" s="145" t="s">
         <v>425</v>
-      </c>
-      <c r="F36" s="121">
-        <v>34000</v>
       </c>
       <c r="G36" s="121">
         <v>34000</v>
       </c>
-      <c r="H36" s="99" t="s">
+      <c r="H36" s="121">
+        <v>34000</v>
+      </c>
+      <c r="I36" s="99" t="s">
         <v>368</v>
       </c>
-      <c r="I36" s="10"/>
-    </row>
-    <row r="37" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J36" s="10"/>
+    </row>
+    <row r="37" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="31">
         <f>IF(LEN(C37)=0,"",COUNTA($C$15:C37))</f>
         <v>18</v>
@@ -3712,19 +3832,22 @@
       <c r="D37" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="145" t="s">
+      <c r="E37" s="121">
+        <v>34000</v>
+      </c>
+      <c r="F37" s="145" t="s">
         <v>425</v>
-      </c>
-      <c r="F37" s="121">
-        <v>34000</v>
       </c>
       <c r="G37" s="121">
         <v>34000</v>
       </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="10"/>
-    </row>
-    <row r="38" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="H37" s="121">
+        <v>34000</v>
+      </c>
+      <c r="I37" s="34"/>
+      <c r="J37" s="10"/>
+    </row>
+    <row r="38" spans="1:12" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="31">
         <f>IF(LEN(C38)=0,"",COUNTA($C$15:C38))</f>
         <v>19</v>
@@ -3738,19 +3861,22 @@
       <c r="D38" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="145" t="s">
+      <c r="E38" s="121">
+        <v>34000</v>
+      </c>
+      <c r="F38" s="145" t="s">
         <v>425</v>
-      </c>
-      <c r="F38" s="121">
-        <v>34000</v>
       </c>
       <c r="G38" s="121">
         <v>34000</v>
       </c>
-      <c r="H38" s="34"/>
-      <c r="I38" s="10"/>
-    </row>
-    <row r="39" spans="1:11" s="126" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="H38" s="121">
+        <v>34000</v>
+      </c>
+      <c r="I38" s="34"/>
+      <c r="J38" s="10"/>
+    </row>
+    <row r="39" spans="1:12" s="126" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="31">
         <f>IF(LEN(C39)=0,"",COUNTA($C$15:C39))</f>
         <v>20</v>
@@ -3762,21 +3888,24 @@
       <c r="D39" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="145" t="s">
+      <c r="E39" s="121">
+        <v>159000</v>
+      </c>
+      <c r="F39" s="145" t="s">
         <v>425</v>
-      </c>
-      <c r="F39" s="121">
-        <v>159000</v>
       </c>
       <c r="G39" s="121">
         <v>159000</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="125"/>
-      <c r="J39" s="9"/>
+      <c r="H39" s="121">
+        <v>159000</v>
+      </c>
+      <c r="I39" s="34"/>
+      <c r="J39" s="125"/>
       <c r="K39" s="9"/>
-    </row>
-    <row r="40" spans="1:11" s="12" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L39" s="9"/>
+    </row>
+    <row r="40" spans="1:12" s="12" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31">
         <f>IF(LEN(C40)=0,"",COUNTA($C$15:C40))</f>
         <v>21</v>
@@ -3788,24 +3917,27 @@
       <c r="D40" s="66" t="s">
         <v>275</v>
       </c>
-      <c r="E40" s="145" t="s">
+      <c r="E40" s="121">
+        <v>250000</v>
+      </c>
+      <c r="F40" s="145" t="s">
         <v>425</v>
-      </c>
-      <c r="F40" s="121">
-        <v>250000</v>
       </c>
       <c r="G40" s="121">
         <v>250000</v>
       </c>
-      <c r="H40" s="123"/>
-      <c r="I40" s="11"/>
-    </row>
-    <row r="41" spans="1:11" s="12" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="121">
+        <v>250000</v>
+      </c>
+      <c r="I40" s="123"/>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" spans="1:12" s="12" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="31">
         <f>IF(LEN(C41)=0,"",COUNTA($C$15:C41))</f>
         <v>22</v>
       </c>
-      <c r="B41" s="173" t="s">
+      <c r="B41" s="176" t="s">
         <v>87</v>
       </c>
       <c r="C41" s="127" t="s">
@@ -3823,17 +3955,20 @@
       <c r="G41" s="121">
         <v>120000</v>
       </c>
-      <c r="H41" s="199" t="s">
+      <c r="H41" s="121">
+        <v>120000</v>
+      </c>
+      <c r="I41" s="179" t="s">
         <v>371</v>
       </c>
-      <c r="I41" s="11"/>
-    </row>
-    <row r="42" spans="1:11" s="12" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J41" s="11"/>
+    </row>
+    <row r="42" spans="1:12" s="12" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="31">
         <f>IF(LEN(C42)=0,"",COUNTA($C$15:C42))</f>
         <v>23</v>
       </c>
-      <c r="B42" s="174"/>
+      <c r="B42" s="177"/>
       <c r="C42" s="127" t="s">
         <v>88</v>
       </c>
@@ -3847,15 +3982,18 @@
       <c r="G42" s="121">
         <v>120000</v>
       </c>
-      <c r="H42" s="157"/>
-      <c r="I42" s="11"/>
-    </row>
-    <row r="43" spans="1:11" s="12" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="121">
+        <v>120000</v>
+      </c>
+      <c r="I42" s="180"/>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:12" s="12" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="31">
         <f>IF(LEN(C43)=0,"",COUNTA($C$15:C43))</f>
         <v>24</v>
       </c>
-      <c r="B43" s="174"/>
+      <c r="B43" s="177"/>
       <c r="C43" s="127" t="s">
         <v>89</v>
       </c>
@@ -3863,21 +4001,24 @@
       <c r="E43" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="F43" s="121">
+      <c r="F43" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="G43" s="121">
         <v>177000</v>
       </c>
-      <c r="G43" s="145" t="s">
+      <c r="H43" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="H43" s="158"/>
-      <c r="I43" s="11"/>
-    </row>
-    <row r="44" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="I43" s="181"/>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A44" s="31">
         <f>IF(LEN(C44)=0,"",COUNTA($C$15:C44))</f>
         <v>25</v>
       </c>
-      <c r="B44" s="209"/>
+      <c r="B44" s="169"/>
       <c r="C44" s="30" t="s">
         <v>318</v>
       </c>
@@ -3893,15 +4034,18 @@
       <c r="G44" s="121">
         <v>150000</v>
       </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="10"/>
-    </row>
-    <row r="45" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="H44" s="121">
+        <v>150000</v>
+      </c>
+      <c r="I44" s="34"/>
+      <c r="J44" s="10"/>
+    </row>
+    <row r="45" spans="1:12" ht="33" x14ac:dyDescent="0.25">
       <c r="A45" s="31">
         <f>IF(LEN(C45)=0,"",COUNTA($C$15:C45))</f>
         <v>26</v>
       </c>
-      <c r="B45" s="209"/>
+      <c r="B45" s="169"/>
       <c r="C45" s="30" t="s">
         <v>319</v>
       </c>
@@ -3917,34 +4061,40 @@
       <c r="G45" s="121">
         <v>150000</v>
       </c>
-      <c r="H45" s="34"/>
-      <c r="I45" s="10"/>
-    </row>
-    <row r="46" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="H45" s="121">
+        <v>150000</v>
+      </c>
+      <c r="I45" s="34"/>
+      <c r="J45" s="10"/>
+    </row>
+    <row r="46" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A46" s="31">
         <f>IF(LEN(C46)=0,"",COUNTA($C$15:C46))</f>
         <v>27</v>
       </c>
-      <c r="B46" s="210"/>
+      <c r="B46" s="170"/>
       <c r="C46" s="30" t="s">
         <v>33</v>
       </c>
       <c r="D46" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="E46" s="134">
+      <c r="E46" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="F46" s="134">
         <v>150000</v>
-      </c>
-      <c r="F46" s="145" t="s">
-        <v>425</v>
       </c>
       <c r="G46" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="H46" s="34"/>
-      <c r="I46" s="10"/>
-    </row>
-    <row r="47" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="H46" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="I46" s="34"/>
+      <c r="J46" s="10"/>
+    </row>
+    <row r="47" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="31">
         <f>IF(LEN(C47)=0,"",COUNTA($C$15:C47))</f>
         <v>28</v>
@@ -3956,32 +4106,34 @@
       <c r="D47" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="134">
+      <c r="E47" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="F47" s="134">
         <v>200000</v>
-      </c>
-      <c r="F47" s="145" t="s">
-        <v>425</v>
       </c>
       <c r="G47" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="H47" s="34"/>
-      <c r="I47" s="10"/>
-    </row>
-    <row r="48" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="31">
-        <f>IF(LEN(C48)=0,"",COUNTA($C$15:C48))</f>
-        <v>29</v>
-      </c>
-      <c r="B48" s="122"/>
-      <c r="C48" s="118" t="s">
-        <v>179</v>
-      </c>
-      <c r="D48" s="118" t="s">
-        <v>180</v>
-      </c>
-      <c r="E48" s="134">
-        <v>250000</v>
+      <c r="H47" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="I47" s="34"/>
+      <c r="J47" s="10"/>
+    </row>
+    <row r="48" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="31"/>
+      <c r="B48" s="152" t="s">
+        <v>199</v>
+      </c>
+      <c r="C48" s="66" t="s">
+        <v>217</v>
+      </c>
+      <c r="D48" s="66" t="s">
+        <v>218</v>
+      </c>
+      <c r="E48" s="135">
+        <v>178000</v>
       </c>
       <c r="F48" s="145" t="s">
         <v>425</v>
@@ -3989,142 +4141,158 @@
       <c r="G48" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="H48" s="34"/>
-      <c r="I48" s="10"/>
-    </row>
-    <row r="49" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="H48" s="145" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31">
         <f>IF(LEN(C49)=0,"",COUNTA($C$15:C49))</f>
         <v>30</v>
       </c>
       <c r="B49" s="122"/>
-      <c r="C49" s="76" t="s">
-        <v>271</v>
-      </c>
-      <c r="D49" s="76" t="s">
-        <v>268</v>
-      </c>
-      <c r="E49" s="121">
-        <v>150000</v>
-      </c>
-      <c r="F49" s="145" t="s">
+      <c r="C49" s="118" t="s">
+        <v>179</v>
+      </c>
+      <c r="D49" s="118" t="s">
+        <v>180</v>
+      </c>
+      <c r="E49" s="145" t="s">
         <v>425</v>
+      </c>
+      <c r="F49" s="134">
+        <v>250000</v>
       </c>
       <c r="G49" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="H49" s="34"/>
-      <c r="I49" s="10"/>
-    </row>
-    <row r="50" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="H49" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="I49" s="34"/>
+      <c r="J49" s="10"/>
+    </row>
+    <row r="50" spans="1:10" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A50" s="31">
         <f>IF(LEN(C50)=0,"",COUNTA($C$15:C50))</f>
         <v>31</v>
       </c>
       <c r="B50" s="122"/>
-      <c r="C50" s="136" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="137" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="129" t="s">
-        <v>413</v>
-      </c>
-      <c r="F50" s="129" t="s">
-        <v>413</v>
-      </c>
-      <c r="G50" s="129" t="s">
-        <v>413</v>
-      </c>
-      <c r="H50" s="34"/>
-      <c r="I50" s="10"/>
-    </row>
-    <row r="51" spans="1:9" s="149" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="C50" s="76" t="s">
+        <v>271</v>
+      </c>
+      <c r="D50" s="76" t="s">
+        <v>268</v>
+      </c>
+      <c r="E50" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="F50" s="121">
+        <v>150000</v>
+      </c>
+      <c r="G50" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="H50" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="I50" s="34"/>
+      <c r="J50" s="10"/>
+    </row>
+    <row r="51" spans="1:10" ht="33" x14ac:dyDescent="0.25">
       <c r="A51" s="31">
         <f>IF(LEN(C51)=0,"",COUNTA($C$15:C51))</f>
         <v>32</v>
       </c>
-      <c r="B51" s="136" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="118" t="s">
-        <v>323</v>
-      </c>
-      <c r="D51" s="118" t="s">
-        <v>324</v>
-      </c>
-      <c r="E51" s="145" t="s">
-        <v>425</v>
-      </c>
-      <c r="F51" s="119">
-        <v>560000</v>
-      </c>
-      <c r="G51" s="119"/>
-      <c r="H51" s="147"/>
-      <c r="I51" s="148"/>
-    </row>
-    <row r="52" spans="1:9" s="12" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="122"/>
+      <c r="C51" s="136" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="137" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="129" t="s">
+        <v>413</v>
+      </c>
+      <c r="F51" s="129" t="s">
+        <v>413</v>
+      </c>
+      <c r="G51" s="129" t="s">
+        <v>413</v>
+      </c>
+      <c r="H51" s="129" t="s">
+        <v>413</v>
+      </c>
+      <c r="I51" s="34"/>
+      <c r="J51" s="10"/>
+    </row>
+    <row r="52" spans="1:10" s="149" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A52" s="31">
         <f>IF(LEN(C52)=0,"",COUNTA($C$15:C52))</f>
         <v>33</v>
       </c>
-      <c r="B52" s="130" t="s">
-        <v>412</v>
+      <c r="B52" s="136" t="s">
+        <v>9</v>
       </c>
       <c r="C52" s="118" t="s">
-        <v>135</v>
+        <v>323</v>
       </c>
       <c r="D52" s="118" t="s">
-        <v>136</v>
+        <v>324</v>
       </c>
       <c r="E52" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="F52" s="128">
-        <v>200000</v>
-      </c>
-      <c r="G52" s="128">
-        <v>200000</v>
-      </c>
-      <c r="H52" s="95"/>
-      <c r="I52" s="11"/>
-    </row>
-    <row r="53" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F52" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="G52" s="119">
+        <v>560000</v>
+      </c>
+      <c r="H52" s="119"/>
+      <c r="I52" s="147"/>
+      <c r="J52" s="148"/>
+    </row>
+    <row r="53" spans="1:10" s="12" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="31">
         <f>IF(LEN(C53)=0,"",COUNTA($C$15:C53))</f>
         <v>34</v>
       </c>
-      <c r="B53" s="131"/>
-      <c r="C53" s="66" t="s">
-        <v>171</v>
-      </c>
-      <c r="D53" s="66" t="s">
-        <v>172</v>
+      <c r="B53" s="130" t="s">
+        <v>412</v>
+      </c>
+      <c r="C53" s="118" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" s="118" t="s">
+        <v>136</v>
       </c>
       <c r="E53" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="F53" s="121">
-        <v>446000</v>
-      </c>
-      <c r="G53" s="145" t="s">
+      <c r="F53" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="H53" s="34"/>
-      <c r="I53" s="10"/>
-    </row>
-    <row r="54" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G53" s="128">
+        <v>200000</v>
+      </c>
+      <c r="H53" s="128">
+        <v>200000</v>
+      </c>
+      <c r="I53" s="95"/>
+      <c r="J53" s="11"/>
+    </row>
+    <row r="54" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="31">
         <f>IF(LEN(C54)=0,"",COUNTA($C$15:C54))</f>
         <v>35</v>
       </c>
-      <c r="B54" s="114"/>
-      <c r="C54" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>414</v>
+      <c r="B54" s="131"/>
+      <c r="C54" s="66" t="s">
+        <v>171</v>
+      </c>
+      <c r="D54" s="66" t="s">
+        <v>172</v>
       </c>
       <c r="E54" s="145" t="s">
         <v>425</v>
@@ -4132,22 +4300,26 @@
       <c r="F54" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="G54" s="115">
-        <v>83000</v>
-      </c>
-      <c r="H54" s="141"/>
-    </row>
-    <row r="55" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G54" s="121">
+        <v>446000</v>
+      </c>
+      <c r="H54" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="I54" s="34"/>
+      <c r="J54" s="10"/>
+    </row>
+    <row r="55" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="31">
         <f>IF(LEN(C55)=0,"",COUNTA($C$15:C55))</f>
         <v>36</v>
       </c>
       <c r="B55" s="114"/>
-      <c r="C55" s="118" t="s">
-        <v>165</v>
-      </c>
-      <c r="D55" s="66" t="s">
-        <v>166</v>
+      <c r="C55" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>414</v>
       </c>
       <c r="E55" s="145" t="s">
         <v>425</v>
@@ -4155,1030 +4327,1042 @@
       <c r="F55" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="G55" s="135">
+      <c r="G55" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="H55" s="115">
+        <v>83000</v>
+      </c>
+      <c r="I55" s="141"/>
+    </row>
+    <row r="56" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="31">
+        <f>IF(LEN(C56)=0,"",COUNTA($C$15:C56))</f>
+        <v>37</v>
+      </c>
+      <c r="B56" s="114"/>
+      <c r="C56" s="118" t="s">
+        <v>165</v>
+      </c>
+      <c r="D56" s="66" t="s">
+        <v>166</v>
+      </c>
+      <c r="E56" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="F56" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="G56" s="145" t="s">
+        <v>425</v>
+      </c>
+      <c r="H56" s="135">
         <v>1600000</v>
       </c>
-      <c r="H55" s="141"/>
-    </row>
-    <row r="56" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="211" t="s">
+      <c r="I56" s="141"/>
+    </row>
+    <row r="57" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="182" t="s">
         <v>25</v>
       </c>
-      <c r="B56" s="212"/>
-      <c r="C56" s="212"/>
-      <c r="D56" s="213"/>
-      <c r="E56" s="112">
-        <f>SUM(E15:E55)</f>
+      <c r="B57" s="183"/>
+      <c r="C57" s="183"/>
+      <c r="D57" s="184"/>
+      <c r="E57" s="112">
+        <f>SUM(E15:E56)</f>
+        <v>2071000</v>
+      </c>
+      <c r="F57" s="112">
+        <f>SUM(F15:F56)</f>
         <v>2158000</v>
       </c>
-      <c r="F56" s="112">
-        <f>SUM(F15:F55)</f>
+      <c r="G57" s="112">
+        <f>SUM(G15:G56)</f>
         <v>3040000</v>
       </c>
-      <c r="G56" s="112">
-        <f>SUM(G15:G55)</f>
+      <c r="H57" s="112">
+        <f>SUM(H15:H56)</f>
         <v>3626000</v>
       </c>
-      <c r="H56" s="39"/>
-      <c r="I56" s="10"/>
-    </row>
-    <row r="57" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="40"/>
-      <c r="B57" s="41"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="138"/>
-      <c r="G57" s="44"/>
-    </row>
-    <row r="58" spans="1:9" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="45" t="s">
+      <c r="I57" s="39"/>
+      <c r="J57" s="10"/>
+    </row>
+    <row r="58" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="40"/>
+      <c r="B58" s="41"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="138"/>
+      <c r="G58" s="44"/>
+    </row>
+    <row r="59" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="B58" s="46"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="105"/>
-      <c r="F58" s="139"/>
-      <c r="G58" s="47"/>
-    </row>
-    <row r="59" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="48"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="50"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="140"/>
-      <c r="G59" s="52"/>
-    </row>
-    <row r="60" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="53" t="s">
+      <c r="B59" s="46"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="105"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="47"/>
+    </row>
+    <row r="60" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="48"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="50"/>
+      <c r="D60" s="50"/>
+      <c r="E60" s="51"/>
+      <c r="F60" s="140"/>
+      <c r="G60" s="52"/>
+    </row>
+    <row r="61" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="B60" s="211" t="s">
+      <c r="B61" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="C60" s="213"/>
-      <c r="D60" s="53" t="s">
+      <c r="C61" s="184"/>
+      <c r="D61" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E60" s="109" t="s">
+      <c r="E61" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="F60" s="109" t="s">
+      <c r="F61" s="109" t="s">
         <v>419</v>
       </c>
-      <c r="G60" s="28" t="s">
+      <c r="G61" s="28" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="54" t="s">
+    <row r="62" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="B61" s="55"/>
-      <c r="C61" s="56"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="58"/>
-      <c r="F61" s="58"/>
-      <c r="G61" s="59"/>
-    </row>
-    <row r="62" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="31">
-        <f>IF(LEN(C62)=0,"",COUNTA($C$62:C62))</f>
+      <c r="B62" s="55"/>
+      <c r="C62" s="56"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="59"/>
+    </row>
+    <row r="63" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="31">
+        <f>IF(LEN(C63)=0,"",COUNTA($C$63:C63))</f>
         <v>1</v>
       </c>
-      <c r="B62" s="32" t="s">
+      <c r="B63" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C62" s="30" t="s">
+      <c r="C63" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D62" s="30" t="s">
+      <c r="D63" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="60">
+      <c r="E63" s="60">
         <v>169000</v>
       </c>
-      <c r="F62" s="60">
-        <f>E62*90%</f>
+      <c r="F63" s="60">
+        <f>E63*90%</f>
         <v>152100</v>
       </c>
-      <c r="G62" s="34"/>
-    </row>
-    <row r="63" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A63" s="31">
-        <f>IF(LEN(C63)=0,"",COUNTA($C$62:C63))</f>
+      <c r="G63" s="34"/>
+    </row>
+    <row r="64" spans="1:10" ht="33" x14ac:dyDescent="0.25">
+      <c r="A64" s="31">
+        <f>IF(LEN(C64)=0,"",COUNTA($C$63:C64))</f>
         <v>2</v>
       </c>
-      <c r="B63" s="32" t="s">
+      <c r="B64" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C63" s="35" t="s">
+      <c r="C64" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D63" s="35" t="s">
+      <c r="D64" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="E63" s="61">
+      <c r="E64" s="61">
         <v>47000</v>
       </c>
-      <c r="F63" s="60">
-        <f t="shared" ref="F63:F128" si="0">E63*90%</f>
+      <c r="F64" s="60">
+        <f t="shared" ref="F64:F129" si="0">E64*90%</f>
         <v>42300</v>
       </c>
-      <c r="G63" s="34"/>
-    </row>
-    <row r="64" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A64" s="31">
-        <f>IF(LEN(C64)=0,"",COUNTA($C$62:C64))</f>
+      <c r="G64" s="34"/>
+    </row>
+    <row r="65" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A65" s="31">
+        <f>IF(LEN(C65)=0,"",COUNTA($C$63:C65))</f>
         <v>3</v>
       </c>
-      <c r="B64" s="70"/>
-      <c r="C64" s="35" t="s">
+      <c r="B65" s="70"/>
+      <c r="C65" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="D64" s="62" t="s">
+      <c r="D65" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="E64" s="61">
+      <c r="E65" s="61">
         <v>59000</v>
       </c>
-      <c r="F64" s="60">
+      <c r="F65" s="60">
         <f t="shared" si="0"/>
         <v>53100</v>
       </c>
-      <c r="G64" s="111"/>
-    </row>
-    <row r="65" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A65" s="31">
-        <f>IF(LEN(C65)=0,"",COUNTA($C$62:C65))</f>
+      <c r="G65" s="111"/>
+    </row>
+    <row r="66" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A66" s="31">
+        <f>IF(LEN(C66)=0,"",COUNTA($C$63:C66))</f>
         <v>4</v>
       </c>
-      <c r="B65" s="63" t="s">
+      <c r="B66" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C66" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D66" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="E65" s="64">
+      <c r="E66" s="64">
         <v>102000</v>
       </c>
-      <c r="F65" s="60">
+      <c r="F66" s="60">
         <f t="shared" si="0"/>
         <v>91800</v>
       </c>
-      <c r="G65" s="34"/>
-    </row>
-    <row r="66" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="31">
-        <f>IF(LEN(C66)=0,"",COUNTA($C$62:C66))</f>
+      <c r="G66" s="34"/>
+    </row>
+    <row r="67" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="31">
+        <f>IF(LEN(C67)=0,"",COUNTA($C$63:C67))</f>
         <v>5</v>
       </c>
-      <c r="B66" s="169" t="s">
+      <c r="B67" s="185" t="s">
         <v>272</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C67" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D67" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="E66" s="64">
+      <c r="E67" s="64">
         <v>62000</v>
       </c>
-      <c r="F66" s="60">
+      <c r="F67" s="60">
         <f t="shared" si="0"/>
         <v>55800</v>
       </c>
-      <c r="G66" s="199" t="s">
+      <c r="G67" s="179" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="31">
-        <f>IF(LEN(C67)=0,"",COUNTA($C$62:C67))</f>
+    <row r="68" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="31">
+        <f>IF(LEN(C68)=0,"",COUNTA($C$63:C68))</f>
         <v>6</v>
       </c>
-      <c r="B67" s="170"/>
-      <c r="C67" s="29" t="s">
+      <c r="B68" s="186"/>
+      <c r="C68" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="D67" s="29" t="s">
+      <c r="D68" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="E67" s="64">
+      <c r="E68" s="64">
         <v>165000</v>
       </c>
-      <c r="F67" s="60">
+      <c r="F68" s="60">
         <f t="shared" si="0"/>
         <v>148500</v>
       </c>
-      <c r="G67" s="157"/>
-    </row>
-    <row r="68" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="31">
-        <f>IF(LEN(C68)=0,"",COUNTA($C$62:C68))</f>
+      <c r="G68" s="180"/>
+    </row>
+    <row r="69" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="31">
+        <f>IF(LEN(C69)=0,"",COUNTA($C$63:C69))</f>
         <v>7</v>
       </c>
-      <c r="B68" s="171"/>
-      <c r="C68" s="29" t="s">
+      <c r="B69" s="187"/>
+      <c r="C69" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="D68" s="29" t="s">
+      <c r="D69" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="E68" s="64">
+      <c r="E69" s="64">
         <v>116000</v>
       </c>
-      <c r="F68" s="60">
+      <c r="F69" s="60">
         <f t="shared" si="0"/>
         <v>104400</v>
       </c>
-      <c r="G68" s="158"/>
-    </row>
-    <row r="69" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="31">
-        <f>IF(LEN(C69)=0,"",COUNTA($C$62:C69))</f>
+      <c r="G69" s="181"/>
+    </row>
+    <row r="70" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="31">
+        <f>IF(LEN(C70)=0,"",COUNTA($C$63:C70))</f>
         <v>8</v>
       </c>
-      <c r="B69" s="169" t="s">
+      <c r="B70" s="185" t="s">
         <v>267</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C70" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="D69" s="29" t="s">
+      <c r="D70" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="E69" s="64">
+      <c r="E70" s="64">
         <v>83000</v>
       </c>
-      <c r="F69" s="60">
+      <c r="F70" s="60">
         <f t="shared" si="0"/>
         <v>74700</v>
       </c>
-      <c r="G69" s="34"/>
-    </row>
-    <row r="70" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="31">
-        <f>IF(LEN(C70)=0,"",COUNTA($C$62:C70))</f>
+      <c r="G70" s="34"/>
+    </row>
+    <row r="71" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="31">
+        <f>IF(LEN(C71)=0,"",COUNTA($C$63:C71))</f>
         <v>9</v>
       </c>
-      <c r="B70" s="170"/>
-      <c r="C70" s="29" t="s">
+      <c r="B71" s="186"/>
+      <c r="C71" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="D70" s="29" t="s">
+      <c r="D71" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="E70" s="64">
+      <c r="E71" s="64">
         <v>130000</v>
       </c>
-      <c r="F70" s="60">
+      <c r="F71" s="60">
         <f t="shared" si="0"/>
         <v>117000</v>
       </c>
-      <c r="G70" s="199" t="s">
+      <c r="G71" s="179" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="31">
-        <f>IF(LEN(C71)=0,"",COUNTA($C$62:C71))</f>
+    <row r="72" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="31">
+        <f>IF(LEN(C72)=0,"",COUNTA($C$63:C72))</f>
         <v>10</v>
       </c>
-      <c r="B71" s="170"/>
-      <c r="C71" s="29" t="s">
+      <c r="B72" s="186"/>
+      <c r="C72" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="D71" s="29" t="s">
+      <c r="D72" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="E71" s="64">
+      <c r="E72" s="64">
         <v>120000</v>
       </c>
-      <c r="F71" s="60">
+      <c r="F72" s="60">
         <f t="shared" si="0"/>
         <v>108000</v>
       </c>
-      <c r="G71" s="157"/>
-    </row>
-    <row r="72" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="31">
-        <f>IF(LEN(C72)=0,"",COUNTA($C$62:C72))</f>
+      <c r="G72" s="180"/>
+    </row>
+    <row r="73" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="31">
+        <f>IF(LEN(C73)=0,"",COUNTA($C$63:C73))</f>
         <v>11</v>
       </c>
-      <c r="B72" s="171"/>
-      <c r="C72" s="29" t="s">
+      <c r="B73" s="187"/>
+      <c r="C73" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="D72" s="29" t="s">
+      <c r="D73" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="E72" s="64">
+      <c r="E73" s="64">
         <v>282000</v>
       </c>
-      <c r="F72" s="60">
+      <c r="F73" s="60">
         <f t="shared" si="0"/>
         <v>253800</v>
       </c>
-      <c r="G72" s="158"/>
-    </row>
-    <row r="73" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="31">
-        <f>IF(LEN(C73)=0,"",COUNTA($C$62:C73))</f>
+      <c r="G73" s="181"/>
+    </row>
+    <row r="74" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="31">
+        <f>IF(LEN(C74)=0,"",COUNTA($C$63:C74))</f>
         <v>12</v>
       </c>
-      <c r="B73" s="63" t="s">
+      <c r="B74" s="63" t="s">
         <v>366</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C74" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="D73" s="29" t="s">
+      <c r="D74" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="E73" s="64">
+      <c r="E74" s="64">
         <v>128000</v>
       </c>
-      <c r="F73" s="60">
+      <c r="F74" s="60">
         <f t="shared" si="0"/>
         <v>115200</v>
       </c>
-      <c r="G73" s="34"/>
-    </row>
-    <row r="74" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="31">
-        <f>IF(LEN(C74)=0,"",COUNTA($C$62:C74))</f>
+      <c r="G74" s="34"/>
+    </row>
+    <row r="75" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="31">
+        <f>IF(LEN(C75)=0,"",COUNTA($C$63:C75))</f>
         <v>13</v>
       </c>
-      <c r="B74" s="100"/>
-      <c r="C74" s="29" t="s">
+      <c r="B75" s="100"/>
+      <c r="C75" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D74" s="29" t="s">
+      <c r="D75" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="E74" s="60">
+      <c r="E75" s="60">
         <v>138000</v>
       </c>
-      <c r="F74" s="60">
+      <c r="F75" s="60">
         <f t="shared" si="0"/>
         <v>124200</v>
       </c>
-      <c r="G74" s="110"/>
-    </row>
-    <row r="75" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="31">
-        <f>IF(LEN(C75)=0,"",COUNTA($C$62:C75))</f>
+      <c r="G75" s="110"/>
+    </row>
+    <row r="76" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="31">
+        <f>IF(LEN(C76)=0,"",COUNTA($C$63:C76))</f>
         <v>14</v>
       </c>
-      <c r="B75" s="100" t="s">
+      <c r="B76" s="100" t="s">
         <v>380</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C76" s="29" t="s">
         <v>381</v>
       </c>
-      <c r="D75" s="29" t="s">
+      <c r="D76" s="29" t="s">
         <v>382</v>
       </c>
-      <c r="E75" s="60">
+      <c r="E76" s="60">
         <v>282000</v>
       </c>
-      <c r="F75" s="60">
+      <c r="F76" s="60">
         <f t="shared" si="0"/>
         <v>253800</v>
       </c>
-      <c r="G75" s="101"/>
-    </row>
-    <row r="76" spans="1:7" s="12" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="31">
-        <f>IF(LEN(C76)=0,"",COUNTA($C$62:C76))</f>
+      <c r="G76" s="101"/>
+    </row>
+    <row r="77" spans="1:7" s="12" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="31">
+        <f>IF(LEN(C77)=0,"",COUNTA($C$63:C77))</f>
         <v>15</v>
       </c>
-      <c r="B76" s="216" t="s">
+      <c r="B77" s="188" t="s">
         <v>200</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C77" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="D76" s="29" t="s">
+      <c r="D77" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="E76" s="64">
+      <c r="E77" s="64">
         <v>30000</v>
       </c>
-      <c r="F76" s="60">
+      <c r="F77" s="60">
         <f t="shared" si="0"/>
         <v>27000</v>
       </c>
-      <c r="G76" s="217" t="s">
+      <c r="G77" s="189" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="77" spans="1:7" s="12" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="31">
-        <f>IF(LEN(C77)=0,"",COUNTA($C$62:C77))</f>
+    <row r="78" spans="1:7" s="12" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="31">
+        <f>IF(LEN(C78)=0,"",COUNTA($C$63:C78))</f>
         <v>16</v>
       </c>
-      <c r="B77" s="216"/>
-      <c r="C77" s="29" t="s">
+      <c r="B78" s="188"/>
+      <c r="C78" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="D77" s="29" t="s">
+      <c r="D78" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="E77" s="64">
+      <c r="E78" s="64">
         <v>20000</v>
       </c>
-      <c r="F77" s="60">
+      <c r="F78" s="60">
         <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="G77" s="218"/>
-    </row>
-    <row r="78" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="159" t="s">
+      <c r="G78" s="190"/>
+    </row>
+    <row r="79" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="191" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="160"/>
-      <c r="C78" s="160"/>
-      <c r="D78" s="161"/>
-      <c r="E78" s="58"/>
-      <c r="F78" s="58"/>
-      <c r="G78" s="59"/>
-    </row>
-    <row r="79" spans="1:7" s="12" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A79" s="31">
-        <f>IF(LEN(C79)=0,"",COUNTA($C$62:C79))</f>
+      <c r="B79" s="192"/>
+      <c r="C79" s="192"/>
+      <c r="D79" s="193"/>
+      <c r="E79" s="58"/>
+      <c r="F79" s="58"/>
+      <c r="G79" s="59"/>
+    </row>
+    <row r="80" spans="1:7" s="12" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A80" s="31">
+        <f>IF(LEN(C80)=0,"",COUNTA($C$63:C80))</f>
         <v>17</v>
       </c>
-      <c r="B79" s="173" t="s">
+      <c r="B80" s="176" t="s">
         <v>255</v>
       </c>
-      <c r="C79" s="65" t="s">
+      <c r="C80" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="D79" s="66" t="s">
+      <c r="D80" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="E79" s="33">
+      <c r="E80" s="33">
         <v>174000</v>
       </c>
-      <c r="F79" s="60">
+      <c r="F80" s="60">
         <f t="shared" si="0"/>
         <v>156600</v>
       </c>
-      <c r="G79" s="34"/>
-    </row>
-    <row r="80" spans="1:7" s="12" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A80" s="31">
-        <f>IF(LEN(C80)=0,"",COUNTA($C$62:C80))</f>
+      <c r="G80" s="34"/>
+    </row>
+    <row r="81" spans="1:7" s="12" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A81" s="31">
+        <f>IF(LEN(C81)=0,"",COUNTA($C$63:C81))</f>
         <v>18</v>
       </c>
-      <c r="B80" s="174"/>
-      <c r="C80" s="65" t="s">
+      <c r="B81" s="177"/>
+      <c r="C81" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="D80" s="66" t="s">
+      <c r="D81" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="E80" s="97">
+      <c r="E81" s="97">
         <v>231000</v>
       </c>
-      <c r="F80" s="60">
+      <c r="F81" s="60">
         <f t="shared" si="0"/>
         <v>207900</v>
       </c>
-      <c r="G80" s="34"/>
-    </row>
-    <row r="81" spans="1:7" s="12" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A81" s="31">
-        <f>IF(LEN(C81)=0,"",COUNTA($C$62:C81))</f>
+      <c r="G81" s="34"/>
+    </row>
+    <row r="82" spans="1:7" s="12" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A82" s="31">
+        <f>IF(LEN(C82)=0,"",COUNTA($C$63:C82))</f>
         <v>19</v>
       </c>
-      <c r="B81" s="174"/>
-      <c r="C81" s="65" t="s">
+      <c r="B82" s="177"/>
+      <c r="C82" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="D81" s="66" t="s">
+      <c r="D82" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="E81" s="33">
+      <c r="E82" s="33">
         <v>732000</v>
       </c>
-      <c r="F81" s="60">
+      <c r="F82" s="60">
         <f t="shared" si="0"/>
         <v>658800</v>
       </c>
-      <c r="G81" s="34"/>
-    </row>
-    <row r="82" spans="1:7" s="12" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A82" s="31">
-        <f>IF(LEN(C82)=0,"",COUNTA($C$62:C82))</f>
+      <c r="G82" s="34"/>
+    </row>
+    <row r="83" spans="1:7" s="12" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A83" s="31">
+        <f>IF(LEN(C83)=0,"",COUNTA($C$63:C83))</f>
         <v>20</v>
       </c>
-      <c r="B82" s="174"/>
-      <c r="C82" s="65" t="s">
+      <c r="B83" s="177"/>
+      <c r="C83" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="D82" s="66" t="s">
+      <c r="D83" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="E82" s="33">
+      <c r="E83" s="33">
         <v>192000</v>
       </c>
-      <c r="F82" s="60">
+      <c r="F83" s="60">
         <f t="shared" si="0"/>
         <v>172800</v>
       </c>
-      <c r="G82" s="34"/>
-    </row>
-    <row r="83" spans="1:7" s="12" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="31">
-        <f>IF(LEN(C83)=0,"",COUNTA($C$62:C83))</f>
+      <c r="G83" s="34"/>
+    </row>
+    <row r="84" spans="1:7" s="12" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="31">
+        <f>IF(LEN(C84)=0,"",COUNTA($C$63:C84))</f>
         <v>21</v>
       </c>
-      <c r="B83" s="174"/>
-      <c r="C83" s="65" t="s">
+      <c r="B84" s="177"/>
+      <c r="C84" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="D83" s="66" t="s">
+      <c r="D84" s="66" t="s">
         <v>276</v>
       </c>
-      <c r="E83" s="97">
+      <c r="E84" s="97">
         <v>231000</v>
       </c>
-      <c r="F83" s="60">
+      <c r="F84" s="60">
         <f t="shared" si="0"/>
         <v>207900</v>
       </c>
-      <c r="G83" s="99" t="s">
+      <c r="G84" s="99" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="84" spans="1:7" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="31">
-        <f>IF(LEN(C84)=0,"",COUNTA($C$62:C84))</f>
+    <row r="85" spans="1:7" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="31">
+        <f>IF(LEN(C85)=0,"",COUNTA($C$63:C85))</f>
         <v>22</v>
       </c>
-      <c r="B84" s="174"/>
-      <c r="C84" s="67" t="s">
+      <c r="B85" s="177"/>
+      <c r="C85" s="67" t="s">
         <v>229</v>
       </c>
-      <c r="D84" s="68" t="s">
+      <c r="D85" s="68" t="s">
         <v>230</v>
       </c>
-      <c r="E84" s="106">
+      <c r="E85" s="106">
         <v>500000</v>
       </c>
-      <c r="F84" s="60">
+      <c r="F85" s="60">
         <f t="shared" si="0"/>
         <v>450000</v>
       </c>
-      <c r="G84" s="34"/>
-    </row>
-    <row r="85" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="31">
-        <f>IF(LEN(C85)=0,"",COUNTA($C$62:C85))</f>
+      <c r="G85" s="34"/>
+    </row>
+    <row r="86" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="31">
+        <f>IF(LEN(C86)=0,"",COUNTA($C$63:C86))</f>
         <v>23</v>
       </c>
-      <c r="B85" s="174"/>
-      <c r="C85" s="65" t="s">
+      <c r="B86" s="177"/>
+      <c r="C86" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="D85" s="66" t="s">
+      <c r="D86" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="E85" s="33">
+      <c r="E86" s="33">
         <v>231000</v>
       </c>
-      <c r="F85" s="60">
+      <c r="F86" s="60">
         <f t="shared" si="0"/>
         <v>207900</v>
       </c>
-      <c r="G85" s="34"/>
-    </row>
-    <row r="86" spans="1:7" s="12" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="31">
-        <f>IF(LEN(C86)=0,"",COUNTA($C$62:C86))</f>
+      <c r="G86" s="34"/>
+    </row>
+    <row r="87" spans="1:7" s="12" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="31">
+        <f>IF(LEN(C87)=0,"",COUNTA($C$63:C87))</f>
         <v>24</v>
       </c>
-      <c r="B86" s="174"/>
-      <c r="C86" s="65" t="s">
+      <c r="B87" s="177"/>
+      <c r="C87" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="D86" s="66" t="s">
+      <c r="D87" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="E86" s="33">
+      <c r="E87" s="33">
         <v>616000</v>
       </c>
-      <c r="F86" s="60">
+      <c r="F87" s="60">
         <f t="shared" si="0"/>
         <v>554400</v>
       </c>
-      <c r="G86" s="34"/>
-    </row>
-    <row r="87" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="31">
-        <f>IF(LEN(C87)=0,"",COUNTA($C$62:C87))</f>
+      <c r="G87" s="34"/>
+    </row>
+    <row r="88" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="31">
+        <f>IF(LEN(C88)=0,"",COUNTA($C$63:C88))</f>
         <v>25</v>
       </c>
-      <c r="B87" s="174"/>
-      <c r="C87" s="65" t="s">
+      <c r="B88" s="177"/>
+      <c r="C88" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="D87" s="66" t="s">
+      <c r="D88" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="E87" s="97">
+      <c r="E88" s="97">
         <v>231000</v>
       </c>
-      <c r="F87" s="60">
+      <c r="F88" s="60">
         <f t="shared" si="0"/>
         <v>207900</v>
       </c>
-      <c r="G87" s="34"/>
-    </row>
-    <row r="88" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="31">
-        <f>IF(LEN(C88)=0,"",COUNTA($C$62:C88))</f>
+      <c r="G88" s="34"/>
+    </row>
+    <row r="89" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="31">
+        <f>IF(LEN(C89)=0,"",COUNTA($C$63:C89))</f>
         <v>26</v>
       </c>
-      <c r="B88" s="175"/>
-      <c r="C88" s="65" t="s">
+      <c r="B89" s="194"/>
+      <c r="C89" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="D88" s="66" t="s">
+      <c r="D89" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="E88" s="33">
+      <c r="E89" s="33">
         <v>412000</v>
       </c>
-      <c r="F88" s="60">
+      <c r="F89" s="60">
         <f t="shared" si="0"/>
         <v>370800</v>
       </c>
-      <c r="G88" s="34"/>
-    </row>
-    <row r="89" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="31">
-        <f>IF(LEN(C89)=0,"",COUNTA($C$62:C89))</f>
+      <c r="G89" s="34"/>
+    </row>
+    <row r="90" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="31">
+        <f>IF(LEN(C90)=0,"",COUNTA($C$63:C90))</f>
         <v>27</v>
       </c>
-      <c r="B89" s="173" t="s">
+      <c r="B90" s="176" t="s">
         <v>388</v>
       </c>
-      <c r="C89" s="65" t="s">
+      <c r="C90" s="65" t="s">
         <v>389</v>
       </c>
-      <c r="D89" s="214" t="s">
+      <c r="D90" s="195" t="s">
         <v>391</v>
       </c>
-      <c r="E89" s="33">
+      <c r="E90" s="33">
         <v>215000</v>
       </c>
-      <c r="F89" s="60">
+      <c r="F90" s="60">
         <f t="shared" si="0"/>
         <v>193500</v>
       </c>
-      <c r="G89" s="95"/>
-    </row>
-    <row r="90" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="31">
-        <f>IF(LEN(C90)=0,"",COUNTA($C$62:C90))</f>
+      <c r="G90" s="95"/>
+    </row>
+    <row r="91" spans="1:7" s="12" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="31">
+        <f>IF(LEN(C91)=0,"",COUNTA($C$63:C91))</f>
         <v>28</v>
       </c>
-      <c r="B90" s="174"/>
-      <c r="C90" s="65" t="s">
+      <c r="B91" s="177"/>
+      <c r="C91" s="65" t="s">
         <v>390</v>
       </c>
-      <c r="D90" s="215"/>
-      <c r="E90" s="33">
+      <c r="D91" s="196"/>
+      <c r="E91" s="33">
         <v>323000</v>
       </c>
-      <c r="F90" s="60">
+      <c r="F91" s="60">
         <f t="shared" si="0"/>
         <v>290700</v>
       </c>
-      <c r="G90" s="95"/>
-    </row>
-    <row r="91" spans="1:7" s="12" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="31">
-        <f>IF(LEN(C91)=0,"",COUNTA($C$62:C91))</f>
+      <c r="G91" s="95"/>
+    </row>
+    <row r="92" spans="1:7" s="12" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="31">
+        <f>IF(LEN(C92)=0,"",COUNTA($C$63:C92))</f>
         <v>29</v>
       </c>
-      <c r="B91" s="174"/>
-      <c r="C91" s="65" t="s">
+      <c r="B92" s="177"/>
+      <c r="C92" s="65" t="s">
         <v>393</v>
       </c>
-      <c r="D91" s="102" t="s">
+      <c r="D92" s="102" t="s">
         <v>392</v>
       </c>
-      <c r="E91" s="33">
+      <c r="E92" s="33">
         <v>269000</v>
       </c>
-      <c r="F91" s="60">
+      <c r="F92" s="60">
         <f t="shared" si="0"/>
         <v>242100</v>
       </c>
-      <c r="G91" s="95"/>
-    </row>
-    <row r="92" spans="1:7" s="12" customFormat="1" ht="66" x14ac:dyDescent="0.25">
-      <c r="A92" s="31">
-        <f>IF(LEN(C92)=0,"",COUNTA($C$62:C92))</f>
+      <c r="G92" s="95"/>
+    </row>
+    <row r="93" spans="1:7" s="12" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+      <c r="A93" s="31">
+        <f>IF(LEN(C93)=0,"",COUNTA($C$63:C93))</f>
         <v>30</v>
       </c>
-      <c r="B92" s="175"/>
-      <c r="C92" s="65" t="s">
+      <c r="B93" s="194"/>
+      <c r="C93" s="65" t="s">
         <v>394</v>
       </c>
-      <c r="D92" s="102" t="s">
+      <c r="D93" s="102" t="s">
         <v>395</v>
       </c>
-      <c r="E92" s="33">
+      <c r="E93" s="33">
         <v>588000</v>
       </c>
-      <c r="F92" s="60">
+      <c r="F93" s="60">
         <f t="shared" si="0"/>
         <v>529200</v>
       </c>
-      <c r="G92" s="95"/>
-    </row>
-    <row r="93" spans="1:7" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="159" t="s">
+      <c r="G93" s="95"/>
+    </row>
+    <row r="94" spans="1:7" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A94" s="191" t="s">
         <v>202</v>
       </c>
-      <c r="B93" s="160"/>
-      <c r="C93" s="160"/>
-      <c r="D93" s="161"/>
-      <c r="E93" s="58"/>
-      <c r="F93" s="58"/>
-      <c r="G93" s="59"/>
-    </row>
-    <row r="94" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="31">
-        <f>IF(LEN(C94)=0,"",COUNTA($C$62:C94))</f>
+      <c r="B94" s="192"/>
+      <c r="C94" s="192"/>
+      <c r="D94" s="193"/>
+      <c r="E94" s="58"/>
+      <c r="F94" s="58"/>
+      <c r="G94" s="59"/>
+    </row>
+    <row r="95" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A95" s="31">
+        <f>IF(LEN(C95)=0,"",COUNTA($C$63:C95))</f>
         <v>31</v>
       </c>
-      <c r="B94" s="176" t="s">
+      <c r="B95" s="197" t="s">
         <v>94</v>
       </c>
-      <c r="C94" s="29" t="s">
+      <c r="C95" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="D94" s="29" t="s">
+      <c r="D95" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="E94" s="64">
+      <c r="E95" s="64">
         <v>123000</v>
       </c>
-      <c r="F94" s="60">
+      <c r="F95" s="60">
         <f t="shared" si="0"/>
         <v>110700</v>
       </c>
-      <c r="G94" s="34"/>
-    </row>
-    <row r="95" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A95" s="31">
-        <f>IF(LEN(C95)=0,"",COUNTA($C$62:C95))</f>
+      <c r="G95" s="34"/>
+    </row>
+    <row r="96" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A96" s="31">
+        <f>IF(LEN(C96)=0,"",COUNTA($C$63:C96))</f>
         <v>32</v>
       </c>
-      <c r="B95" s="176"/>
-      <c r="C95" s="29" t="s">
+      <c r="B96" s="197"/>
+      <c r="C96" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D95" s="29" t="s">
+      <c r="D96" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="E95" s="64">
+      <c r="E96" s="64">
         <v>66000</v>
       </c>
-      <c r="F95" s="60">
+      <c r="F96" s="60">
         <f t="shared" si="0"/>
         <v>59400</v>
       </c>
-      <c r="G95" s="34"/>
-    </row>
-    <row r="96" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="A96" s="31">
-        <f>IF(LEN(C96)=0,"",COUNTA($C$62:C96))</f>
+      <c r="G96" s="34"/>
+    </row>
+    <row r="97" spans="1:7" ht="207" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="31">
+        <f>IF(LEN(C97)=0,"",COUNTA($C$63:C97))</f>
         <v>33</v>
       </c>
-      <c r="B96" s="176"/>
-      <c r="C96" s="29" t="s">
+      <c r="B97" s="197"/>
+      <c r="C97" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="29" t="s">
+      <c r="D97" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="E96" s="64">
+      <c r="E97" s="64">
         <v>139000</v>
       </c>
-      <c r="F96" s="60">
+      <c r="F97" s="60">
         <f t="shared" si="0"/>
         <v>125100</v>
       </c>
-      <c r="G96" s="34" t="s">
+      <c r="G97" s="34" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="A97" s="31">
-        <f>IF(LEN(C97)=0,"",COUNTA($C$62:C97))</f>
+    <row r="98" spans="1:7" ht="198.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="31">
+        <f>IF(LEN(C98)=0,"",COUNTA($C$63:C98))</f>
         <v>34</v>
       </c>
-      <c r="B97" s="176"/>
-      <c r="C97" s="29" t="s">
+      <c r="B98" s="197"/>
+      <c r="C98" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="D97" s="29" t="s">
+      <c r="D98" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="E97" s="64">
+      <c r="E98" s="64">
         <v>66000</v>
       </c>
-      <c r="F97" s="60">
+      <c r="F98" s="60">
         <f t="shared" si="0"/>
         <v>59400</v>
       </c>
-      <c r="G97" s="34" t="s">
+      <c r="G98" s="34" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="148.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="31">
-        <f>IF(LEN(C98)=0,"",COUNTA($C$62:C98))</f>
+    <row r="99" spans="1:7" ht="148.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="31">
+        <f>IF(LEN(C99)=0,"",COUNTA($C$63:C99))</f>
         <v>35</v>
       </c>
-      <c r="B98" s="176"/>
-      <c r="C98" s="29" t="s">
+      <c r="B99" s="197"/>
+      <c r="C99" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="D98" s="29" t="s">
+      <c r="D99" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="E98" s="64">
+      <c r="E99" s="64">
         <v>212000</v>
       </c>
-      <c r="F98" s="60">
+      <c r="F99" s="60">
         <f t="shared" si="0"/>
         <v>190800</v>
       </c>
-      <c r="G98" s="34"/>
-    </row>
-    <row r="99" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="31">
-        <f>IF(LEN(C99)=0,"",COUNTA($C$62:C99))</f>
+      <c r="G99" s="34"/>
+    </row>
+    <row r="100" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="31">
+        <f>IF(LEN(C100)=0,"",COUNTA($C$63:C100))</f>
         <v>36</v>
       </c>
-      <c r="B99" s="176"/>
-      <c r="C99" s="29" t="s">
+      <c r="B100" s="197"/>
+      <c r="C100" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="D99" s="29" t="s">
+      <c r="D100" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="E99" s="64">
+      <c r="E100" s="64">
         <v>868000</v>
       </c>
-      <c r="F99" s="60">
+      <c r="F100" s="60">
         <f t="shared" si="0"/>
         <v>781200</v>
       </c>
-      <c r="G99" s="99" t="s">
+      <c r="G100" s="99" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="31">
-        <f>IF(LEN(C100)=0,"",COUNTA($C$62:C100))</f>
+    <row r="101" spans="1:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="31">
+        <f>IF(LEN(C101)=0,"",COUNTA($C$63:C101))</f>
         <v>37</v>
       </c>
-      <c r="B100" s="176"/>
-      <c r="C100" s="29" t="s">
+      <c r="B101" s="197"/>
+      <c r="C101" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="D100" s="29" t="s">
+      <c r="D101" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="E100" s="64">
+      <c r="E101" s="64">
         <v>139000</v>
       </c>
-      <c r="F100" s="60">
+      <c r="F101" s="60">
         <f t="shared" si="0"/>
         <v>125100</v>
       </c>
-      <c r="G100" s="99" t="s">
+      <c r="G101" s="99" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="31">
-        <f>IF(LEN(C101)=0,"",COUNTA($C$62:C101))</f>
+    <row r="102" spans="1:7" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="31">
+        <f>IF(LEN(C102)=0,"",COUNTA($C$63:C102))</f>
         <v>38</v>
       </c>
-      <c r="B101" s="176"/>
-      <c r="C101" s="29" t="s">
+      <c r="B102" s="197"/>
+      <c r="C102" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="29" t="s">
+      <c r="D102" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="E101" s="64">
+      <c r="E102" s="64">
         <v>72000</v>
       </c>
-      <c r="F101" s="60">
+      <c r="F102" s="60">
         <f t="shared" si="0"/>
         <v>64800</v>
       </c>
-      <c r="G101" s="99" t="s">
+      <c r="G102" s="99" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A102" s="31">
-        <f>IF(LEN(C102)=0,"",COUNTA($C$62:C102))</f>
+    <row r="103" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A103" s="31">
+        <f>IF(LEN(C103)=0,"",COUNTA($C$63:C103))</f>
         <v>39</v>
       </c>
-      <c r="B102" s="176" t="s">
+      <c r="B103" s="197" t="s">
         <v>113</v>
       </c>
-      <c r="C102" s="29" t="s">
+      <c r="C103" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="D102" s="29" t="s">
+      <c r="D103" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="E102" s="64">
+      <c r="E103" s="64">
         <v>174000</v>
       </c>
-      <c r="F102" s="60">
+      <c r="F103" s="60">
         <f t="shared" si="0"/>
         <v>156600</v>
       </c>
-      <c r="G102" s="34"/>
-    </row>
-    <row r="103" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A103" s="31">
-        <f>IF(LEN(C103)=0,"",COUNTA($C$62:C103))</f>
+      <c r="G103" s="34"/>
+    </row>
+    <row r="104" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A104" s="31">
+        <f>IF(LEN(C104)=0,"",COUNTA($C$63:C104))</f>
         <v>40</v>
       </c>
-      <c r="B103" s="176"/>
-      <c r="C103" s="29" t="s">
+      <c r="B104" s="197"/>
+      <c r="C104" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D103" s="29" t="s">
+      <c r="D104" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="E103" s="64">
+      <c r="E104" s="64">
         <v>88000</v>
       </c>
-      <c r="F103" s="60">
+      <c r="F104" s="60">
         <f t="shared" si="0"/>
         <v>79200</v>
       </c>
-      <c r="G103" s="34"/>
-    </row>
-    <row r="104" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="31">
-        <f>IF(LEN(C104)=0,"",COUNTA($C$62:C104))</f>
-        <v>41</v>
-      </c>
-      <c r="B104" s="165" t="s">
-        <v>118</v>
-      </c>
-      <c r="C104" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D104" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="E104" s="60">
-        <v>168000</v>
-      </c>
-      <c r="F104" s="60">
-        <f t="shared" si="0"/>
-        <v>151200</v>
-      </c>
       <c r="G104" s="34"/>
     </row>
     <row r="105" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A105" s="31">
-        <f>IF(LEN(C105)=0,"",COUNTA($C$62:C105))</f>
-        <v>42</v>
-      </c>
-      <c r="B105" s="166"/>
+        <f>IF(LEN(C105)=0,"",COUNTA($C$63:C105))</f>
+        <v>41</v>
+      </c>
+      <c r="B105" s="198" t="s">
+        <v>118</v>
+      </c>
       <c r="C105" s="29" t="s">
-        <v>379</v>
+        <v>119</v>
       </c>
       <c r="D105" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E105" s="60">
         <v>168000</v>
@@ -5189,193 +5373,195 @@
       </c>
       <c r="G105" s="34"/>
     </row>
-    <row r="106" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A106" s="31">
-        <f>IF(LEN(C106)=0,"",COUNTA($C$62:C106))</f>
-        <v>43</v>
-      </c>
-      <c r="B106" s="167"/>
+        <f>IF(LEN(C106)=0,"",COUNTA($C$63:C106))</f>
+        <v>42</v>
+      </c>
+      <c r="B106" s="199"/>
       <c r="C106" s="29" t="s">
-        <v>122</v>
+        <v>379</v>
       </c>
       <c r="D106" s="29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E106" s="60">
-        <v>253000</v>
+        <v>168000</v>
       </c>
       <c r="F106" s="60">
         <f t="shared" si="0"/>
+        <v>151200</v>
+      </c>
+      <c r="G106" s="34"/>
+    </row>
+    <row r="107" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A107" s="31">
+        <f>IF(LEN(C107)=0,"",COUNTA($C$63:C107))</f>
+        <v>43</v>
+      </c>
+      <c r="B107" s="200"/>
+      <c r="C107" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D107" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E107" s="60">
+        <v>253000</v>
+      </c>
+      <c r="F107" s="60">
+        <f t="shared" si="0"/>
         <v>227700</v>
       </c>
-      <c r="G106" s="34"/>
-    </row>
-    <row r="107" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="159" t="s">
+      <c r="G107" s="34"/>
+    </row>
+    <row r="108" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="191" t="s">
         <v>256</v>
       </c>
-      <c r="B107" s="160"/>
-      <c r="C107" s="160"/>
-      <c r="D107" s="161"/>
-      <c r="E107" s="69"/>
-      <c r="F107" s="69"/>
-      <c r="G107" s="59"/>
-    </row>
-    <row r="108" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="31">
-        <f>IF(LEN(C108)=0,"",COUNTA($C$62:C108))</f>
+      <c r="B108" s="192"/>
+      <c r="C108" s="192"/>
+      <c r="D108" s="193"/>
+      <c r="E108" s="69"/>
+      <c r="F108" s="69"/>
+      <c r="G108" s="59"/>
+    </row>
+    <row r="109" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A109" s="31">
+        <f>IF(LEN(C109)=0,"",COUNTA($C$63:C109))</f>
         <v>44</v>
       </c>
-      <c r="B108" s="169" t="s">
+      <c r="B109" s="185" t="s">
         <v>235</v>
       </c>
-      <c r="C108" s="29" t="s">
+      <c r="C109" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="D108" s="29" t="s">
+      <c r="D109" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="E108" s="60">
+      <c r="E109" s="60">
         <v>250000</v>
       </c>
-      <c r="F108" s="60">
+      <c r="F109" s="60">
         <f t="shared" si="0"/>
         <v>225000</v>
       </c>
-      <c r="G108" s="34"/>
-    </row>
-    <row r="109" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="31">
-        <f>IF(LEN(C109)=0,"",COUNTA($C$62:C109))</f>
+      <c r="G109" s="34"/>
+    </row>
+    <row r="110" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A110" s="31">
+        <f>IF(LEN(C110)=0,"",COUNTA($C$63:C110))</f>
         <v>45</v>
       </c>
-      <c r="B109" s="171"/>
-      <c r="C109" s="29" t="s">
+      <c r="B110" s="187"/>
+      <c r="C110" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="D109" s="29" t="s">
+      <c r="D110" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="E109" s="60">
+      <c r="E110" s="60">
         <v>399000</v>
       </c>
-      <c r="F109" s="60">
+      <c r="F110" s="60">
         <f t="shared" si="0"/>
         <v>359100</v>
       </c>
-      <c r="G109" s="34"/>
-    </row>
-    <row r="110" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="31">
-        <f>IF(LEN(C110)=0,"",COUNTA($C$62:C110))</f>
+      <c r="G110" s="34"/>
+    </row>
+    <row r="111" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="31">
+        <f>IF(LEN(C111)=0,"",COUNTA($C$63:C111))</f>
         <v>46</v>
       </c>
-      <c r="B110" s="165" t="s">
+      <c r="B111" s="198" t="s">
         <v>238</v>
       </c>
-      <c r="C110" s="29" t="s">
+      <c r="C111" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="D110" s="29"/>
-      <c r="E110" s="60">
+      <c r="D111" s="29"/>
+      <c r="E111" s="60">
         <v>2500000</v>
       </c>
-      <c r="F110" s="60">
+      <c r="F111" s="60">
         <f t="shared" si="0"/>
         <v>2250000</v>
       </c>
-      <c r="G110" s="34"/>
-    </row>
-    <row r="111" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="31">
-        <f>IF(LEN(C111)=0,"",COUNTA($C$62:C111))</f>
+      <c r="G111" s="34"/>
+    </row>
+    <row r="112" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A112" s="31">
+        <f>IF(LEN(C112)=0,"",COUNTA($C$63:C112))</f>
         <v>47</v>
       </c>
-      <c r="B111" s="167"/>
-      <c r="C111" s="29" t="s">
+      <c r="B112" s="200"/>
+      <c r="C112" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="D111" s="29"/>
-      <c r="E111" s="60">
+      <c r="D112" s="29"/>
+      <c r="E112" s="60">
         <v>2200000</v>
       </c>
-      <c r="F111" s="60">
+      <c r="F112" s="60">
         <f t="shared" si="0"/>
         <v>1980000</v>
       </c>
-      <c r="G111" s="34"/>
-    </row>
-    <row r="112" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="31">
-        <f>IF(LEN(C112)=0,"",COUNTA($C$62:C112))</f>
+      <c r="G112" s="34"/>
+    </row>
+    <row r="113" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A113" s="31">
+        <f>IF(LEN(C113)=0,"",COUNTA($C$63:C113))</f>
         <v>48</v>
       </c>
-      <c r="B112" s="94" t="s">
+      <c r="B113" s="94" t="s">
         <v>306</v>
       </c>
-      <c r="C112" s="29" t="s">
+      <c r="C113" s="29" t="s">
         <v>367</v>
       </c>
-      <c r="D112" s="29"/>
-      <c r="E112" s="60">
+      <c r="D113" s="29"/>
+      <c r="E113" s="60">
         <v>250000</v>
       </c>
-      <c r="F112" s="60">
+      <c r="F113" s="60">
         <f t="shared" si="0"/>
         <v>225000</v>
       </c>
-      <c r="G112" s="34" t="s">
+      <c r="G113" s="34" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="31">
-        <f>IF(LEN(C113)=0,"",COUNTA($C$62:C113))</f>
+    <row r="114" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="31">
+        <f>IF(LEN(C114)=0,"",COUNTA($C$63:C114))</f>
         <v>49</v>
       </c>
-      <c r="B113" s="165" t="s">
+      <c r="B114" s="198" t="s">
         <v>253</v>
       </c>
-      <c r="C113" s="29" t="s">
+      <c r="C114" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="D113" s="29"/>
-      <c r="E113" s="60">
+      <c r="D114" s="29"/>
+      <c r="E114" s="60">
         <v>275000</v>
       </c>
-      <c r="F113" s="60">
+      <c r="F114" s="60">
         <f t="shared" si="0"/>
         <v>247500</v>
       </c>
-      <c r="G113" s="34"/>
-    </row>
-    <row r="114" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="31">
-        <f>IF(LEN(C114)=0,"",COUNTA($C$62:C114))</f>
-        <v>50</v>
-      </c>
-      <c r="B114" s="166"/>
-      <c r="C114" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="D114" s="29"/>
-      <c r="E114" s="60">
-        <v>187000</v>
-      </c>
-      <c r="F114" s="60">
-        <f t="shared" si="0"/>
-        <v>168300</v>
-      </c>
       <c r="G114" s="34"/>
     </row>
     <row r="115" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="31">
-        <f>IF(LEN(C115)=0,"",COUNTA($C$62:C115))</f>
-        <v>51</v>
-      </c>
-      <c r="B115" s="166"/>
+        <f>IF(LEN(C115)=0,"",COUNTA($C$63:C115))</f>
+        <v>50</v>
+      </c>
+      <c r="B115" s="199"/>
       <c r="C115" s="29" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D115" s="29"/>
       <c r="E115" s="60">
@@ -5389,69 +5575,69 @@
     </row>
     <row r="116" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="31">
-        <f>IF(LEN(C116)=0,"",COUNTA($C$62:C116))</f>
-        <v>52</v>
-      </c>
-      <c r="B116" s="166"/>
+        <f>IF(LEN(C116)=0,"",COUNTA($C$63:C116))</f>
+        <v>51</v>
+      </c>
+      <c r="B116" s="199"/>
       <c r="C116" s="29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D116" s="29"/>
       <c r="E116" s="60">
-        <v>189000</v>
+        <v>187000</v>
       </c>
       <c r="F116" s="60">
         <f t="shared" si="0"/>
-        <v>170100</v>
+        <v>168300</v>
       </c>
       <c r="G116" s="34"/>
     </row>
     <row r="117" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="31">
-        <f>IF(LEN(C117)=0,"",COUNTA($C$62:C117))</f>
-        <v>53</v>
-      </c>
-      <c r="B117" s="166"/>
+        <f>IF(LEN(C117)=0,"",COUNTA($C$63:C117))</f>
+        <v>52</v>
+      </c>
+      <c r="B117" s="199"/>
       <c r="C117" s="29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D117" s="29"/>
       <c r="E117" s="60">
-        <v>150000</v>
+        <v>189000</v>
       </c>
       <c r="F117" s="60">
         <f t="shared" si="0"/>
-        <v>135000</v>
+        <v>170100</v>
       </c>
       <c r="G117" s="34"/>
     </row>
     <row r="118" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="31">
-        <f>IF(LEN(C118)=0,"",COUNTA($C$62:C118))</f>
-        <v>54</v>
-      </c>
-      <c r="B118" s="166"/>
+        <f>IF(LEN(C118)=0,"",COUNTA($C$63:C118))</f>
+        <v>53</v>
+      </c>
+      <c r="B118" s="199"/>
       <c r="C118" s="29" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D118" s="29"/>
       <c r="E118" s="60">
-        <v>189000</v>
+        <v>150000</v>
       </c>
       <c r="F118" s="60">
         <f t="shared" si="0"/>
-        <v>170100</v>
+        <v>135000</v>
       </c>
       <c r="G118" s="34"/>
     </row>
     <row r="119" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="31">
-        <f>IF(LEN(C119)=0,"",COUNTA($C$62:C119))</f>
-        <v>55</v>
-      </c>
-      <c r="B119" s="166"/>
+        <f>IF(LEN(C119)=0,"",COUNTA($C$63:C119))</f>
+        <v>54</v>
+      </c>
+      <c r="B119" s="199"/>
       <c r="C119" s="29" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D119" s="29"/>
       <c r="E119" s="60">
@@ -5465,69 +5651,69 @@
     </row>
     <row r="120" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="31">
-        <f>IF(LEN(C120)=0,"",COUNTA($C$62:C120))</f>
-        <v>56</v>
-      </c>
-      <c r="B120" s="166"/>
+        <f>IF(LEN(C120)=0,"",COUNTA($C$63:C120))</f>
+        <v>55</v>
+      </c>
+      <c r="B120" s="199"/>
       <c r="C120" s="29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D120" s="29"/>
       <c r="E120" s="60">
-        <v>187000</v>
+        <v>189000</v>
       </c>
       <c r="F120" s="60">
         <f t="shared" si="0"/>
-        <v>168300</v>
+        <v>170100</v>
       </c>
       <c r="G120" s="34"/>
     </row>
     <row r="121" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="31">
-        <f>IF(LEN(C121)=0,"",COUNTA($C$62:C121))</f>
-        <v>57</v>
-      </c>
-      <c r="B121" s="166"/>
+        <f>IF(LEN(C121)=0,"",COUNTA($C$63:C121))</f>
+        <v>56</v>
+      </c>
+      <c r="B121" s="199"/>
       <c r="C121" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D121" s="29"/>
       <c r="E121" s="60">
-        <v>201000</v>
+        <v>187000</v>
       </c>
       <c r="F121" s="60">
         <f t="shared" si="0"/>
-        <v>180900</v>
+        <v>168300</v>
       </c>
       <c r="G121" s="34"/>
     </row>
     <row r="122" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="31">
-        <f>IF(LEN(C122)=0,"",COUNTA($C$62:C122))</f>
-        <v>58</v>
-      </c>
-      <c r="B122" s="166"/>
+        <f>IF(LEN(C122)=0,"",COUNTA($C$63:C122))</f>
+        <v>57</v>
+      </c>
+      <c r="B122" s="199"/>
       <c r="C122" s="29" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D122" s="29"/>
       <c r="E122" s="60">
-        <v>187000</v>
+        <v>201000</v>
       </c>
       <c r="F122" s="60">
         <f t="shared" si="0"/>
-        <v>168300</v>
+        <v>180900</v>
       </c>
       <c r="G122" s="34"/>
     </row>
     <row r="123" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="31">
-        <f>IF(LEN(C123)=0,"",COUNTA($C$62:C123))</f>
-        <v>59</v>
-      </c>
-      <c r="B123" s="166"/>
+        <f>IF(LEN(C123)=0,"",COUNTA($C$63:C123))</f>
+        <v>58</v>
+      </c>
+      <c r="B123" s="199"/>
       <c r="C123" s="29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D123" s="29"/>
       <c r="E123" s="60">
@@ -5541,262 +5727,260 @@
     </row>
     <row r="124" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="31">
-        <f>IF(LEN(C124)=0,"",COUNTA($C$62:C124))</f>
-        <v>60</v>
-      </c>
-      <c r="B124" s="166"/>
+        <f>IF(LEN(C124)=0,"",COUNTA($C$63:C124))</f>
+        <v>59</v>
+      </c>
+      <c r="B124" s="199"/>
       <c r="C124" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D124" s="29"/>
       <c r="E124" s="60">
-        <v>132000</v>
+        <v>187000</v>
       </c>
       <c r="F124" s="60">
         <f t="shared" si="0"/>
-        <v>118800</v>
+        <v>168300</v>
       </c>
       <c r="G124" s="34"/>
     </row>
     <row r="125" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="31">
-        <f>IF(LEN(C125)=0,"",COUNTA($C$62:C125))</f>
-        <v>61</v>
-      </c>
-      <c r="B125" s="166"/>
+        <f>IF(LEN(C125)=0,"",COUNTA($C$63:C125))</f>
+        <v>60</v>
+      </c>
+      <c r="B125" s="199"/>
       <c r="C125" s="29" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D125" s="29"/>
       <c r="E125" s="60">
-        <v>187000</v>
+        <v>132000</v>
       </c>
       <c r="F125" s="60">
         <f t="shared" si="0"/>
-        <v>168300</v>
+        <v>118800</v>
       </c>
       <c r="G125" s="34"/>
     </row>
     <row r="126" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="31">
-        <f>IF(LEN(C126)=0,"",COUNTA($C$62:C126))</f>
-        <v>62</v>
-      </c>
-      <c r="B126" s="167"/>
+        <f>IF(LEN(C126)=0,"",COUNTA($C$63:C126))</f>
+        <v>61</v>
+      </c>
+      <c r="B126" s="199"/>
       <c r="C126" s="29" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D126" s="29"/>
       <c r="E126" s="60">
-        <v>1073000</v>
+        <v>187000</v>
       </c>
       <c r="F126" s="60">
         <f t="shared" si="0"/>
+        <v>168300</v>
+      </c>
+      <c r="G126" s="34"/>
+    </row>
+    <row r="127" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="31">
+        <f>IF(LEN(C127)=0,"",COUNTA($C$63:C127))</f>
+        <v>62</v>
+      </c>
+      <c r="B127" s="200"/>
+      <c r="C127" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="D127" s="29"/>
+      <c r="E127" s="60">
+        <v>1073000</v>
+      </c>
+      <c r="F127" s="60">
+        <f t="shared" si="0"/>
         <v>965700</v>
       </c>
-      <c r="G126" s="34"/>
-    </row>
-    <row r="127" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="159" t="s">
+      <c r="G127" s="34"/>
+    </row>
+    <row r="128" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A128" s="191" t="s">
         <v>221</v>
       </c>
-      <c r="B127" s="160"/>
-      <c r="C127" s="160"/>
-      <c r="D127" s="161"/>
-      <c r="E127" s="58"/>
-      <c r="F127" s="58"/>
-      <c r="G127" s="59"/>
-    </row>
-    <row r="128" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="31">
-        <f>IF(LEN(C128)=0,"",COUNTA($C$62:C128))</f>
+      <c r="B128" s="192"/>
+      <c r="C128" s="192"/>
+      <c r="D128" s="193"/>
+      <c r="E128" s="58"/>
+      <c r="F128" s="58"/>
+      <c r="G128" s="59"/>
+    </row>
+    <row r="129" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="31">
+        <f>IF(LEN(C129)=0,"",COUNTA($C$63:C129))</f>
         <v>63</v>
       </c>
-      <c r="B128" s="63" t="s">
+      <c r="B129" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="C128" s="29" t="s">
+      <c r="C129" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="D128" s="29" t="s">
+      <c r="D129" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="E128" s="60">
+      <c r="E129" s="60">
         <v>50000</v>
       </c>
-      <c r="F128" s="60">
+      <c r="F129" s="60">
         <f t="shared" si="0"/>
         <v>45000</v>
       </c>
-      <c r="G128" s="34"/>
-    </row>
-    <row r="129" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="31">
-        <f>IF(LEN(C129)=0,"",COUNTA($C$62:C129))</f>
+      <c r="G129" s="34"/>
+    </row>
+    <row r="130" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A130" s="31">
+        <f>IF(LEN(C130)=0,"",COUNTA($C$63:C130))</f>
         <v>64</v>
       </c>
-      <c r="B129" s="63" t="s">
+      <c r="B130" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="C129" s="29" t="s">
+      <c r="C130" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="D129" s="29" t="s">
+      <c r="D130" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="E129" s="60">
+      <c r="E130" s="60">
         <v>108000</v>
       </c>
-      <c r="F129" s="60">
-        <f t="shared" ref="F129" si="1">E129*90%</f>
+      <c r="F130" s="60">
+        <f t="shared" ref="F130" si="1">E130*90%</f>
         <v>97200</v>
       </c>
-      <c r="G129" s="34"/>
-    </row>
-    <row r="130" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="156" t="s">
+      <c r="G130" s="34"/>
+    </row>
+    <row r="131" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="203" t="s">
         <v>257</v>
       </c>
-      <c r="B130" s="156"/>
-      <c r="C130" s="156"/>
-      <c r="D130" s="156"/>
-      <c r="E130" s="69"/>
-      <c r="F130" s="69"/>
-      <c r="G130" s="59"/>
-    </row>
-    <row r="131" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="31">
-        <f>IF(LEN(C131)=0,"",COUNTA($C$62:C131))</f>
-        <v>65</v>
-      </c>
-      <c r="B131" s="168"/>
-      <c r="C131" s="29" t="s">
-        <v>398</v>
-      </c>
-      <c r="D131" s="29"/>
-      <c r="E131" s="64">
-        <v>250000</v>
-      </c>
-      <c r="F131" s="60">
-        <f t="shared" ref="F131:F197" si="2">E131*90%</f>
-        <v>225000</v>
-      </c>
-      <c r="G131" s="34"/>
+      <c r="B131" s="203"/>
+      <c r="C131" s="203"/>
+      <c r="D131" s="203"/>
+      <c r="E131" s="69"/>
+      <c r="F131" s="69"/>
+      <c r="G131" s="59"/>
     </row>
     <row r="132" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="31">
-        <f>IF(LEN(C132)=0,"",COUNTA($C$62:C132))</f>
-        <v>66</v>
-      </c>
-      <c r="B132" s="168"/>
+        <f>IF(LEN(C132)=0,"",COUNTA($C$63:C132))</f>
+        <v>65</v>
+      </c>
+      <c r="B132" s="204"/>
       <c r="C132" s="29" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D132" s="29"/>
       <c r="E132" s="64">
+        <v>250000</v>
+      </c>
+      <c r="F132" s="60">
+        <f t="shared" ref="F132:F197" si="2">E132*90%</f>
+        <v>225000</v>
+      </c>
+      <c r="G132" s="34"/>
+    </row>
+    <row r="133" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="31">
+        <f>IF(LEN(C133)=0,"",COUNTA($C$63:C133))</f>
+        <v>66</v>
+      </c>
+      <c r="B133" s="204"/>
+      <c r="C133" s="29" t="s">
+        <v>399</v>
+      </c>
+      <c r="D133" s="29"/>
+      <c r="E133" s="64">
         <v>375000</v>
       </c>
-      <c r="F132" s="60">
+      <c r="F133" s="60">
         <f t="shared" si="2"/>
         <v>337500</v>
       </c>
-      <c r="G132" s="34"/>
-    </row>
-    <row r="133" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="31">
-        <f>IF(LEN(C133)=0,"",COUNTA($C$62:C133))</f>
+      <c r="G133" s="34"/>
+    </row>
+    <row r="134" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="31">
+        <f>IF(LEN(C134)=0,"",COUNTA($C$63:C134))</f>
         <v>67</v>
       </c>
-      <c r="B133" s="168"/>
-      <c r="C133" s="29" t="s">
+      <c r="B134" s="204"/>
+      <c r="C134" s="29" t="s">
         <v>400</v>
       </c>
-      <c r="D133" s="29"/>
-      <c r="E133" s="64">
+      <c r="D134" s="29"/>
+      <c r="E134" s="64">
         <v>500000</v>
       </c>
-      <c r="F133" s="60">
+      <c r="F134" s="60">
         <f t="shared" si="2"/>
         <v>450000</v>
       </c>
-      <c r="G133" s="34"/>
-    </row>
-    <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A134" s="31">
-        <f>IF(LEN(C134)=0,"",COUNTA($C$62:C134))</f>
+      <c r="G134" s="34"/>
+    </row>
+    <row r="135" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A135" s="31">
+        <f>IF(LEN(C135)=0,"",COUNTA($C$63:C135))</f>
         <v>68</v>
       </c>
-      <c r="B134" s="168"/>
-      <c r="C134" s="30" t="s">
+      <c r="B135" s="204"/>
+      <c r="C135" s="30" t="s">
         <v>401</v>
       </c>
-      <c r="D134" s="30" t="s">
+      <c r="D135" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="E134" s="60">
+      <c r="E135" s="60">
         <v>700000</v>
       </c>
-      <c r="F134" s="60">
+      <c r="F135" s="60">
         <f t="shared" si="2"/>
         <v>630000</v>
       </c>
-      <c r="G134" s="34"/>
-    </row>
-    <row r="135" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="31">
-        <f>IF(LEN(C135)=0,"",COUNTA($C$62:C135))</f>
+      <c r="G135" s="34"/>
+    </row>
+    <row r="136" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A136" s="31">
+        <f>IF(LEN(C136)=0,"",COUNTA($C$63:C136))</f>
         <v>69</v>
       </c>
-      <c r="B135" s="168"/>
-      <c r="C135" s="30" t="s">
+      <c r="B136" s="204"/>
+      <c r="C136" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="D135" s="98" t="s">
+      <c r="D136" s="98" t="s">
         <v>322</v>
       </c>
-      <c r="E135" s="60">
+      <c r="E136" s="60">
         <v>770000</v>
       </c>
-      <c r="F135" s="60">
+      <c r="F136" s="60">
         <f t="shared" si="2"/>
         <v>693000</v>
       </c>
-      <c r="G135" s="34"/>
-    </row>
-    <row r="136" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="31">
-        <f>IF(LEN(C136)=0,"",COUNTA($C$62:C136))</f>
-        <v>70</v>
-      </c>
-      <c r="B136" s="169" t="s">
-        <v>277</v>
-      </c>
-      <c r="C136" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="D136" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E136" s="64">
-        <v>157000</v>
-      </c>
-      <c r="F136" s="60">
-        <f t="shared" si="2"/>
-        <v>141300</v>
-      </c>
       <c r="G136" s="34"/>
     </row>
     <row r="137" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="31">
-        <f>IF(LEN(C137)=0,"",COUNTA($C$62:C137))</f>
-        <v>71</v>
-      </c>
-      <c r="B137" s="170"/>
+        <f>IF(LEN(C137)=0,"",COUNTA($C$63:C137))</f>
+        <v>70</v>
+      </c>
+      <c r="B137" s="185" t="s">
+        <v>277</v>
+      </c>
       <c r="C137" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D137" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E137" s="64">
         <v>157000</v>
@@ -5809,99 +5993,99 @@
     </row>
     <row r="138" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="31">
-        <f>IF(LEN(C138)=0,"",COUNTA($C$62:C138))</f>
-        <v>72</v>
-      </c>
-      <c r="B138" s="170"/>
+        <f>IF(LEN(C138)=0,"",COUNTA($C$63:C138))</f>
+        <v>71</v>
+      </c>
+      <c r="B138" s="186"/>
       <c r="C138" s="29" t="s">
-        <v>383</v>
+        <v>139</v>
       </c>
       <c r="D138" s="29" t="s">
-        <v>384</v>
+        <v>140</v>
       </c>
       <c r="E138" s="64">
-        <v>143000</v>
+        <v>157000</v>
       </c>
       <c r="F138" s="60">
         <f t="shared" si="2"/>
-        <v>128700</v>
+        <v>141300</v>
       </c>
       <c r="G138" s="34"/>
     </row>
     <row r="139" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="31">
-        <f>IF(LEN(C139)=0,"",COUNTA($C$62:C139))</f>
-        <v>73</v>
-      </c>
-      <c r="B139" s="170"/>
+        <f>IF(LEN(C139)=0,"",COUNTA($C$63:C139))</f>
+        <v>72</v>
+      </c>
+      <c r="B139" s="186"/>
       <c r="C139" s="29" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D139" s="29" t="s">
         <v>384</v>
       </c>
       <c r="E139" s="64">
-        <v>185000</v>
+        <v>143000</v>
       </c>
       <c r="F139" s="60">
         <f t="shared" si="2"/>
-        <v>166500</v>
+        <v>128700</v>
       </c>
       <c r="G139" s="34"/>
     </row>
-    <row r="140" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="31">
-        <f>IF(LEN(C140)=0,"",COUNTA($C$62:C140))</f>
-        <v>74</v>
-      </c>
-      <c r="B140" s="170"/>
+        <f>IF(LEN(C140)=0,"",COUNTA($C$63:C140))</f>
+        <v>73</v>
+      </c>
+      <c r="B140" s="186"/>
       <c r="C140" s="29" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="D140" s="29" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="E140" s="64">
-        <v>1200000</v>
+        <v>185000</v>
       </c>
       <c r="F140" s="60">
         <f t="shared" si="2"/>
-        <v>1080000</v>
-      </c>
-      <c r="G140" s="99"/>
-    </row>
-    <row r="141" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+        <v>166500</v>
+      </c>
+      <c r="G140" s="34"/>
+    </row>
+    <row r="141" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A141" s="31">
-        <f>IF(LEN(C141)=0,"",COUNTA($C$62:C141))</f>
-        <v>75</v>
-      </c>
-      <c r="B141" s="171"/>
+        <f>IF(LEN(C141)=0,"",COUNTA($C$63:C141))</f>
+        <v>74</v>
+      </c>
+      <c r="B141" s="186"/>
       <c r="C141" s="29" t="s">
-        <v>141</v>
+        <v>362</v>
       </c>
       <c r="D141" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="E141" s="64"/>
+        <v>363</v>
+      </c>
+      <c r="E141" s="64">
+        <v>1200000</v>
+      </c>
       <c r="F141" s="60">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G141" s="34"/>
+        <v>1080000</v>
+      </c>
+      <c r="G141" s="99"/>
     </row>
     <row r="142" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A142" s="31">
-        <f>IF(LEN(C142)=0,"",COUNTA($C$62:C142))</f>
-        <v>76</v>
-      </c>
-      <c r="B142" s="170" t="s">
-        <v>278</v>
-      </c>
+        <f>IF(LEN(C142)=0,"",COUNTA($C$63:C142))</f>
+        <v>75</v>
+      </c>
+      <c r="B142" s="187"/>
       <c r="C142" s="29" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D142" s="29" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E142" s="64"/>
       <c r="F142" s="60">
@@ -5912,143 +6096,141 @@
     </row>
     <row r="143" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A143" s="31">
-        <f>IF(LEN(C143)=0,"",COUNTA($C$62:C143))</f>
-        <v>77</v>
-      </c>
-      <c r="B143" s="170"/>
+        <f>IF(LEN(C143)=0,"",COUNTA($C$63:C143))</f>
+        <v>76</v>
+      </c>
+      <c r="B143" s="186" t="s">
+        <v>278</v>
+      </c>
       <c r="C143" s="29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D143" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="E143" s="60">
-        <v>847000</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="E143" s="64"/>
       <c r="F143" s="60">
         <f t="shared" si="2"/>
-        <v>762300</v>
+        <v>0</v>
       </c>
       <c r="G143" s="34"/>
     </row>
     <row r="144" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A144" s="31">
-        <f>IF(LEN(C144)=0,"",COUNTA($C$62:C144))</f>
-        <v>78</v>
-      </c>
-      <c r="B144" s="170"/>
+        <f>IF(LEN(C144)=0,"",COUNTA($C$63:C144))</f>
+        <v>77</v>
+      </c>
+      <c r="B144" s="186"/>
       <c r="C144" s="29" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D144" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E144" s="60">
-        <v>2178000</v>
+        <v>847000</v>
       </c>
       <c r="F144" s="60">
         <f t="shared" si="2"/>
-        <v>1960200</v>
+        <v>762300</v>
       </c>
       <c r="G144" s="34"/>
     </row>
-    <row r="145" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A145" s="31">
-        <f>IF(LEN(C145)=0,"",COUNTA($C$62:C145))</f>
-        <v>79</v>
-      </c>
-      <c r="B145" s="170"/>
+        <f>IF(LEN(C145)=0,"",COUNTA($C$63:C145))</f>
+        <v>78</v>
+      </c>
+      <c r="B145" s="186"/>
       <c r="C145" s="29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D145" s="29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E145" s="60">
-        <v>847000</v>
+        <v>2178000</v>
       </c>
       <c r="F145" s="60">
         <f t="shared" si="2"/>
-        <v>762300</v>
+        <v>1960200</v>
       </c>
       <c r="G145" s="34"/>
     </row>
-    <row r="146" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A146" s="31">
-        <f>IF(LEN(C146)=0,"",COUNTA($C$62:C146))</f>
-        <v>80</v>
-      </c>
-      <c r="B146" s="170"/>
+        <f>IF(LEN(C146)=0,"",COUNTA($C$63:C146))</f>
+        <v>79</v>
+      </c>
+      <c r="B146" s="186"/>
       <c r="C146" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="D146" s="98" t="s">
-        <v>325</v>
+        <v>151</v>
+      </c>
+      <c r="D146" s="29" t="s">
+        <v>152</v>
       </c>
       <c r="E146" s="60">
-        <v>1700000</v>
+        <v>847000</v>
       </c>
       <c r="F146" s="60">
         <f t="shared" si="2"/>
-        <v>1530000</v>
+        <v>762300</v>
       </c>
       <c r="G146" s="34"/>
     </row>
-    <row r="147" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A147" s="31">
-        <f>IF(LEN(C147)=0,"",COUNTA($C$62:C147))</f>
-        <v>81</v>
-      </c>
-      <c r="B147" s="170"/>
+        <f>IF(LEN(C147)=0,"",COUNTA($C$63:C147))</f>
+        <v>80</v>
+      </c>
+      <c r="B147" s="186"/>
       <c r="C147" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D147" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="E147" s="60"/>
+        <v>153</v>
+      </c>
+      <c r="D147" s="98" t="s">
+        <v>325</v>
+      </c>
+      <c r="E147" s="60">
+        <v>1700000</v>
+      </c>
       <c r="F147" s="60">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1530000</v>
       </c>
       <c r="G147" s="34"/>
     </row>
-    <row r="148" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A148" s="31">
-        <f>IF(LEN(C148)=0,"",COUNTA($C$62:C148))</f>
-        <v>82</v>
-      </c>
-      <c r="B148" s="172" t="s">
-        <v>299</v>
-      </c>
+        <f>IF(LEN(C148)=0,"",COUNTA($C$63:C148))</f>
+        <v>81</v>
+      </c>
+      <c r="B148" s="186"/>
       <c r="C148" s="29" t="s">
-        <v>334</v>
+        <v>154</v>
       </c>
       <c r="D148" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="E148" s="97">
-        <v>3420000</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="E148" s="60"/>
       <c r="F148" s="60">
         <f t="shared" si="2"/>
-        <v>3078000</v>
-      </c>
-      <c r="G148" s="103" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="G148" s="34"/>
+    </row>
+    <row r="149" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="31">
-        <f>IF(LEN(C149)=0,"",COUNTA($C$62:C149))</f>
-        <v>83</v>
-      </c>
-      <c r="B149" s="172"/>
+        <f>IF(LEN(C149)=0,"",COUNTA($C$63:C149))</f>
+        <v>82</v>
+      </c>
+      <c r="B149" s="205" t="s">
+        <v>299</v>
+      </c>
       <c r="C149" s="29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D149" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E149" s="97">
         <v>3420000</v>
@@ -6057,19 +6239,22 @@
         <f t="shared" si="2"/>
         <v>3078000</v>
       </c>
-      <c r="G149" s="34"/>
-    </row>
-    <row r="150" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G149" s="221" t="s">
+        <v>327</v>
+      </c>
+      <c r="H149" s="10"/>
+    </row>
+    <row r="150" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A150" s="31">
-        <f>IF(LEN(C150)=0,"",COUNTA($C$62:C150))</f>
-        <v>84</v>
-      </c>
-      <c r="B150" s="172"/>
+        <f>IF(LEN(C150)=0,"",COUNTA($C$63:C150))</f>
+        <v>83</v>
+      </c>
+      <c r="B150" s="205"/>
       <c r="C150" s="29" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D150" s="29" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="E150" s="97">
         <v>3420000</v>
@@ -6078,21 +6263,20 @@
         <f t="shared" si="2"/>
         <v>3078000</v>
       </c>
-      <c r="G150" s="103" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G150" s="34"/>
+      <c r="H150" s="10"/>
+    </row>
+    <row r="151" spans="1:8" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="31">
-        <f>IF(LEN(C151)=0,"",COUNTA($C$62:C151))</f>
-        <v>85</v>
-      </c>
-      <c r="B151" s="172"/>
+        <f>IF(LEN(C151)=0,"",COUNTA($C$63:C151))</f>
+        <v>84</v>
+      </c>
+      <c r="B151" s="205"/>
       <c r="C151" s="29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D151" s="29" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E151" s="97">
         <v>3420000</v>
@@ -6101,19 +6285,22 @@
         <f t="shared" si="2"/>
         <v>3078000</v>
       </c>
-      <c r="G151" s="34"/>
-    </row>
-    <row r="152" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G151" s="221" t="s">
+        <v>327</v>
+      </c>
+      <c r="H151" s="10"/>
+    </row>
+    <row r="152" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="31">
-        <f>IF(LEN(C152)=0,"",COUNTA($C$62:C152))</f>
-        <v>86</v>
-      </c>
-      <c r="B152" s="172"/>
+        <f>IF(LEN(C152)=0,"",COUNTA($C$63:C152))</f>
+        <v>85</v>
+      </c>
+      <c r="B152" s="205"/>
       <c r="C152" s="29" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D152" s="29" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="E152" s="97">
         <v>3420000</v>
@@ -6124,271 +6311,271 @@
       </c>
       <c r="G152" s="34"/>
     </row>
-    <row r="153" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="31">
-        <f>IF(LEN(C153)=0,"",COUNTA($C$62:C153))</f>
-        <v>87</v>
-      </c>
-      <c r="B153" s="172"/>
-      <c r="C153" s="98" t="s">
-        <v>365</v>
+        <f>IF(LEN(C153)=0,"",COUNTA($C$63:C153))</f>
+        <v>86</v>
+      </c>
+      <c r="B153" s="205"/>
+      <c r="C153" s="29" t="s">
+        <v>338</v>
       </c>
       <c r="D153" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E153" s="97">
-        <v>5730000</v>
+        <v>3420000</v>
       </c>
       <c r="F153" s="60">
         <f t="shared" si="2"/>
-        <v>5157000</v>
+        <v>3078000</v>
       </c>
       <c r="G153" s="34"/>
     </row>
-    <row r="154" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="31">
-        <f>IF(LEN(C154)=0,"",COUNTA($C$62:C154))</f>
-        <v>88</v>
-      </c>
-      <c r="B154" s="172"/>
-      <c r="C154" s="29" t="s">
-        <v>339</v>
+        <f>IF(LEN(C154)=0,"",COUNTA($C$63:C154))</f>
+        <v>87</v>
+      </c>
+      <c r="B154" s="205"/>
+      <c r="C154" s="98" t="s">
+        <v>365</v>
       </c>
       <c r="D154" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E154" s="97">
-        <v>3420000</v>
+        <v>5730000</v>
       </c>
       <c r="F154" s="60">
         <f t="shared" si="2"/>
-        <v>3078000</v>
+        <v>5157000</v>
       </c>
       <c r="G154" s="34"/>
     </row>
-    <row r="155" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="31">
-        <f>IF(LEN(C155)=0,"",COUNTA($C$62:C155))</f>
-        <v>89</v>
-      </c>
-      <c r="B155" s="172"/>
+        <f>IF(LEN(C155)=0,"",COUNTA($C$63:C155))</f>
+        <v>88</v>
+      </c>
+      <c r="B155" s="205"/>
       <c r="C155" s="29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D155" s="29" t="s">
         <v>283</v>
       </c>
       <c r="E155" s="97">
-        <v>4530000</v>
+        <v>3420000</v>
       </c>
       <c r="F155" s="60">
         <f t="shared" si="2"/>
-        <v>4077000</v>
+        <v>3078000</v>
       </c>
       <c r="G155" s="34"/>
     </row>
-    <row r="156" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="31">
-        <f>IF(LEN(C156)=0,"",COUNTA($C$62:C156))</f>
-        <v>90</v>
-      </c>
-      <c r="B156" s="172"/>
+        <f>IF(LEN(C156)=0,"",COUNTA($C$63:C156))</f>
+        <v>89</v>
+      </c>
+      <c r="B156" s="205"/>
       <c r="C156" s="29" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D156" s="29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E156" s="97">
-        <v>3420000</v>
+        <v>4530000</v>
       </c>
       <c r="F156" s="60">
         <f t="shared" si="2"/>
-        <v>3078000</v>
+        <v>4077000</v>
       </c>
       <c r="G156" s="34"/>
     </row>
-    <row r="157" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="31">
-        <f>IF(LEN(C157)=0,"",COUNTA($C$62:C157))</f>
-        <v>91</v>
-      </c>
-      <c r="B157" s="172"/>
-      <c r="C157" s="98" t="s">
-        <v>364</v>
+        <f>IF(LEN(C157)=0,"",COUNTA($C$63:C157))</f>
+        <v>90</v>
+      </c>
+      <c r="B157" s="205"/>
+      <c r="C157" s="29" t="s">
+        <v>341</v>
       </c>
       <c r="D157" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E157" s="97">
-        <v>5515200</v>
+        <v>3420000</v>
       </c>
       <c r="F157" s="60">
         <f t="shared" si="2"/>
-        <v>4963680</v>
+        <v>3078000</v>
       </c>
       <c r="G157" s="34"/>
     </row>
-    <row r="158" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A158" s="31">
-        <f>IF(LEN(C158)=0,"",COUNTA($C$62:C158))</f>
-        <v>92</v>
-      </c>
-      <c r="B158" s="172"/>
-      <c r="C158" s="29" t="s">
-        <v>342</v>
+        <f>IF(LEN(C158)=0,"",COUNTA($C$63:C158))</f>
+        <v>91</v>
+      </c>
+      <c r="B158" s="205"/>
+      <c r="C158" s="98" t="s">
+        <v>364</v>
       </c>
       <c r="D158" s="29" t="s">
-        <v>287</v>
-      </c>
-      <c r="E158" s="64">
-        <v>2790000</v>
+        <v>285</v>
+      </c>
+      <c r="E158" s="97">
+        <v>5515200</v>
       </c>
       <c r="F158" s="60">
         <f t="shared" si="2"/>
-        <v>2511000</v>
-      </c>
-      <c r="G158" s="104" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+        <v>4963680</v>
+      </c>
+      <c r="G158" s="34"/>
+    </row>
+    <row r="159" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A159" s="31">
-        <f>IF(LEN(C159)=0,"",COUNTA($C$62:C159))</f>
-        <v>93</v>
-      </c>
-      <c r="B159" s="172"/>
+        <f>IF(LEN(C159)=0,"",COUNTA($C$63:C159))</f>
+        <v>92</v>
+      </c>
+      <c r="B159" s="205"/>
       <c r="C159" s="29" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D159" s="29" t="s">
-        <v>288</v>
-      </c>
-      <c r="E159" s="97">
-        <v>3078000</v>
+        <v>287</v>
+      </c>
+      <c r="E159" s="64">
+        <v>2790000</v>
       </c>
       <c r="F159" s="60">
         <f t="shared" si="2"/>
-        <v>2770200</v>
-      </c>
-      <c r="G159" s="34"/>
-    </row>
-    <row r="160" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+        <v>2511000</v>
+      </c>
+      <c r="G159" s="104" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A160" s="31">
-        <f>IF(LEN(C160)=0,"",COUNTA($C$62:C160))</f>
-        <v>94</v>
-      </c>
-      <c r="B160" s="172"/>
+        <f>IF(LEN(C160)=0,"",COUNTA($C$63:C160))</f>
+        <v>93</v>
+      </c>
+      <c r="B160" s="205"/>
       <c r="C160" s="29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D160" s="29" t="s">
         <v>288</v>
       </c>
       <c r="E160" s="97">
-        <v>4200000</v>
+        <v>3078000</v>
       </c>
       <c r="F160" s="60">
         <f t="shared" si="2"/>
-        <v>3780000</v>
+        <v>2770200</v>
       </c>
       <c r="G160" s="34"/>
     </row>
     <row r="161" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A161" s="31">
-        <f>IF(LEN(C161)=0,"",COUNTA($C$62:C161))</f>
-        <v>95</v>
-      </c>
-      <c r="B161" s="172"/>
+        <f>IF(LEN(C161)=0,"",COUNTA($C$63:C161))</f>
+        <v>94</v>
+      </c>
+      <c r="B161" s="205"/>
       <c r="C161" s="29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D161" s="29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E161" s="97">
-        <v>3078000</v>
+        <v>4200000</v>
       </c>
       <c r="F161" s="60">
         <f t="shared" si="2"/>
-        <v>2770200</v>
+        <v>3780000</v>
       </c>
       <c r="G161" s="34"/>
     </row>
     <row r="162" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A162" s="31">
-        <f>IF(LEN(C162)=0,"",COUNTA($C$62:C162))</f>
-        <v>96</v>
-      </c>
-      <c r="B162" s="172"/>
+        <f>IF(LEN(C162)=0,"",COUNTA($C$63:C162))</f>
+        <v>95</v>
+      </c>
+      <c r="B162" s="205"/>
       <c r="C162" s="29" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D162" s="29" t="s">
         <v>289</v>
       </c>
       <c r="E162" s="97">
-        <v>4200000</v>
+        <v>3078000</v>
       </c>
       <c r="F162" s="60">
         <f t="shared" si="2"/>
-        <v>3780000</v>
+        <v>2770200</v>
       </c>
       <c r="G162" s="34"/>
     </row>
     <row r="163" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A163" s="31">
-        <f>IF(LEN(C163)=0,"",COUNTA($C$62:C163))</f>
-        <v>97</v>
-      </c>
-      <c r="B163" s="172"/>
+        <f>IF(LEN(C163)=0,"",COUNTA($C$63:C163))</f>
+        <v>96</v>
+      </c>
+      <c r="B163" s="205"/>
       <c r="C163" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D163" s="29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E163" s="97">
-        <v>3078000</v>
+        <v>4200000</v>
       </c>
       <c r="F163" s="60">
         <f t="shared" si="2"/>
-        <v>2770200</v>
+        <v>3780000</v>
       </c>
       <c r="G163" s="34"/>
     </row>
-    <row r="164" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A164" s="31">
-        <f>IF(LEN(C164)=0,"",COUNTA($C$62:C164))</f>
-        <v>98</v>
-      </c>
-      <c r="B164" s="172"/>
+        <f>IF(LEN(C164)=0,"",COUNTA($C$63:C164))</f>
+        <v>97</v>
+      </c>
+      <c r="B164" s="205"/>
       <c r="C164" s="29" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D164" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E164" s="97">
-        <v>3420000</v>
+        <v>3078000</v>
       </c>
       <c r="F164" s="60">
         <f t="shared" si="2"/>
-        <v>3078000</v>
+        <v>2770200</v>
       </c>
       <c r="G164" s="34"/>
     </row>
     <row r="165" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A165" s="31">
-        <f>IF(LEN(C165)=0,"",COUNTA($C$62:C165))</f>
-        <v>99</v>
-      </c>
-      <c r="B165" s="172"/>
+        <f>IF(LEN(C165)=0,"",COUNTA($C$63:C165))</f>
+        <v>98</v>
+      </c>
+      <c r="B165" s="205"/>
       <c r="C165" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D165" s="29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E165" s="97">
         <v>3420000</v>
@@ -6401,15 +6588,15 @@
     </row>
     <row r="166" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A166" s="31">
-        <f>IF(LEN(C166)=0,"",COUNTA($C$62:C166))</f>
-        <v>100</v>
-      </c>
-      <c r="B166" s="172"/>
+        <f>IF(LEN(C166)=0,"",COUNTA($C$63:C166))</f>
+        <v>99</v>
+      </c>
+      <c r="B166" s="205"/>
       <c r="C166" s="29" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D166" s="29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E166" s="97">
         <v>3420000</v>
@@ -6422,15 +6609,15 @@
     </row>
     <row r="167" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A167" s="31">
-        <f>IF(LEN(C167)=0,"",COUNTA($C$62:C167))</f>
-        <v>101</v>
-      </c>
-      <c r="B167" s="172"/>
+        <f>IF(LEN(C167)=0,"",COUNTA($C$63:C167))</f>
+        <v>100</v>
+      </c>
+      <c r="B167" s="205"/>
       <c r="C167" s="29" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D167" s="29" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E167" s="97">
         <v>3420000</v>
@@ -6443,115 +6630,117 @@
     </row>
     <row r="168" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A168" s="31">
-        <f>IF(LEN(C168)=0,"",COUNTA($C$62:C168))</f>
-        <v>102</v>
-      </c>
-      <c r="B168" s="172"/>
+        <f>IF(LEN(C168)=0,"",COUNTA($C$63:C168))</f>
+        <v>101</v>
+      </c>
+      <c r="B168" s="205"/>
       <c r="C168" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D168" s="29" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E168" s="97">
-        <v>7740000</v>
+        <v>3420000</v>
       </c>
       <c r="F168" s="60">
         <f t="shared" si="2"/>
-        <v>6966000</v>
+        <v>3078000</v>
       </c>
       <c r="G168" s="34"/>
     </row>
     <row r="169" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A169" s="31">
-        <f>IF(LEN(C169)=0,"",COUNTA($C$62:C169))</f>
-        <v>103</v>
-      </c>
-      <c r="B169" s="172"/>
+        <f>IF(LEN(C169)=0,"",COUNTA($C$63:C169))</f>
+        <v>102</v>
+      </c>
+      <c r="B169" s="205"/>
       <c r="C169" s="29" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D169" s="29" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="E169" s="97">
-        <v>3420000</v>
+        <v>7740000</v>
       </c>
       <c r="F169" s="60">
         <f t="shared" si="2"/>
-        <v>3078000</v>
+        <v>6966000</v>
       </c>
       <c r="G169" s="34"/>
     </row>
-    <row r="170" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A170" s="31">
-        <f>IF(LEN(C170)=0,"",COUNTA($C$62:C170))</f>
-        <v>104</v>
-      </c>
-      <c r="B170" s="172"/>
+        <f>IF(LEN(C170)=0,"",COUNTA($C$63:C170))</f>
+        <v>103</v>
+      </c>
+      <c r="B170" s="205"/>
       <c r="C170" s="29" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D170" s="29" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E170" s="97">
-        <v>4740000</v>
+        <v>3420000</v>
       </c>
       <c r="F170" s="60">
         <f t="shared" si="2"/>
-        <v>4266000</v>
+        <v>3078000</v>
       </c>
       <c r="G170" s="34"/>
     </row>
-    <row r="171" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A171" s="31">
-        <f>IF(LEN(C171)=0,"",COUNTA($C$62:C171))</f>
-        <v>105</v>
-      </c>
-      <c r="B171" s="172"/>
+        <f>IF(LEN(C171)=0,"",COUNTA($C$63:C171))</f>
+        <v>104</v>
+      </c>
+      <c r="B171" s="205"/>
       <c r="C171" s="29" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D171" s="29" t="s">
-        <v>303</v>
-      </c>
-      <c r="E171" s="64">
-        <v>3720000</v>
+        <v>302</v>
+      </c>
+      <c r="E171" s="97">
+        <v>4740000</v>
       </c>
       <c r="F171" s="60">
         <f t="shared" si="2"/>
-        <v>3348000</v>
+        <v>4266000</v>
       </c>
       <c r="G171" s="34"/>
     </row>
     <row r="172" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A172" s="31">
-        <f>IF(LEN(C172)=0,"",COUNTA($C$62:C172))</f>
-        <v>106</v>
-      </c>
-      <c r="B172" s="172"/>
+        <f>IF(LEN(C172)=0,"",COUNTA($C$63:C172))</f>
+        <v>105</v>
+      </c>
+      <c r="B172" s="205"/>
       <c r="C172" s="29" t="s">
-        <v>356</v>
-      </c>
-      <c r="D172" s="29"/>
-      <c r="E172" s="97">
-        <v>6060000</v>
+        <v>355</v>
+      </c>
+      <c r="D172" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="E172" s="64">
+        <v>3720000</v>
       </c>
       <c r="F172" s="60">
         <f t="shared" si="2"/>
-        <v>5454000</v>
+        <v>3348000</v>
       </c>
       <c r="G172" s="34"/>
     </row>
     <row r="173" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A173" s="31">
-        <f>IF(LEN(C173)=0,"",COUNTA($C$62:C173))</f>
-        <v>107</v>
-      </c>
-      <c r="B173" s="172"/>
+        <f>IF(LEN(C173)=0,"",COUNTA($C$63:C173))</f>
+        <v>106</v>
+      </c>
+      <c r="B173" s="205"/>
       <c r="C173" s="29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D173" s="29"/>
       <c r="E173" s="97">
@@ -6565,171 +6754,167 @@
     </row>
     <row r="174" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A174" s="31">
-        <f>IF(LEN(C174)=0,"",COUNTA($C$62:C174))</f>
-        <v>108</v>
-      </c>
-      <c r="B174" s="172"/>
+        <f>IF(LEN(C174)=0,"",COUNTA($C$63:C174))</f>
+        <v>107</v>
+      </c>
+      <c r="B174" s="205"/>
       <c r="C174" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="D174" s="29" t="s">
-        <v>296</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="D174" s="29"/>
       <c r="E174" s="97">
-        <v>5520000</v>
+        <v>6060000</v>
       </c>
       <c r="F174" s="60">
         <f t="shared" si="2"/>
-        <v>4968000</v>
+        <v>5454000</v>
       </c>
       <c r="G174" s="34"/>
     </row>
     <row r="175" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A175" s="31">
-        <f>IF(LEN(C175)=0,"",COUNTA($C$62:C175))</f>
-        <v>109</v>
-      </c>
-      <c r="B175" s="172"/>
+        <f>IF(LEN(C175)=0,"",COUNTA($C$63:C175))</f>
+        <v>108</v>
+      </c>
+      <c r="B175" s="205"/>
       <c r="C175" s="29" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D175" s="29" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E175" s="97">
-        <v>9930000</v>
+        <v>5520000</v>
       </c>
       <c r="F175" s="60">
         <f t="shared" si="2"/>
-        <v>8937000</v>
+        <v>4968000</v>
       </c>
       <c r="G175" s="34"/>
     </row>
     <row r="176" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A176" s="31">
-        <f>IF(LEN(C176)=0,"",COUNTA($C$62:C176))</f>
-        <v>110</v>
-      </c>
-      <c r="B176" s="172"/>
+        <f>IF(LEN(C176)=0,"",COUNTA($C$63:C176))</f>
+        <v>109</v>
+      </c>
+      <c r="B176" s="205"/>
       <c r="C176" s="29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D176" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E176" s="97">
-        <v>7740000</v>
+        <v>9930000</v>
       </c>
       <c r="F176" s="60">
         <f t="shared" si="2"/>
-        <v>6966000</v>
+        <v>8937000</v>
       </c>
       <c r="G176" s="34"/>
     </row>
     <row r="177" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A177" s="31">
-        <f>IF(LEN(C177)=0,"",COUNTA($C$62:C177))</f>
-        <v>111</v>
-      </c>
-      <c r="B177" s="172"/>
+        <f>IF(LEN(C177)=0,"",COUNTA($C$63:C177))</f>
+        <v>110</v>
+      </c>
+      <c r="B177" s="205"/>
       <c r="C177" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D177" s="29" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E177" s="97">
-        <v>23160000</v>
+        <v>7740000</v>
       </c>
       <c r="F177" s="60">
         <f t="shared" si="2"/>
+        <v>6966000</v>
+      </c>
+      <c r="G177" s="34"/>
+    </row>
+    <row r="178" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="A178" s="31">
+        <f>IF(LEN(C178)=0,"",COUNTA($C$63:C178))</f>
+        <v>111</v>
+      </c>
+      <c r="B178" s="205"/>
+      <c r="C178" s="29" t="s">
+        <v>361</v>
+      </c>
+      <c r="D178" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="E178" s="97">
+        <v>23160000</v>
+      </c>
+      <c r="F178" s="60">
+        <f t="shared" si="2"/>
         <v>20844000</v>
       </c>
-      <c r="G177" s="34"/>
-    </row>
-    <row r="178" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A178" s="156" t="s">
+      <c r="G178" s="34"/>
+    </row>
+    <row r="179" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A179" s="203" t="s">
         <v>201</v>
       </c>
-      <c r="B178" s="156"/>
-      <c r="C178" s="156"/>
-      <c r="D178" s="156"/>
-      <c r="E178" s="69"/>
-      <c r="F178" s="69"/>
-      <c r="G178" s="59"/>
-    </row>
-    <row r="179" spans="1:8" ht="33" x14ac:dyDescent="0.25">
-      <c r="A179" s="31">
-        <f>IF(LEN(C179)=0,"",COUNTA($C$62:C179))</f>
+      <c r="B179" s="203"/>
+      <c r="C179" s="203"/>
+      <c r="D179" s="203"/>
+      <c r="E179" s="69"/>
+      <c r="F179" s="69"/>
+      <c r="G179" s="59"/>
+    </row>
+    <row r="180" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="A180" s="31">
+        <f>IF(LEN(C180)=0,"",COUNTA($C$63:C180))</f>
         <v>112</v>
       </c>
-      <c r="B179" s="70"/>
-      <c r="C179" s="29" t="s">
+      <c r="B180" s="70"/>
+      <c r="C180" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="D179" s="29" t="s">
+      <c r="D180" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="E179" s="64">
+      <c r="E180" s="64">
         <v>88000</v>
       </c>
-      <c r="F179" s="60">
+      <c r="F180" s="60">
         <f t="shared" si="2"/>
         <v>79200</v>
       </c>
-      <c r="G179" s="34"/>
-    </row>
-    <row r="180" spans="1:8" ht="33" x14ac:dyDescent="0.25">
-      <c r="A180" s="31">
-        <f>IF(LEN(C180)=0,"",COUNTA($C$62:C180))</f>
+      <c r="G180" s="34"/>
+    </row>
+    <row r="181" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="A181" s="31">
+        <f>IF(LEN(C181)=0,"",COUNTA($C$63:C181))</f>
         <v>113</v>
       </c>
-      <c r="B180" s="71"/>
-      <c r="C180" s="72" t="s">
+      <c r="B181" s="71"/>
+      <c r="C181" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="D180" s="72" t="s">
+      <c r="D181" s="72" t="s">
         <v>144</v>
       </c>
-      <c r="E180" s="73">
+      <c r="E181" s="73">
         <v>450000</v>
       </c>
-      <c r="F180" s="60">
+      <c r="F181" s="60">
         <f t="shared" si="2"/>
         <v>405000</v>
       </c>
-      <c r="G180" s="34"/>
-      <c r="H180" s="10"/>
-    </row>
-    <row r="181" spans="1:8" s="13" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A181" s="31">
-        <f>IF(LEN(C181)=0,"",COUNTA($C$62:C181))</f>
-        <v>114</v>
-      </c>
-      <c r="B181" s="169" t="s">
-        <v>199</v>
-      </c>
-      <c r="C181" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="D181" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="E181" s="64">
-        <v>178000</v>
-      </c>
-      <c r="F181" s="60">
-        <f t="shared" si="2"/>
-        <v>160200</v>
-      </c>
       <c r="G181" s="34"/>
+      <c r="H181" s="10"/>
     </row>
     <row r="182" spans="1:8" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A182" s="31">
-        <f>IF(LEN(C182)=0,"",COUNTA($C$62:C182))</f>
-        <v>115</v>
-      </c>
-      <c r="B182" s="171"/>
+        <f>IF(LEN(C182)=0,"",COUNTA($C$63:C182))</f>
+        <v>114</v>
+      </c>
+      <c r="B182" s="63"/>
       <c r="C182" s="29" t="s">
         <v>219</v>
       </c>
@@ -6746,20 +6931,20 @@
       <c r="G182" s="34"/>
     </row>
     <row r="183" spans="1:8" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A183" s="159" t="s">
+      <c r="A183" s="191" t="s">
         <v>159</v>
       </c>
-      <c r="B183" s="160"/>
-      <c r="C183" s="160"/>
-      <c r="D183" s="161"/>
+      <c r="B183" s="192"/>
+      <c r="C183" s="192"/>
+      <c r="D183" s="193"/>
       <c r="E183" s="108"/>
       <c r="F183" s="108"/>
       <c r="G183" s="54"/>
     </row>
     <row r="184" spans="1:8" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A184" s="31">
-        <f>IF(LEN(C184)=0,"",COUNTA($C$62:C184))</f>
-        <v>116</v>
+        <f>IF(LEN(C184)=0,"",COUNTA($C$63:C184))</f>
+        <v>115</v>
       </c>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
@@ -6775,14 +6960,14 @@
         <f t="shared" si="2"/>
         <v>63900</v>
       </c>
-      <c r="G184" s="154" t="s">
+      <c r="G184" s="201" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="185" spans="1:8" s="14" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A185" s="31">
-        <f>IF(LEN(C185)=0,"",COUNTA($C$62:C185))</f>
-        <v>117</v>
+        <f>IF(LEN(C185)=0,"",COUNTA($C$63:C185))</f>
+        <v>116</v>
       </c>
       <c r="B185" s="75"/>
       <c r="C185" s="76" t="s">
@@ -6798,15 +6983,15 @@
         <f t="shared" si="2"/>
         <v>77400</v>
       </c>
-      <c r="G185" s="155"/>
+      <c r="G185" s="202"/>
     </row>
     <row r="186" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A186" s="156" t="s">
+      <c r="A186" s="203" t="s">
         <v>164</v>
       </c>
-      <c r="B186" s="156"/>
-      <c r="C186" s="156"/>
-      <c r="D186" s="156"/>
+      <c r="B186" s="203"/>
+      <c r="C186" s="203"/>
+      <c r="D186" s="203"/>
       <c r="E186" s="69"/>
       <c r="F186" s="69"/>
       <c r="G186" s="59"/>
@@ -6830,12 +7015,13 @@
         <f t="shared" si="2"/>
         <v>1771200</v>
       </c>
-      <c r="G187" s="9"/>
+      <c r="G187" s="123"/>
+      <c r="H187" s="10"/>
     </row>
     <row r="188" spans="1:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="31">
-        <f>IF(LEN(C188)=0,"",COUNTA($C$62:C188))</f>
-        <v>119</v>
+        <f>IF(LEN(C188)=0,"",COUNTA($C$63:C188))</f>
+        <v>118</v>
       </c>
       <c r="B188" s="32"/>
       <c r="C188" s="29" t="s">
@@ -6851,12 +7037,12 @@
         <f t="shared" si="2"/>
         <v>2656800</v>
       </c>
-      <c r="G188" s="157"/>
+      <c r="G188" s="180"/>
     </row>
     <row r="189" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A189" s="31">
-        <f>IF(LEN(C189)=0,"",COUNTA($C$62:C189))</f>
-        <v>120</v>
+        <f>IF(LEN(C189)=0,"",COUNTA($C$63:C189))</f>
+        <v>119</v>
       </c>
       <c r="B189" s="32"/>
       <c r="C189" s="29" t="s">
@@ -6872,12 +7058,12 @@
         <f t="shared" si="2"/>
         <v>3690000</v>
       </c>
-      <c r="G189" s="158"/>
+      <c r="G189" s="181"/>
     </row>
     <row r="190" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A190" s="31">
-        <f>IF(LEN(C190)=0,"",COUNTA($C$62:C190))</f>
-        <v>121</v>
+        <f>IF(LEN(C190)=0,"",COUNTA($C$63:C190))</f>
+        <v>120</v>
       </c>
       <c r="B190" s="32"/>
       <c r="C190" s="29" t="s">
@@ -6897,8 +7083,8 @@
     </row>
     <row r="191" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A191" s="31">
-        <f>IF(LEN(C191)=0,"",COUNTA($C$62:C191))</f>
-        <v>122</v>
+        <f>IF(LEN(C191)=0,"",COUNTA($C$63:C191))</f>
+        <v>121</v>
       </c>
       <c r="B191" s="32"/>
       <c r="C191" s="29" t="s">
@@ -6918,8 +7104,8 @@
     </row>
     <row r="192" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A192" s="31">
-        <f>IF(LEN(C192)=0,"",COUNTA($C$62:C192))</f>
-        <v>123</v>
+        <f>IF(LEN(C192)=0,"",COUNTA($C$63:C192))</f>
+        <v>122</v>
       </c>
       <c r="B192" s="32"/>
       <c r="C192" s="29" t="s">
@@ -6939,8 +7125,8 @@
     </row>
     <row r="193" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A193" s="31">
-        <f>IF(LEN(C193)=0,"",COUNTA($C$62:C193))</f>
-        <v>124</v>
+        <f>IF(LEN(C193)=0,"",COUNTA($C$63:C193))</f>
+        <v>123</v>
       </c>
       <c r="B193" s="32"/>
       <c r="C193" s="29" t="s">
@@ -6959,20 +7145,20 @@
       <c r="G193" s="34"/>
     </row>
     <row r="194" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A194" s="156" t="s">
+      <c r="A194" s="203" t="s">
         <v>258</v>
       </c>
-      <c r="B194" s="156"/>
-      <c r="C194" s="156"/>
-      <c r="D194" s="156"/>
+      <c r="B194" s="203"/>
+      <c r="C194" s="203"/>
+      <c r="D194" s="203"/>
       <c r="E194" s="69"/>
       <c r="F194" s="69"/>
       <c r="G194" s="59"/>
     </row>
     <row r="195" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A195" s="31">
-        <f>IF(LEN(C195)=0,"",COUNTA($C$62:C195))</f>
-        <v>125</v>
+        <f>IF(LEN(C195)=0,"",COUNTA($C$63:C195))</f>
+        <v>124</v>
       </c>
       <c r="B195" s="32"/>
       <c r="C195" s="29" t="s">
@@ -6991,20 +7177,20 @@
       <c r="G195" s="34"/>
     </row>
     <row r="196" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A196" s="156" t="s">
+      <c r="A196" s="203" t="s">
         <v>228</v>
       </c>
-      <c r="B196" s="156"/>
-      <c r="C196" s="156"/>
-      <c r="D196" s="156"/>
+      <c r="B196" s="203"/>
+      <c r="C196" s="203"/>
+      <c r="D196" s="203"/>
       <c r="E196" s="69"/>
       <c r="F196" s="69"/>
       <c r="G196" s="59"/>
     </row>
     <row r="197" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A197" s="31">
-        <f>IF(LEN(C197)=0,"",COUNTA($C$62:C197))</f>
-        <v>126</v>
+        <f>IF(LEN(C197)=0,"",COUNTA($C$63:C197))</f>
+        <v>125</v>
       </c>
       <c r="B197" s="70"/>
       <c r="C197" s="30" t="s">
@@ -7024,8 +7210,8 @@
     </row>
     <row r="198" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A198" s="31">
-        <f>IF(LEN(C198)=0,"",COUNTA($C$62:C198))</f>
-        <v>127</v>
+        <f>IF(LEN(C198)=0,"",COUNTA($C$63:C198))</f>
+        <v>126</v>
       </c>
       <c r="B198" s="70"/>
       <c r="C198" s="30" t="s">
@@ -7045,8 +7231,8 @@
     </row>
     <row r="199" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A199" s="31">
-        <f>IF(LEN(C199)=0,"",COUNTA($C$62:C199))</f>
-        <v>128</v>
+        <f>IF(LEN(C199)=0,"",COUNTA($C$63:C199))</f>
+        <v>127</v>
       </c>
       <c r="B199" s="70"/>
       <c r="C199" s="30" t="s">
@@ -7066,8 +7252,8 @@
     </row>
     <row r="200" spans="1:7" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="31">
-        <f>IF(LEN(C200)=0,"",COUNTA($C$62:C200))</f>
-        <v>129</v>
+        <f>IF(LEN(C200)=0,"",COUNTA($C$63:C200))</f>
+        <v>128</v>
       </c>
       <c r="B200" s="70"/>
       <c r="C200" s="76" t="s">
@@ -7087,8 +7273,8 @@
     </row>
     <row r="201" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="31">
-        <f>IF(LEN(C201)=0,"",COUNTA($C$62:C201))</f>
-        <v>130</v>
+        <f>IF(LEN(C201)=0,"",COUNTA($C$63:C201))</f>
+        <v>129</v>
       </c>
       <c r="B201" s="70"/>
       <c r="C201" s="29" t="s">
@@ -7108,8 +7294,8 @@
     </row>
     <row r="202" spans="1:7" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="31">
-        <f>IF(LEN(C202)=0,"",COUNTA($C$62:C202))</f>
-        <v>131</v>
+        <f>IF(LEN(C202)=0,"",COUNTA($C$63:C202))</f>
+        <v>130</v>
       </c>
       <c r="B202" s="70"/>
       <c r="C202" s="29" t="s">
@@ -7129,8 +7315,8 @@
     </row>
     <row r="203" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A203" s="31">
-        <f>IF(LEN(C203)=0,"",COUNTA($C$62:C203))</f>
-        <v>132</v>
+        <f>IF(LEN(C203)=0,"",COUNTA($C$63:C203))</f>
+        <v>131</v>
       </c>
       <c r="B203" s="70"/>
       <c r="C203" s="29" t="s">
@@ -7149,20 +7335,20 @@
       <c r="G203" s="34"/>
     </row>
     <row r="204" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A204" s="159" t="s">
+      <c r="A204" s="191" t="s">
         <v>317</v>
       </c>
-      <c r="B204" s="160"/>
-      <c r="C204" s="160"/>
-      <c r="D204" s="161"/>
+      <c r="B204" s="192"/>
+      <c r="C204" s="192"/>
+      <c r="D204" s="193"/>
       <c r="E204" s="58"/>
       <c r="F204" s="58"/>
       <c r="G204" s="59"/>
     </row>
     <row r="205" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A205" s="31">
-        <f>IF(LEN(C205)=0,"",COUNTA($C$62:C205))</f>
-        <v>133</v>
+        <f>IF(LEN(C205)=0,"",COUNTA($C$63:C205))</f>
+        <v>132</v>
       </c>
       <c r="B205" s="70"/>
       <c r="C205" s="29" t="s">
@@ -7180,8 +7366,8 @@
     </row>
     <row r="206" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A206" s="31">
-        <f>IF(LEN(C206)=0,"",COUNTA($C$62:C206))</f>
-        <v>134</v>
+        <f>IF(LEN(C206)=0,"",COUNTA($C$63:C206))</f>
+        <v>133</v>
       </c>
       <c r="B206" s="70"/>
       <c r="C206" s="29" t="s">
@@ -7201,8 +7387,8 @@
     </row>
     <row r="207" spans="1:7" ht="132" x14ac:dyDescent="0.25">
       <c r="A207" s="31">
-        <f>IF(LEN(C207)=0,"",COUNTA($C$62:C207))</f>
-        <v>135</v>
+        <f>IF(LEN(C207)=0,"",COUNTA($C$63:C207))</f>
+        <v>134</v>
       </c>
       <c r="B207" s="70"/>
       <c r="C207" s="29" t="s">
@@ -7222,8 +7408,8 @@
     </row>
     <row r="208" spans="1:7" ht="99" x14ac:dyDescent="0.25">
       <c r="A208" s="31">
-        <f>IF(LEN(C208)=0,"",COUNTA($C$62:C208))</f>
-        <v>136</v>
+        <f>IF(LEN(C208)=0,"",COUNTA($C$63:C208))</f>
+        <v>135</v>
       </c>
       <c r="B208" s="70"/>
       <c r="C208" s="29" t="s">
@@ -7243,8 +7429,8 @@
     </row>
     <row r="209" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A209" s="31">
-        <f>IF(LEN(C209)=0,"",COUNTA($C$62:C209))</f>
-        <v>137</v>
+        <f>IF(LEN(C209)=0,"",COUNTA($C$63:C209))</f>
+        <v>136</v>
       </c>
       <c r="B209" s="70"/>
       <c r="C209" s="29" t="s">
@@ -7263,20 +7449,20 @@
       <c r="G209" s="34"/>
     </row>
     <row r="210" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A210" s="159" t="s">
+      <c r="A210" s="191" t="s">
         <v>216</v>
       </c>
-      <c r="B210" s="160"/>
-      <c r="C210" s="160"/>
-      <c r="D210" s="161"/>
+      <c r="B210" s="192"/>
+      <c r="C210" s="192"/>
+      <c r="D210" s="193"/>
       <c r="E210" s="58"/>
       <c r="F210" s="58"/>
       <c r="G210" s="59"/>
     </row>
     <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A211" s="31">
-        <f>IF(LEN(C211)=0,"",COUNTA($C$62:C211))</f>
-        <v>138</v>
+        <f>IF(LEN(C211)=0,"",COUNTA($C$63:C211))</f>
+        <v>137</v>
       </c>
       <c r="B211" s="70"/>
       <c r="C211" s="77" t="s">
@@ -7296,8 +7482,8 @@
     </row>
     <row r="212" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A212" s="31">
-        <f>IF(LEN(C212)=0,"",COUNTA($C$62:C212))</f>
-        <v>139</v>
+        <f>IF(LEN(C212)=0,"",COUNTA($C$63:C212))</f>
+        <v>138</v>
       </c>
       <c r="B212" s="70"/>
       <c r="C212" s="79" t="s">
@@ -7317,8 +7503,8 @@
     </row>
     <row r="213" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A213" s="31">
-        <f>IF(LEN(C213)=0,"",COUNTA($C$62:C213))</f>
-        <v>140</v>
+        <f>IF(LEN(C213)=0,"",COUNTA($C$63:C213))</f>
+        <v>139</v>
       </c>
       <c r="B213" s="70"/>
       <c r="C213" s="79" t="s">
@@ -7337,30 +7523,30 @@
       <c r="G213" s="34"/>
     </row>
     <row r="214" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A214" s="159" t="s">
+      <c r="A214" s="191" t="s">
         <v>205</v>
       </c>
-      <c r="B214" s="160"/>
-      <c r="C214" s="160"/>
-      <c r="D214" s="161"/>
+      <c r="B214" s="192"/>
+      <c r="C214" s="192"/>
+      <c r="D214" s="193"/>
       <c r="E214" s="58"/>
       <c r="F214" s="58"/>
       <c r="G214" s="59"/>
     </row>
     <row r="215" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A215" s="31">
-        <f>IF(LEN(C215)=0,"",COUNTA($C$62:C215))</f>
-        <v>141</v>
+        <f>IF(LEN(C215)=0,"",COUNTA($C$63:C215))</f>
+        <v>140</v>
       </c>
       <c r="B215" s="70"/>
       <c r="C215" s="29" t="s">
         <v>206</v>
       </c>
       <c r="D215" s="29"/>
-      <c r="E215" s="162">
+      <c r="E215" s="207">
         <v>183000</v>
       </c>
-      <c r="F215" s="200">
+      <c r="F215" s="210">
         <f>E215*90%</f>
         <v>164700</v>
       </c>
@@ -7368,61 +7554,61 @@
     </row>
     <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A216" s="31">
-        <f>IF(LEN(C216)=0,"",COUNTA($C$62:C216))</f>
-        <v>142</v>
+        <f>IF(LEN(C216)=0,"",COUNTA($C$63:C216))</f>
+        <v>141</v>
       </c>
       <c r="B216" s="70"/>
       <c r="C216" s="29" t="s">
         <v>207</v>
       </c>
       <c r="D216" s="29"/>
-      <c r="E216" s="163"/>
-      <c r="F216" s="201"/>
+      <c r="E216" s="208"/>
+      <c r="F216" s="211"/>
       <c r="G216" s="34"/>
     </row>
     <row r="217" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A217" s="31">
-        <f>IF(LEN(C217)=0,"",COUNTA($C$62:C217))</f>
-        <v>143</v>
+        <f>IF(LEN(C217)=0,"",COUNTA($C$63:C217))</f>
+        <v>142</v>
       </c>
       <c r="B217" s="70"/>
       <c r="C217" s="29" t="s">
         <v>208</v>
       </c>
       <c r="D217" s="29"/>
-      <c r="E217" s="163"/>
-      <c r="F217" s="201"/>
+      <c r="E217" s="208"/>
+      <c r="F217" s="211"/>
       <c r="G217" s="34"/>
     </row>
     <row r="218" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A218" s="31">
-        <f>IF(LEN(C218)=0,"",COUNTA($C$62:C218))</f>
-        <v>144</v>
+        <f>IF(LEN(C218)=0,"",COUNTA($C$63:C218))</f>
+        <v>143</v>
       </c>
       <c r="B218" s="70"/>
       <c r="C218" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D218" s="29"/>
-      <c r="E218" s="164"/>
-      <c r="F218" s="202"/>
+      <c r="E218" s="209"/>
+      <c r="F218" s="212"/>
       <c r="G218" s="34"/>
     </row>
     <row r="219" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A219" s="159" t="s">
+      <c r="A219" s="191" t="s">
         <v>403</v>
       </c>
-      <c r="B219" s="160"/>
-      <c r="C219" s="160"/>
-      <c r="D219" s="161"/>
+      <c r="B219" s="192"/>
+      <c r="C219" s="192"/>
+      <c r="D219" s="193"/>
       <c r="E219" s="58"/>
       <c r="F219" s="58"/>
       <c r="G219" s="59"/>
     </row>
     <row r="220" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A220" s="31">
-        <f>IF(LEN(C220)=0,"",COUNTA($C$62:C220))</f>
-        <v>145</v>
+        <f>IF(LEN(C220)=0,"",COUNTA($C$63:C220))</f>
+        <v>144</v>
       </c>
       <c r="B220" s="70"/>
       <c r="C220" s="29" t="s">
@@ -7440,8 +7626,8 @@
     </row>
     <row r="221" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A221" s="31">
-        <f>IF(LEN(C221)=0,"",COUNTA($C$62:C221))</f>
-        <v>146</v>
+        <f>IF(LEN(C221)=0,"",COUNTA($C$63:C221))</f>
+        <v>145</v>
       </c>
       <c r="B221" s="70"/>
       <c r="C221" s="29" t="s">
@@ -7459,8 +7645,8 @@
     </row>
     <row r="222" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A222" s="31">
-        <f>IF(LEN(C222)=0,"",COUNTA($C$62:C222))</f>
-        <v>147</v>
+        <f>IF(LEN(C222)=0,"",COUNTA($C$63:C222))</f>
+        <v>146</v>
       </c>
       <c r="B222" s="70"/>
       <c r="C222" s="29" t="s">
@@ -7478,8 +7664,8 @@
     </row>
     <row r="223" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A223" s="31">
-        <f>IF(LEN(C223)=0,"",COUNTA($C$62:C223))</f>
-        <v>148</v>
+        <f>IF(LEN(C223)=0,"",COUNTA($C$63:C223))</f>
+        <v>147</v>
       </c>
       <c r="B223" s="70"/>
       <c r="C223" s="30" t="s">
@@ -7496,7 +7682,7 @@
       <c r="G223" s="34"/>
     </row>
     <row r="224" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="219" t="s">
+      <c r="A224" s="151" t="s">
         <v>423</v>
       </c>
       <c r="B224" s="82"/>
@@ -7520,22 +7706,22 @@
       <c r="B226" s="82"/>
       <c r="C226" s="81"/>
       <c r="D226" s="81"/>
-      <c r="E226" s="203" t="s">
+      <c r="E226" s="213" t="s">
         <v>422</v>
       </c>
-      <c r="F226" s="204"/>
-      <c r="G226" s="205"/>
+      <c r="F226" s="214"/>
+      <c r="G226" s="215"/>
     </row>
     <row r="227" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A227" s="81"/>
       <c r="B227" s="82"/>
       <c r="C227" s="81"/>
       <c r="D227" s="81"/>
-      <c r="E227" s="206" t="s">
+      <c r="E227" s="216" t="s">
         <v>421</v>
       </c>
-      <c r="F227" s="207"/>
-      <c r="G227" s="208"/>
+      <c r="F227" s="217"/>
+      <c r="G227" s="218"/>
     </row>
     <row r="228" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A228" s="81"/>
@@ -7627,201 +7813,264 @@
       <c r="F237" s="83"/>
       <c r="G237" s="84"/>
     </row>
-    <row r="238" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A238" s="153" t="s">
+    <row r="238" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A238" s="81"/>
+      <c r="B238" s="82"/>
+      <c r="C238" s="81"/>
+      <c r="D238" s="81"/>
+      <c r="E238" s="83"/>
+      <c r="F238" s="83"/>
+      <c r="G238" s="84"/>
+    </row>
+    <row r="239" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A239" s="81"/>
+      <c r="B239" s="82"/>
+      <c r="C239" s="81"/>
+      <c r="D239" s="81"/>
+      <c r="E239" s="83"/>
+      <c r="F239" s="83"/>
+      <c r="G239" s="84"/>
+    </row>
+    <row r="240" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A240" s="81"/>
+      <c r="B240" s="82"/>
+      <c r="C240" s="81"/>
+      <c r="D240" s="81"/>
+      <c r="E240" s="83"/>
+      <c r="F240" s="83"/>
+      <c r="G240" s="84"/>
+    </row>
+    <row r="241" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A241" s="81"/>
+      <c r="B241" s="82"/>
+      <c r="C241" s="81"/>
+      <c r="D241" s="81"/>
+      <c r="E241" s="83"/>
+      <c r="F241" s="83"/>
+      <c r="G241" s="84"/>
+    </row>
+    <row r="242" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A242" s="81"/>
+      <c r="B242" s="82"/>
+      <c r="C242" s="81"/>
+      <c r="D242" s="81"/>
+      <c r="E242" s="83"/>
+      <c r="F242" s="83"/>
+      <c r="G242" s="84"/>
+    </row>
+    <row r="243" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A243" s="81"/>
+      <c r="B243" s="82"/>
+      <c r="C243" s="81"/>
+      <c r="D243" s="81"/>
+      <c r="E243" s="83"/>
+      <c r="F243" s="83"/>
+      <c r="G243" s="84"/>
+    </row>
+    <row r="244" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A244" s="81"/>
+      <c r="B244" s="82"/>
+      <c r="C244" s="81"/>
+      <c r="D244" s="81"/>
+      <c r="E244" s="83"/>
+      <c r="F244" s="83"/>
+      <c r="G244" s="84"/>
+    </row>
+    <row r="245" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A245" s="219" t="s">
         <v>26</v>
       </c>
-      <c r="B238" s="153"/>
-      <c r="C238" s="153"/>
-      <c r="D238" s="153"/>
-      <c r="E238" s="24"/>
-      <c r="F238" s="24"/>
-      <c r="G238" s="85"/>
-    </row>
-    <row r="239" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A239" s="86"/>
-      <c r="B239" s="151" t="s">
-        <v>261</v>
-      </c>
-      <c r="C239" s="151"/>
-      <c r="D239" s="151"/>
-      <c r="E239" s="151"/>
-      <c r="F239" s="151"/>
-      <c r="G239" s="151"/>
-    </row>
-    <row r="240" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A240" s="86"/>
-      <c r="B240" s="151" t="s">
-        <v>408</v>
-      </c>
-      <c r="C240" s="151"/>
-      <c r="D240" s="151"/>
-      <c r="E240" s="151"/>
-      <c r="F240" s="151"/>
-      <c r="G240" s="151"/>
-    </row>
-    <row r="241" spans="1:7" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="87"/>
-      <c r="B241" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="C241" s="151"/>
-      <c r="D241" s="151"/>
-      <c r="E241" s="151"/>
-      <c r="F241" s="151"/>
-      <c r="G241" s="151"/>
-    </row>
-    <row r="242" spans="1:7" s="15" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="88"/>
-      <c r="B242" s="152" t="s">
-        <v>28</v>
-      </c>
-      <c r="C242" s="152"/>
-      <c r="D242" s="152"/>
-      <c r="E242" s="152"/>
-      <c r="F242" s="152"/>
-      <c r="G242" s="152"/>
-    </row>
-    <row r="243" spans="1:7" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="85"/>
-      <c r="B243" s="151" t="s">
-        <v>29</v>
-      </c>
-      <c r="C243" s="151"/>
-      <c r="D243" s="151"/>
-      <c r="E243" s="151"/>
-      <c r="F243" s="151"/>
-      <c r="G243" s="151"/>
-    </row>
-    <row r="244" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A244" s="85"/>
-      <c r="B244" s="87" t="s">
-        <v>30</v>
-      </c>
-      <c r="C244" s="87"/>
-      <c r="D244" s="89"/>
-      <c r="E244" s="24"/>
-      <c r="F244" s="24"/>
-      <c r="G244" s="21"/>
-    </row>
-    <row r="245" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A245" s="85"/>
-      <c r="B245" s="87" t="s">
-        <v>31</v>
-      </c>
-      <c r="C245" s="87"/>
-      <c r="D245" s="89"/>
+      <c r="B245" s="219"/>
+      <c r="C245" s="219"/>
+      <c r="D245" s="219"/>
       <c r="E245" s="24"/>
       <c r="F245" s="24"/>
-      <c r="G245" s="21"/>
-    </row>
-    <row r="246" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A246" s="91" t="s">
+      <c r="G245" s="85"/>
+    </row>
+    <row r="246" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A246" s="86"/>
+      <c r="B246" s="206" t="s">
+        <v>261</v>
+      </c>
+      <c r="C246" s="206"/>
+      <c r="D246" s="206"/>
+      <c r="E246" s="206"/>
+      <c r="F246" s="206"/>
+      <c r="G246" s="206"/>
+    </row>
+    <row r="247" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A247" s="86"/>
+      <c r="B247" s="206" t="s">
+        <v>408</v>
+      </c>
+      <c r="C247" s="206"/>
+      <c r="D247" s="206"/>
+      <c r="E247" s="206"/>
+      <c r="F247" s="206"/>
+      <c r="G247" s="206"/>
+    </row>
+    <row r="248" spans="1:7" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="87"/>
+      <c r="B248" s="206" t="s">
+        <v>27</v>
+      </c>
+      <c r="C248" s="206"/>
+      <c r="D248" s="206"/>
+      <c r="E248" s="206"/>
+      <c r="F248" s="206"/>
+      <c r="G248" s="206"/>
+    </row>
+    <row r="249" spans="1:7" s="15" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="88"/>
+      <c r="B249" s="220" t="s">
+        <v>28</v>
+      </c>
+      <c r="C249" s="220"/>
+      <c r="D249" s="220"/>
+      <c r="E249" s="220"/>
+      <c r="F249" s="220"/>
+      <c r="G249" s="220"/>
+    </row>
+    <row r="250" spans="1:7" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="85"/>
+      <c r="B250" s="206" t="s">
+        <v>29</v>
+      </c>
+      <c r="C250" s="206"/>
+      <c r="D250" s="206"/>
+      <c r="E250" s="206"/>
+      <c r="F250" s="206"/>
+      <c r="G250" s="206"/>
+    </row>
+    <row r="251" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A251" s="85"/>
+      <c r="B251" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="C251" s="87"/>
+      <c r="D251" s="89"/>
+      <c r="E251" s="24"/>
+      <c r="F251" s="24"/>
+      <c r="G251" s="21"/>
+    </row>
+    <row r="252" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A252" s="85"/>
+      <c r="B252" s="87" t="s">
+        <v>31</v>
+      </c>
+      <c r="C252" s="87"/>
+      <c r="D252" s="89"/>
+      <c r="E252" s="24"/>
+      <c r="F252" s="24"/>
+      <c r="G252" s="21"/>
+    </row>
+    <row r="253" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A253" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="B246" s="92"/>
-      <c r="C246" s="92"/>
-      <c r="D246" s="92"/>
-      <c r="E246" s="107"/>
-      <c r="F246" s="107"/>
-      <c r="G246" s="90"/>
-    </row>
-    <row r="247" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A247" s="85"/>
-      <c r="B247" s="21" t="s">
+      <c r="B253" s="92"/>
+      <c r="C253" s="92"/>
+      <c r="D253" s="92"/>
+      <c r="E253" s="107"/>
+      <c r="F253" s="107"/>
+      <c r="G253" s="90"/>
+    </row>
+    <row r="254" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A254" s="85"/>
+      <c r="B254" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C247" s="21"/>
-      <c r="D247" s="89"/>
-      <c r="E247" s="93"/>
-      <c r="F247" s="93"/>
-      <c r="G247" s="21"/>
-    </row>
-    <row r="248" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A248" s="85"/>
-      <c r="B248" s="21" t="s">
+      <c r="C254" s="21"/>
+      <c r="D254" s="89"/>
+      <c r="E254" s="93"/>
+      <c r="F254" s="93"/>
+      <c r="G254" s="21"/>
+    </row>
+    <row r="255" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="85"/>
+      <c r="B255" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="C248" s="21"/>
-      <c r="D248" s="89"/>
-      <c r="E248" s="93"/>
-      <c r="F248" s="93"/>
-      <c r="G248" s="21"/>
-    </row>
-    <row r="249" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A249" s="85"/>
-      <c r="B249" s="21" t="s">
+      <c r="C255" s="21"/>
+      <c r="D255" s="89"/>
+      <c r="E255" s="93"/>
+      <c r="F255" s="93"/>
+      <c r="G255" s="21"/>
+    </row>
+    <row r="256" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A256" s="85"/>
+      <c r="B256" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C249" s="21"/>
-      <c r="D249" s="89"/>
-      <c r="E249" s="93"/>
-      <c r="F249" s="93"/>
-      <c r="G249" s="21"/>
+      <c r="C256" s="21"/>
+      <c r="D256" s="89"/>
+      <c r="E256" s="93"/>
+      <c r="F256" s="93"/>
+      <c r="G256" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
-    <mergeCell ref="A238:D238"/>
-    <mergeCell ref="B239:G239"/>
-    <mergeCell ref="B240:G240"/>
-    <mergeCell ref="B241:G241"/>
-    <mergeCell ref="B242:G242"/>
-    <mergeCell ref="B243:G243"/>
+  <mergeCells count="72">
+    <mergeCell ref="G188:G189"/>
+    <mergeCell ref="A194:D194"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A204:D204"/>
+    <mergeCell ref="B250:G250"/>
     <mergeCell ref="A214:D214"/>
     <mergeCell ref="E215:E218"/>
     <mergeCell ref="F215:F218"/>
     <mergeCell ref="A219:D219"/>
     <mergeCell ref="E226:G226"/>
     <mergeCell ref="E227:G227"/>
+    <mergeCell ref="A245:D245"/>
+    <mergeCell ref="B246:G246"/>
+    <mergeCell ref="B247:G247"/>
+    <mergeCell ref="B248:G248"/>
+    <mergeCell ref="B249:G249"/>
+    <mergeCell ref="A210:D210"/>
+    <mergeCell ref="B143:B148"/>
+    <mergeCell ref="B149:B178"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="A183:D183"/>
     <mergeCell ref="A186:D186"/>
-    <mergeCell ref="G188:G189"/>
-    <mergeCell ref="A194:D194"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A204:D204"/>
-    <mergeCell ref="A210:D210"/>
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B148:B177"/>
-    <mergeCell ref="A178:D178"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="A183:D183"/>
     <mergeCell ref="G184:G185"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="B113:B126"/>
-    <mergeCell ref="A127:D127"/>
-    <mergeCell ref="A130:D130"/>
-    <mergeCell ref="B131:B135"/>
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A93:D93"/>
-    <mergeCell ref="B94:B101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="A107:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B92"/>
-    <mergeCell ref="D89:D90"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="G66:G68"/>
-    <mergeCell ref="B69:B72"/>
-    <mergeCell ref="G70:G72"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="B114:B127"/>
+    <mergeCell ref="A128:D128"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="B132:B136"/>
+    <mergeCell ref="B137:B142"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="G77:G78"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="B80:B89"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="B95:B102"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="B105:B107"/>
+    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="H15:H20"/>
+    <mergeCell ref="I15:I20"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="E26:E27"/>
     <mergeCell ref="B29:B32"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="D41:D42"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="G15:G20"/>
-    <mergeCell ref="H15:H20"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I41:I43"/>
     <mergeCell ref="D1:G5"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="B9:G9"/>
@@ -7830,15 +8079,23 @@
     <mergeCell ref="A15:A20"/>
     <mergeCell ref="B15:B20"/>
     <mergeCell ref="C15:C20"/>
+    <mergeCell ref="F15:F20"/>
+    <mergeCell ref="G15:G20"/>
     <mergeCell ref="E15:E20"/>
-    <mergeCell ref="F15:F20"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="C1:C47 C49:C1048576">
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C48">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="49" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -7866,48 +8123,48 @@
       <c r="A1" s="20"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
-      <c r="D1" s="179" t="s">
+      <c r="D1" s="158" t="s">
         <v>307</v>
       </c>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
-      <c r="D2" s="180"/>
-      <c r="E2" s="180"/>
-      <c r="F2" s="180"/>
-      <c r="G2" s="180"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
-      <c r="D3" s="180"/>
-      <c r="E3" s="180"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="180"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
-      <c r="D4" s="180"/>
-      <c r="E4" s="180"/>
-      <c r="F4" s="180"/>
-      <c r="G4" s="180"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
-      <c r="F5" s="180"/>
-      <c r="G5" s="180"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="21"/>
@@ -7919,15 +8176,15 @@
       <c r="G6" s="21"/>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="160" t="s">
         <v>409</v>
       </c>
-      <c r="B7" s="181"/>
-      <c r="C7" s="181"/>
-      <c r="D7" s="181"/>
-      <c r="E7" s="181"/>
-      <c r="F7" s="181"/>
-      <c r="G7" s="181"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -7948,41 +8205,41 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="26"/>
-      <c r="B9" s="182" t="s">
+      <c r="B9" s="161" t="s">
         <v>411</v>
       </c>
-      <c r="C9" s="182"/>
-      <c r="D9" s="182"/>
-      <c r="E9" s="182"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="182"/>
+      <c r="C9" s="161"/>
+      <c r="D9" s="161"/>
+      <c r="E9" s="161"/>
+      <c r="F9" s="161"/>
+      <c r="G9" s="161"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="183" t="s">
+      <c r="A10" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="184"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="184"/>
-      <c r="E10" s="184"/>
-      <c r="F10" s="184"/>
-      <c r="G10" s="185"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="163"/>
+      <c r="G10" s="164"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="186"/>
-      <c r="B11" s="187"/>
-      <c r="C11" s="187"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="187"/>
-      <c r="F11" s="187"/>
-      <c r="G11" s="188"/>
+      <c r="A11" s="165"/>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="167"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
@@ -8003,10 +8260,10 @@
       <c r="A13" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="B13" s="189" t="s">
+      <c r="B13" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="189"/>
+      <c r="C13" s="168"/>
       <c r="D13" s="27" t="s">
         <v>3</v>
       </c>
@@ -8043,94 +8300,94 @@
       <c r="H14" s="141"/>
     </row>
     <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="190">
+      <c r="A15" s="153">
         <f>IF(LEN(C15)=0,"",COUNTA($C$15:C15))</f>
         <v>1</v>
       </c>
-      <c r="B15" s="177" t="s">
+      <c r="B15" s="154" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="191" t="s">
+      <c r="C15" s="155" t="s">
         <v>320</v>
       </c>
       <c r="D15" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="193">
+      <c r="E15" s="156">
         <v>150000</v>
       </c>
-      <c r="F15" s="198" t="s">
+      <c r="F15" s="157" t="s">
         <v>425</v>
       </c>
-      <c r="G15" s="198" t="s">
+      <c r="G15" s="157" t="s">
         <v>425</v>
       </c>
-      <c r="H15" s="194"/>
+      <c r="H15" s="171"/>
       <c r="I15" s="116"/>
     </row>
     <row r="16" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="190"/>
-      <c r="B16" s="177"/>
-      <c r="C16" s="191"/>
+      <c r="A16" s="153"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="155"/>
       <c r="D16" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="193"/>
-      <c r="F16" s="198"/>
-      <c r="G16" s="198"/>
-      <c r="H16" s="194"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="157"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="171"/>
       <c r="I16" s="116"/>
     </row>
     <row r="17" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A17" s="190"/>
-      <c r="B17" s="177"/>
-      <c r="C17" s="191"/>
+      <c r="A17" s="153"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="155"/>
       <c r="D17" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="193"/>
-      <c r="F17" s="198"/>
-      <c r="G17" s="198"/>
-      <c r="H17" s="194"/>
+      <c r="E17" s="156"/>
+      <c r="F17" s="157"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="171"/>
       <c r="I17" s="116"/>
     </row>
     <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="190"/>
-      <c r="B18" s="177"/>
-      <c r="C18" s="191"/>
+      <c r="A18" s="153"/>
+      <c r="B18" s="154"/>
+      <c r="C18" s="155"/>
       <c r="D18" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="193"/>
-      <c r="F18" s="198"/>
-      <c r="G18" s="198"/>
-      <c r="H18" s="194"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="157"/>
+      <c r="H18" s="171"/>
       <c r="I18" s="10"/>
     </row>
     <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="190"/>
-      <c r="B19" s="177"/>
-      <c r="C19" s="191"/>
+      <c r="A19" s="153"/>
+      <c r="B19" s="154"/>
+      <c r="C19" s="155"/>
       <c r="D19" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="E19" s="193"/>
-      <c r="F19" s="198"/>
-      <c r="G19" s="198"/>
-      <c r="H19" s="194"/>
+      <c r="E19" s="156"/>
+      <c r="F19" s="157"/>
+      <c r="G19" s="157"/>
+      <c r="H19" s="171"/>
       <c r="I19" s="10"/>
     </row>
     <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="190"/>
-      <c r="B20" s="177"/>
-      <c r="C20" s="191"/>
+      <c r="A20" s="153"/>
+      <c r="B20" s="154"/>
+      <c r="C20" s="155"/>
       <c r="D20" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="193"/>
-      <c r="F20" s="198"/>
-      <c r="G20" s="198"/>
-      <c r="H20" s="194"/>
+      <c r="E20" s="156"/>
+      <c r="F20" s="157"/>
+      <c r="G20" s="157"/>
+      <c r="H20" s="171"/>
       <c r="I20" s="10"/>
     </row>
     <row r="21" spans="1:9" ht="33" x14ac:dyDescent="0.25">
@@ -8265,7 +8522,7 @@
         <f>IF(LEN(C26)=0,"",COUNTA($C$15:C26))</f>
         <v>7</v>
       </c>
-      <c r="B26" s="177" t="s">
+      <c r="B26" s="154" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="35" t="s">
@@ -8274,16 +8531,16 @@
       <c r="D26" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="195">
+      <c r="E26" s="172">
         <v>50000</v>
       </c>
-      <c r="F26" s="195">
+      <c r="F26" s="172">
         <v>50000</v>
       </c>
-      <c r="G26" s="195">
+      <c r="G26" s="172">
         <v>50000</v>
       </c>
-      <c r="H26" s="197" t="s">
+      <c r="H26" s="174" t="s">
         <v>372</v>
       </c>
       <c r="I26" s="10"/>
@@ -8293,17 +8550,17 @@
         <f>IF(LEN(C27)=0,"",COUNTA($C$15:C27))</f>
         <v>8</v>
       </c>
-      <c r="B27" s="177"/>
+      <c r="B27" s="154"/>
       <c r="C27" s="35" t="s">
         <v>41</v>
       </c>
       <c r="D27" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="196"/>
-      <c r="F27" s="196"/>
-      <c r="G27" s="196"/>
-      <c r="H27" s="197"/>
+      <c r="E27" s="173"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="174"/>
       <c r="I27" s="10"/>
     </row>
     <row r="28" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
@@ -8337,7 +8594,7 @@
         <f>IF(LEN(C29)=0,"",COUNTA($C$15:C29))</f>
         <v>10</v>
       </c>
-      <c r="B29" s="192" t="s">
+      <c r="B29" s="175" t="s">
         <v>58</v>
       </c>
       <c r="C29" s="35" t="s">
@@ -8363,7 +8620,7 @@
         <f>IF(LEN(C30)=0,"",COUNTA($C$15:C30))</f>
         <v>11</v>
       </c>
-      <c r="B30" s="192"/>
+      <c r="B30" s="175"/>
       <c r="C30" s="38" t="s">
         <v>61</v>
       </c>
@@ -8387,7 +8644,7 @@
         <f>IF(LEN(C31)=0,"",COUNTA($C$15:C31))</f>
         <v>12</v>
       </c>
-      <c r="B31" s="192"/>
+      <c r="B31" s="175"/>
       <c r="C31" s="38" t="s">
         <v>65</v>
       </c>
@@ -8411,7 +8668,7 @@
         <f>IF(LEN(C32)=0,"",COUNTA($C$15:C32))</f>
         <v>13</v>
       </c>
-      <c r="B32" s="192"/>
+      <c r="B32" s="175"/>
       <c r="C32" s="38" t="s">
         <v>67</v>
       </c>
@@ -8483,7 +8740,7 @@
         <f>IF(LEN(C35)=0,"",COUNTA($C$15:C35))</f>
         <v>16</v>
       </c>
-      <c r="B35" s="177" t="s">
+      <c r="B35" s="154" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="38" t="s">
@@ -8511,7 +8768,7 @@
         <f>IF(LEN(C36)=0,"",COUNTA($C$15:C36))</f>
         <v>17</v>
       </c>
-      <c r="B36" s="177"/>
+      <c r="B36" s="154"/>
       <c r="C36" s="38" t="s">
         <v>269</v>
       </c>
@@ -8639,7 +8896,7 @@
         <f>IF(LEN(C41)=0,"",COUNTA($C$15:C41))</f>
         <v>22</v>
       </c>
-      <c r="B41" s="173" t="s">
+      <c r="B41" s="176" t="s">
         <v>87</v>
       </c>
       <c r="C41" s="127" t="s">
@@ -8657,7 +8914,7 @@
       <c r="G41" s="121">
         <v>120000</v>
       </c>
-      <c r="H41" s="199" t="s">
+      <c r="H41" s="179" t="s">
         <v>371</v>
       </c>
       <c r="I41" s="11"/>
@@ -8667,7 +8924,7 @@
         <f>IF(LEN(C42)=0,"",COUNTA($C$15:C42))</f>
         <v>23</v>
       </c>
-      <c r="B42" s="174"/>
+      <c r="B42" s="177"/>
       <c r="C42" s="127" t="s">
         <v>88</v>
       </c>
@@ -8681,7 +8938,7 @@
       <c r="G42" s="121">
         <v>120000</v>
       </c>
-      <c r="H42" s="157"/>
+      <c r="H42" s="180"/>
       <c r="I42" s="11"/>
     </row>
     <row r="43" spans="1:11" s="12" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8689,7 +8946,7 @@
         <f>IF(LEN(C43)=0,"",COUNTA($C$15:C43))</f>
         <v>24</v>
       </c>
-      <c r="B43" s="174"/>
+      <c r="B43" s="177"/>
       <c r="C43" s="127" t="s">
         <v>89</v>
       </c>
@@ -8703,7 +8960,7 @@
       <c r="G43" s="145" t="s">
         <v>425</v>
       </c>
-      <c r="H43" s="158"/>
+      <c r="H43" s="181"/>
       <c r="I43" s="11"/>
     </row>
     <row r="44" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
@@ -8711,7 +8968,7 @@
         <f>IF(LEN(C44)=0,"",COUNTA($C$15:C44))</f>
         <v>25</v>
       </c>
-      <c r="B44" s="209"/>
+      <c r="B44" s="169"/>
       <c r="C44" s="30" t="s">
         <v>318</v>
       </c>
@@ -8735,7 +8992,7 @@
         <f>IF(LEN(C45)=0,"",COUNTA($C$15:C45))</f>
         <v>26</v>
       </c>
-      <c r="B45" s="209"/>
+      <c r="B45" s="169"/>
       <c r="C45" s="30" t="s">
         <v>319</v>
       </c>
@@ -8759,7 +9016,7 @@
         <f>IF(LEN(C46)=0,"",COUNTA($C$15:C46))</f>
         <v>27</v>
       </c>
-      <c r="B46" s="210"/>
+      <c r="B46" s="170"/>
       <c r="C46" s="30" t="s">
         <v>33</v>
       </c>
@@ -8995,12 +9252,12 @@
       <c r="H55" s="141"/>
     </row>
     <row r="56" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="211" t="s">
+      <c r="A56" s="182" t="s">
         <v>25</v>
       </c>
-      <c r="B56" s="212"/>
-      <c r="C56" s="212"/>
-      <c r="D56" s="213"/>
+      <c r="B56" s="183"/>
+      <c r="C56" s="183"/>
+      <c r="D56" s="184"/>
       <c r="E56" s="112">
         <f>SUM(E15:E55)</f>
         <v>2158000</v>
@@ -9049,10 +9306,10 @@
       <c r="A60" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="B60" s="211" t="s">
+      <c r="B60" s="182" t="s">
         <v>2</v>
       </c>
-      <c r="C60" s="213"/>
+      <c r="C60" s="184"/>
       <c r="D60" s="53" t="s">
         <v>3</v>
       </c>
@@ -9172,7 +9429,7 @@
         <f>IF(LEN(C66)=0,"",COUNTA($C$62:C66))</f>
         <v>5</v>
       </c>
-      <c r="B66" s="169" t="s">
+      <c r="B66" s="185" t="s">
         <v>272</v>
       </c>
       <c r="C66" s="29" t="s">
@@ -9188,7 +9445,7 @@
         <f t="shared" si="0"/>
         <v>55800</v>
       </c>
-      <c r="G66" s="199" t="s">
+      <c r="G66" s="179" t="s">
         <v>370</v>
       </c>
     </row>
@@ -9197,7 +9454,7 @@
         <f>IF(LEN(C67)=0,"",COUNTA($C$62:C67))</f>
         <v>6</v>
       </c>
-      <c r="B67" s="170"/>
+      <c r="B67" s="186"/>
       <c r="C67" s="29" t="s">
         <v>192</v>
       </c>
@@ -9211,14 +9468,14 @@
         <f t="shared" si="0"/>
         <v>148500</v>
       </c>
-      <c r="G67" s="157"/>
+      <c r="G67" s="180"/>
     </row>
     <row r="68" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A68" s="31">
         <f>IF(LEN(C68)=0,"",COUNTA($C$62:C68))</f>
         <v>7</v>
       </c>
-      <c r="B68" s="171"/>
+      <c r="B68" s="187"/>
       <c r="C68" s="29" t="s">
         <v>197</v>
       </c>
@@ -9232,14 +9489,14 @@
         <f t="shared" si="0"/>
         <v>104400</v>
       </c>
-      <c r="G68" s="158"/>
+      <c r="G68" s="181"/>
     </row>
     <row r="69" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A69" s="31">
         <f>IF(LEN(C69)=0,"",COUNTA($C$62:C69))</f>
         <v>8</v>
       </c>
-      <c r="B69" s="169" t="s">
+      <c r="B69" s="185" t="s">
         <v>267</v>
       </c>
       <c r="C69" s="29" t="s">
@@ -9262,7 +9519,7 @@
         <f>IF(LEN(C70)=0,"",COUNTA($C$62:C70))</f>
         <v>9</v>
       </c>
-      <c r="B70" s="170"/>
+      <c r="B70" s="186"/>
       <c r="C70" s="29" t="s">
         <v>264</v>
       </c>
@@ -9276,7 +9533,7 @@
         <f t="shared" si="0"/>
         <v>117000</v>
       </c>
-      <c r="G70" s="199" t="s">
+      <c r="G70" s="179" t="s">
         <v>370</v>
       </c>
     </row>
@@ -9285,7 +9542,7 @@
         <f>IF(LEN(C71)=0,"",COUNTA($C$62:C71))</f>
         <v>10</v>
       </c>
-      <c r="B71" s="170"/>
+      <c r="B71" s="186"/>
       <c r="C71" s="29" t="s">
         <v>265</v>
       </c>
@@ -9299,14 +9556,14 @@
         <f t="shared" si="0"/>
         <v>108000</v>
       </c>
-      <c r="G71" s="157"/>
+      <c r="G71" s="180"/>
     </row>
     <row r="72" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="31">
         <f>IF(LEN(C72)=0,"",COUNTA($C$62:C72))</f>
         <v>11</v>
       </c>
-      <c r="B72" s="171"/>
+      <c r="B72" s="187"/>
       <c r="C72" s="29" t="s">
         <v>266</v>
       </c>
@@ -9320,7 +9577,7 @@
         <f t="shared" si="0"/>
         <v>253800</v>
       </c>
-      <c r="G72" s="158"/>
+      <c r="G72" s="181"/>
     </row>
     <row r="73" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="31">
@@ -9394,7 +9651,7 @@
         <f>IF(LEN(C76)=0,"",COUNTA($C$62:C76))</f>
         <v>15</v>
       </c>
-      <c r="B76" s="216" t="s">
+      <c r="B76" s="188" t="s">
         <v>200</v>
       </c>
       <c r="C76" s="29" t="s">
@@ -9410,7 +9667,7 @@
         <f t="shared" si="0"/>
         <v>27000</v>
       </c>
-      <c r="G76" s="217" t="s">
+      <c r="G76" s="189" t="s">
         <v>373</v>
       </c>
     </row>
@@ -9419,7 +9676,7 @@
         <f>IF(LEN(C77)=0,"",COUNTA($C$62:C77))</f>
         <v>16</v>
       </c>
-      <c r="B77" s="216"/>
+      <c r="B77" s="188"/>
       <c r="C77" s="29" t="s">
         <v>273</v>
       </c>
@@ -9433,15 +9690,15 @@
         <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="G77" s="218"/>
+      <c r="G77" s="190"/>
     </row>
     <row r="78" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="159" t="s">
+      <c r="A78" s="191" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="160"/>
-      <c r="C78" s="160"/>
-      <c r="D78" s="161"/>
+      <c r="B78" s="192"/>
+      <c r="C78" s="192"/>
+      <c r="D78" s="193"/>
       <c r="E78" s="58"/>
       <c r="F78" s="58"/>
       <c r="G78" s="59"/>
@@ -9451,7 +9708,7 @@
         <f>IF(LEN(C79)=0,"",COUNTA($C$62:C79))</f>
         <v>17</v>
       </c>
-      <c r="B79" s="173" t="s">
+      <c r="B79" s="176" t="s">
         <v>255</v>
       </c>
       <c r="C79" s="65" t="s">
@@ -9474,7 +9731,7 @@
         <f>IF(LEN(C80)=0,"",COUNTA($C$62:C80))</f>
         <v>18</v>
       </c>
-      <c r="B80" s="174"/>
+      <c r="B80" s="177"/>
       <c r="C80" s="65" t="s">
         <v>80</v>
       </c>
@@ -9495,7 +9752,7 @@
         <f>IF(LEN(C81)=0,"",COUNTA($C$62:C81))</f>
         <v>19</v>
       </c>
-      <c r="B81" s="174"/>
+      <c r="B81" s="177"/>
       <c r="C81" s="65" t="s">
         <v>82</v>
       </c>
@@ -9516,7 +9773,7 @@
         <f>IF(LEN(C82)=0,"",COUNTA($C$62:C82))</f>
         <v>20</v>
       </c>
-      <c r="B82" s="174"/>
+      <c r="B82" s="177"/>
       <c r="C82" s="65" t="s">
         <v>90</v>
       </c>
@@ -9537,7 +9794,7 @@
         <f>IF(LEN(C83)=0,"",COUNTA($C$62:C83))</f>
         <v>21</v>
       </c>
-      <c r="B83" s="174"/>
+      <c r="B83" s="177"/>
       <c r="C83" s="65" t="s">
         <v>79</v>
       </c>
@@ -9560,7 +9817,7 @@
         <f>IF(LEN(C84)=0,"",COUNTA($C$62:C84))</f>
         <v>22</v>
       </c>
-      <c r="B84" s="174"/>
+      <c r="B84" s="177"/>
       <c r="C84" s="67" t="s">
         <v>229</v>
       </c>
@@ -9581,7 +9838,7 @@
         <f>IF(LEN(C85)=0,"",COUNTA($C$62:C85))</f>
         <v>23</v>
       </c>
-      <c r="B85" s="174"/>
+      <c r="B85" s="177"/>
       <c r="C85" s="65" t="s">
         <v>72</v>
       </c>
@@ -9602,7 +9859,7 @@
         <f>IF(LEN(C86)=0,"",COUNTA($C$62:C86))</f>
         <v>24</v>
       </c>
-      <c r="B86" s="174"/>
+      <c r="B86" s="177"/>
       <c r="C86" s="65" t="s">
         <v>74</v>
       </c>
@@ -9623,7 +9880,7 @@
         <f>IF(LEN(C87)=0,"",COUNTA($C$62:C87))</f>
         <v>25</v>
       </c>
-      <c r="B87" s="174"/>
+      <c r="B87" s="177"/>
       <c r="C87" s="65" t="s">
         <v>84</v>
       </c>
@@ -9644,7 +9901,7 @@
         <f>IF(LEN(C88)=0,"",COUNTA($C$62:C88))</f>
         <v>26</v>
       </c>
-      <c r="B88" s="175"/>
+      <c r="B88" s="194"/>
       <c r="C88" s="65" t="s">
         <v>92</v>
       </c>
@@ -9665,13 +9922,13 @@
         <f>IF(LEN(C89)=0,"",COUNTA($C$62:C89))</f>
         <v>27</v>
       </c>
-      <c r="B89" s="173" t="s">
+      <c r="B89" s="176" t="s">
         <v>388</v>
       </c>
       <c r="C89" s="65" t="s">
         <v>389</v>
       </c>
-      <c r="D89" s="214" t="s">
+      <c r="D89" s="195" t="s">
         <v>391</v>
       </c>
       <c r="E89" s="33">
@@ -9688,11 +9945,11 @@
         <f>IF(LEN(C90)=0,"",COUNTA($C$62:C90))</f>
         <v>28</v>
       </c>
-      <c r="B90" s="174"/>
+      <c r="B90" s="177"/>
       <c r="C90" s="65" t="s">
         <v>390</v>
       </c>
-      <c r="D90" s="215"/>
+      <c r="D90" s="196"/>
       <c r="E90" s="33">
         <v>323000</v>
       </c>
@@ -9707,7 +9964,7 @@
         <f>IF(LEN(C91)=0,"",COUNTA($C$62:C91))</f>
         <v>29</v>
       </c>
-      <c r="B91" s="174"/>
+      <c r="B91" s="177"/>
       <c r="C91" s="65" t="s">
         <v>393</v>
       </c>
@@ -9728,7 +9985,7 @@
         <f>IF(LEN(C92)=0,"",COUNTA($C$62:C92))</f>
         <v>30</v>
       </c>
-      <c r="B92" s="175"/>
+      <c r="B92" s="194"/>
       <c r="C92" s="65" t="s">
         <v>394</v>
       </c>
@@ -9745,12 +10002,12 @@
       <c r="G92" s="95"/>
     </row>
     <row r="93" spans="1:7" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="159" t="s">
+      <c r="A93" s="191" t="s">
         <v>202</v>
       </c>
-      <c r="B93" s="160"/>
-      <c r="C93" s="160"/>
-      <c r="D93" s="161"/>
+      <c r="B93" s="192"/>
+      <c r="C93" s="192"/>
+      <c r="D93" s="193"/>
       <c r="E93" s="58"/>
       <c r="F93" s="58"/>
       <c r="G93" s="59"/>
@@ -9760,7 +10017,7 @@
         <f>IF(LEN(C94)=0,"",COUNTA($C$62:C94))</f>
         <v>31</v>
       </c>
-      <c r="B94" s="176" t="s">
+      <c r="B94" s="197" t="s">
         <v>94</v>
       </c>
       <c r="C94" s="29" t="s">
@@ -9783,7 +10040,7 @@
         <f>IF(LEN(C95)=0,"",COUNTA($C$62:C95))</f>
         <v>32</v>
       </c>
-      <c r="B95" s="176"/>
+      <c r="B95" s="197"/>
       <c r="C95" s="29" t="s">
         <v>97</v>
       </c>
@@ -9804,7 +10061,7 @@
         <f>IF(LEN(C96)=0,"",COUNTA($C$62:C96))</f>
         <v>33</v>
       </c>
-      <c r="B96" s="176"/>
+      <c r="B96" s="197"/>
       <c r="C96" s="29" t="s">
         <v>99</v>
       </c>
@@ -9827,7 +10084,7 @@
         <f>IF(LEN(C97)=0,"",COUNTA($C$62:C97))</f>
         <v>34</v>
       </c>
-      <c r="B97" s="176"/>
+      <c r="B97" s="197"/>
       <c r="C97" s="29" t="s">
         <v>102</v>
       </c>
@@ -9850,7 +10107,7 @@
         <f>IF(LEN(C98)=0,"",COUNTA($C$62:C98))</f>
         <v>35</v>
       </c>
-      <c r="B98" s="176"/>
+      <c r="B98" s="197"/>
       <c r="C98" s="29" t="s">
         <v>396</v>
       </c>
@@ -9871,7 +10128,7 @@
         <f>IF(LEN(C99)=0,"",COUNTA($C$62:C99))</f>
         <v>36</v>
       </c>
-      <c r="B99" s="176"/>
+      <c r="B99" s="197"/>
       <c r="C99" s="29" t="s">
         <v>104</v>
       </c>
@@ -9894,7 +10151,7 @@
         <f>IF(LEN(C100)=0,"",COUNTA($C$62:C100))</f>
         <v>37</v>
       </c>
-      <c r="B100" s="176"/>
+      <c r="B100" s="197"/>
       <c r="C100" s="29" t="s">
         <v>107</v>
       </c>
@@ -9917,7 +10174,7 @@
         <f>IF(LEN(C101)=0,"",COUNTA($C$62:C101))</f>
         <v>38</v>
       </c>
-      <c r="B101" s="176"/>
+      <c r="B101" s="197"/>
       <c r="C101" s="29" t="s">
         <v>110</v>
       </c>
@@ -9940,7 +10197,7 @@
         <f>IF(LEN(C102)=0,"",COUNTA($C$62:C102))</f>
         <v>39</v>
       </c>
-      <c r="B102" s="176" t="s">
+      <c r="B102" s="197" t="s">
         <v>113</v>
       </c>
       <c r="C102" s="29" t="s">
@@ -9963,7 +10220,7 @@
         <f>IF(LEN(C103)=0,"",COUNTA($C$62:C103))</f>
         <v>40</v>
       </c>
-      <c r="B103" s="176"/>
+      <c r="B103" s="197"/>
       <c r="C103" s="29" t="s">
         <v>116</v>
       </c>
@@ -9984,7 +10241,7 @@
         <f>IF(LEN(C104)=0,"",COUNTA($C$62:C104))</f>
         <v>41</v>
       </c>
-      <c r="B104" s="165" t="s">
+      <c r="B104" s="198" t="s">
         <v>118</v>
       </c>
       <c r="C104" s="29" t="s">
@@ -10007,7 +10264,7 @@
         <f>IF(LEN(C105)=0,"",COUNTA($C$62:C105))</f>
         <v>42</v>
       </c>
-      <c r="B105" s="166"/>
+      <c r="B105" s="199"/>
       <c r="C105" s="29" t="s">
         <v>379</v>
       </c>
@@ -10028,7 +10285,7 @@
         <f>IF(LEN(C106)=0,"",COUNTA($C$62:C106))</f>
         <v>43</v>
       </c>
-      <c r="B106" s="167"/>
+      <c r="B106" s="200"/>
       <c r="C106" s="29" t="s">
         <v>122</v>
       </c>
@@ -10045,12 +10302,12 @@
       <c r="G106" s="34"/>
     </row>
     <row r="107" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="159" t="s">
+      <c r="A107" s="191" t="s">
         <v>256</v>
       </c>
-      <c r="B107" s="160"/>
-      <c r="C107" s="160"/>
-      <c r="D107" s="161"/>
+      <c r="B107" s="192"/>
+      <c r="C107" s="192"/>
+      <c r="D107" s="193"/>
       <c r="E107" s="69"/>
       <c r="F107" s="69"/>
       <c r="G107" s="59"/>
@@ -10060,7 +10317,7 @@
         <f>IF(LEN(C108)=0,"",COUNTA($C$62:C108))</f>
         <v>44</v>
       </c>
-      <c r="B108" s="169" t="s">
+      <c r="B108" s="185" t="s">
         <v>235</v>
       </c>
       <c r="C108" s="29" t="s">
@@ -10083,7 +10340,7 @@
         <f>IF(LEN(C109)=0,"",COUNTA($C$62:C109))</f>
         <v>45</v>
       </c>
-      <c r="B109" s="171"/>
+      <c r="B109" s="187"/>
       <c r="C109" s="29" t="s">
         <v>234</v>
       </c>
@@ -10104,7 +10361,7 @@
         <f>IF(LEN(C110)=0,"",COUNTA($C$62:C110))</f>
         <v>46</v>
       </c>
-      <c r="B110" s="165" t="s">
+      <c r="B110" s="198" t="s">
         <v>238</v>
       </c>
       <c r="C110" s="29" t="s">
@@ -10125,7 +10382,7 @@
         <f>IF(LEN(C111)=0,"",COUNTA($C$62:C111))</f>
         <v>47</v>
       </c>
-      <c r="B111" s="167"/>
+      <c r="B111" s="200"/>
       <c r="C111" s="29" t="s">
         <v>237</v>
       </c>
@@ -10167,7 +10424,7 @@
         <f>IF(LEN(C113)=0,"",COUNTA($C$62:C113))</f>
         <v>49</v>
       </c>
-      <c r="B113" s="165" t="s">
+      <c r="B113" s="198" t="s">
         <v>253</v>
       </c>
       <c r="C113" s="29" t="s">
@@ -10188,7 +10445,7 @@
         <f>IF(LEN(C114)=0,"",COUNTA($C$62:C114))</f>
         <v>50</v>
       </c>
-      <c r="B114" s="166"/>
+      <c r="B114" s="199"/>
       <c r="C114" s="29" t="s">
         <v>240</v>
       </c>
@@ -10207,7 +10464,7 @@
         <f>IF(LEN(C115)=0,"",COUNTA($C$62:C115))</f>
         <v>51</v>
       </c>
-      <c r="B115" s="166"/>
+      <c r="B115" s="199"/>
       <c r="C115" s="29" t="s">
         <v>241</v>
       </c>
@@ -10226,7 +10483,7 @@
         <f>IF(LEN(C116)=0,"",COUNTA($C$62:C116))</f>
         <v>52</v>
       </c>
-      <c r="B116" s="166"/>
+      <c r="B116" s="199"/>
       <c r="C116" s="29" t="s">
         <v>242</v>
       </c>
@@ -10245,7 +10502,7 @@
         <f>IF(LEN(C117)=0,"",COUNTA($C$62:C117))</f>
         <v>53</v>
       </c>
-      <c r="B117" s="166"/>
+      <c r="B117" s="199"/>
       <c r="C117" s="29" t="s">
         <v>243</v>
       </c>
@@ -10264,7 +10521,7 @@
         <f>IF(LEN(C118)=0,"",COUNTA($C$62:C118))</f>
         <v>54</v>
       </c>
-      <c r="B118" s="166"/>
+      <c r="B118" s="199"/>
       <c r="C118" s="29" t="s">
         <v>244</v>
       </c>
@@ -10283,7 +10540,7 @@
         <f>IF(LEN(C119)=0,"",COUNTA($C$62:C119))</f>
         <v>55</v>
       </c>
-      <c r="B119" s="166"/>
+      <c r="B119" s="199"/>
       <c r="C119" s="29" t="s">
         <v>245</v>
       </c>
@@ -10302,7 +10559,7 @@
         <f>IF(LEN(C120)=0,"",COUNTA($C$62:C120))</f>
         <v>56</v>
       </c>
-      <c r="B120" s="166"/>
+      <c r="B120" s="199"/>
       <c r="C120" s="29" t="s">
         <v>246</v>
       </c>
@@ -10321,7 +10578,7 @@
         <f>IF(LEN(C121)=0,"",COUNTA($C$62:C121))</f>
         <v>57</v>
       </c>
-      <c r="B121" s="166"/>
+      <c r="B121" s="199"/>
       <c r="C121" s="29" t="s">
         <v>247</v>
       </c>
@@ -10340,7 +10597,7 @@
         <f>IF(LEN(C122)=0,"",COUNTA($C$62:C122))</f>
         <v>58</v>
       </c>
-      <c r="B122" s="166"/>
+      <c r="B122" s="199"/>
       <c r="C122" s="29" t="s">
         <v>248</v>
       </c>
@@ -10359,7 +10616,7 @@
         <f>IF(LEN(C123)=0,"",COUNTA($C$62:C123))</f>
         <v>59</v>
       </c>
-      <c r="B123" s="166"/>
+      <c r="B123" s="199"/>
       <c r="C123" s="29" t="s">
         <v>249</v>
       </c>
@@ -10378,7 +10635,7 @@
         <f>IF(LEN(C124)=0,"",COUNTA($C$62:C124))</f>
         <v>60</v>
       </c>
-      <c r="B124" s="166"/>
+      <c r="B124" s="199"/>
       <c r="C124" s="29" t="s">
         <v>250</v>
       </c>
@@ -10397,7 +10654,7 @@
         <f>IF(LEN(C125)=0,"",COUNTA($C$62:C125))</f>
         <v>61</v>
       </c>
-      <c r="B125" s="166"/>
+      <c r="B125" s="199"/>
       <c r="C125" s="29" t="s">
         <v>251</v>
       </c>
@@ -10416,7 +10673,7 @@
         <f>IF(LEN(C126)=0,"",COUNTA($C$62:C126))</f>
         <v>62</v>
       </c>
-      <c r="B126" s="167"/>
+      <c r="B126" s="200"/>
       <c r="C126" s="29" t="s">
         <v>252</v>
       </c>
@@ -10431,12 +10688,12 @@
       <c r="G126" s="34"/>
     </row>
     <row r="127" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="159" t="s">
+      <c r="A127" s="191" t="s">
         <v>221</v>
       </c>
-      <c r="B127" s="160"/>
-      <c r="C127" s="160"/>
-      <c r="D127" s="161"/>
+      <c r="B127" s="192"/>
+      <c r="C127" s="192"/>
+      <c r="D127" s="193"/>
       <c r="E127" s="58"/>
       <c r="F127" s="58"/>
       <c r="G127" s="59"/>
@@ -10488,12 +10745,12 @@
       <c r="G129" s="34"/>
     </row>
     <row r="130" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="156" t="s">
+      <c r="A130" s="203" t="s">
         <v>257</v>
       </c>
-      <c r="B130" s="156"/>
-      <c r="C130" s="156"/>
-      <c r="D130" s="156"/>
+      <c r="B130" s="203"/>
+      <c r="C130" s="203"/>
+      <c r="D130" s="203"/>
       <c r="E130" s="69"/>
       <c r="F130" s="69"/>
       <c r="G130" s="59"/>
@@ -10503,7 +10760,7 @@
         <f>IF(LEN(C131)=0,"",COUNTA($C$62:C131))</f>
         <v>65</v>
       </c>
-      <c r="B131" s="168"/>
+      <c r="B131" s="204"/>
       <c r="C131" s="29" t="s">
         <v>398</v>
       </c>
@@ -10522,7 +10779,7 @@
         <f>IF(LEN(C132)=0,"",COUNTA($C$62:C132))</f>
         <v>66</v>
       </c>
-      <c r="B132" s="168"/>
+      <c r="B132" s="204"/>
       <c r="C132" s="29" t="s">
         <v>399</v>
       </c>
@@ -10541,7 +10798,7 @@
         <f>IF(LEN(C133)=0,"",COUNTA($C$62:C133))</f>
         <v>67</v>
       </c>
-      <c r="B133" s="168"/>
+      <c r="B133" s="204"/>
       <c r="C133" s="29" t="s">
         <v>400</v>
       </c>
@@ -10560,7 +10817,7 @@
         <f>IF(LEN(C134)=0,"",COUNTA($C$62:C134))</f>
         <v>68</v>
       </c>
-      <c r="B134" s="168"/>
+      <c r="B134" s="204"/>
       <c r="C134" s="30" t="s">
         <v>401</v>
       </c>
@@ -10581,7 +10838,7 @@
         <f>IF(LEN(C135)=0,"",COUNTA($C$62:C135))</f>
         <v>69</v>
       </c>
-      <c r="B135" s="168"/>
+      <c r="B135" s="204"/>
       <c r="C135" s="30" t="s">
         <v>134</v>
       </c>
@@ -10602,7 +10859,7 @@
         <f>IF(LEN(C136)=0,"",COUNTA($C$62:C136))</f>
         <v>70</v>
       </c>
-      <c r="B136" s="169" t="s">
+      <c r="B136" s="185" t="s">
         <v>277</v>
       </c>
       <c r="C136" s="29" t="s">
@@ -10625,7 +10882,7 @@
         <f>IF(LEN(C137)=0,"",COUNTA($C$62:C137))</f>
         <v>71</v>
       </c>
-      <c r="B137" s="170"/>
+      <c r="B137" s="186"/>
       <c r="C137" s="29" t="s">
         <v>139</v>
       </c>
@@ -10646,7 +10903,7 @@
         <f>IF(LEN(C138)=0,"",COUNTA($C$62:C138))</f>
         <v>72</v>
       </c>
-      <c r="B138" s="170"/>
+      <c r="B138" s="186"/>
       <c r="C138" s="29" t="s">
         <v>383</v>
       </c>
@@ -10667,7 +10924,7 @@
         <f>IF(LEN(C139)=0,"",COUNTA($C$62:C139))</f>
         <v>73</v>
       </c>
-      <c r="B139" s="170"/>
+      <c r="B139" s="186"/>
       <c r="C139" s="29" t="s">
         <v>385</v>
       </c>
@@ -10688,7 +10945,7 @@
         <f>IF(LEN(C140)=0,"",COUNTA($C$62:C140))</f>
         <v>74</v>
       </c>
-      <c r="B140" s="170"/>
+      <c r="B140" s="186"/>
       <c r="C140" s="29" t="s">
         <v>362</v>
       </c>
@@ -10709,7 +10966,7 @@
         <f>IF(LEN(C141)=0,"",COUNTA($C$62:C141))</f>
         <v>75</v>
       </c>
-      <c r="B141" s="171"/>
+      <c r="B141" s="187"/>
       <c r="C141" s="29" t="s">
         <v>141</v>
       </c>
@@ -10728,7 +10985,7 @@
         <f>IF(LEN(C142)=0,"",COUNTA($C$62:C142))</f>
         <v>76</v>
       </c>
-      <c r="B142" s="170" t="s">
+      <c r="B142" s="186" t="s">
         <v>278</v>
       </c>
       <c r="C142" s="29" t="s">
@@ -10749,7 +11006,7 @@
         <f>IF(LEN(C143)=0,"",COUNTA($C$62:C143))</f>
         <v>77</v>
       </c>
-      <c r="B143" s="170"/>
+      <c r="B143" s="186"/>
       <c r="C143" s="29" t="s">
         <v>147</v>
       </c>
@@ -10770,7 +11027,7 @@
         <f>IF(LEN(C144)=0,"",COUNTA($C$62:C144))</f>
         <v>78</v>
       </c>
-      <c r="B144" s="170"/>
+      <c r="B144" s="186"/>
       <c r="C144" s="29" t="s">
         <v>149</v>
       </c>
@@ -10791,7 +11048,7 @@
         <f>IF(LEN(C145)=0,"",COUNTA($C$62:C145))</f>
         <v>79</v>
       </c>
-      <c r="B145" s="170"/>
+      <c r="B145" s="186"/>
       <c r="C145" s="29" t="s">
         <v>151</v>
       </c>
@@ -10812,7 +11069,7 @@
         <f>IF(LEN(C146)=0,"",COUNTA($C$62:C146))</f>
         <v>80</v>
       </c>
-      <c r="B146" s="170"/>
+      <c r="B146" s="186"/>
       <c r="C146" s="29" t="s">
         <v>153</v>
       </c>
@@ -10833,7 +11090,7 @@
         <f>IF(LEN(C147)=0,"",COUNTA($C$62:C147))</f>
         <v>81</v>
       </c>
-      <c r="B147" s="170"/>
+      <c r="B147" s="186"/>
       <c r="C147" s="29" t="s">
         <v>154</v>
       </c>
@@ -10852,7 +11109,7 @@
         <f>IF(LEN(C148)=0,"",COUNTA($C$62:C148))</f>
         <v>82</v>
       </c>
-      <c r="B148" s="172" t="s">
+      <c r="B148" s="205" t="s">
         <v>299</v>
       </c>
       <c r="C148" s="29" t="s">
@@ -10877,7 +11134,7 @@
         <f>IF(LEN(C149)=0,"",COUNTA($C$62:C149))</f>
         <v>83</v>
       </c>
-      <c r="B149" s="172"/>
+      <c r="B149" s="205"/>
       <c r="C149" s="29" t="s">
         <v>335</v>
       </c>
@@ -10898,7 +11155,7 @@
         <f>IF(LEN(C150)=0,"",COUNTA($C$62:C150))</f>
         <v>84</v>
       </c>
-      <c r="B150" s="172"/>
+      <c r="B150" s="205"/>
       <c r="C150" s="29" t="s">
         <v>336</v>
       </c>
@@ -10921,7 +11178,7 @@
         <f>IF(LEN(C151)=0,"",COUNTA($C$62:C151))</f>
         <v>85</v>
       </c>
-      <c r="B151" s="172"/>
+      <c r="B151" s="205"/>
       <c r="C151" s="29" t="s">
         <v>337</v>
       </c>
@@ -10942,7 +11199,7 @@
         <f>IF(LEN(C152)=0,"",COUNTA($C$62:C152))</f>
         <v>86</v>
       </c>
-      <c r="B152" s="172"/>
+      <c r="B152" s="205"/>
       <c r="C152" s="29" t="s">
         <v>338</v>
       </c>
@@ -10963,7 +11220,7 @@
         <f>IF(LEN(C153)=0,"",COUNTA($C$62:C153))</f>
         <v>87</v>
       </c>
-      <c r="B153" s="172"/>
+      <c r="B153" s="205"/>
       <c r="C153" s="98" t="s">
         <v>365</v>
       </c>
@@ -10984,7 +11241,7 @@
         <f>IF(LEN(C154)=0,"",COUNTA($C$62:C154))</f>
         <v>88</v>
       </c>
-      <c r="B154" s="172"/>
+      <c r="B154" s="205"/>
       <c r="C154" s="29" t="s">
         <v>339</v>
       </c>
@@ -11005,7 +11262,7 @@
         <f>IF(LEN(C155)=0,"",COUNTA($C$62:C155))</f>
         <v>89</v>
       </c>
-      <c r="B155" s="172"/>
+      <c r="B155" s="205"/>
       <c r="C155" s="29" t="s">
         <v>340</v>
       </c>
@@ -11026,7 +11283,7 @@
         <f>IF(LEN(C156)=0,"",COUNTA($C$62:C156))</f>
         <v>90</v>
       </c>
-      <c r="B156" s="172"/>
+      <c r="B156" s="205"/>
       <c r="C156" s="29" t="s">
         <v>341</v>
       </c>
@@ -11047,7 +11304,7 @@
         <f>IF(LEN(C157)=0,"",COUNTA($C$62:C157))</f>
         <v>91</v>
       </c>
-      <c r="B157" s="172"/>
+      <c r="B157" s="205"/>
       <c r="C157" s="98" t="s">
         <v>364</v>
       </c>
@@ -11068,7 +11325,7 @@
         <f>IF(LEN(C158)=0,"",COUNTA($C$62:C158))</f>
         <v>92</v>
       </c>
-      <c r="B158" s="172"/>
+      <c r="B158" s="205"/>
       <c r="C158" s="29" t="s">
         <v>342</v>
       </c>
@@ -11091,7 +11348,7 @@
         <f>IF(LEN(C159)=0,"",COUNTA($C$62:C159))</f>
         <v>93</v>
       </c>
-      <c r="B159" s="172"/>
+      <c r="B159" s="205"/>
       <c r="C159" s="29" t="s">
         <v>343</v>
       </c>
@@ -11112,7 +11369,7 @@
         <f>IF(LEN(C160)=0,"",COUNTA($C$62:C160))</f>
         <v>94</v>
       </c>
-      <c r="B160" s="172"/>
+      <c r="B160" s="205"/>
       <c r="C160" s="29" t="s">
         <v>344</v>
       </c>
@@ -11133,7 +11390,7 @@
         <f>IF(LEN(C161)=0,"",COUNTA($C$62:C161))</f>
         <v>95</v>
       </c>
-      <c r="B161" s="172"/>
+      <c r="B161" s="205"/>
       <c r="C161" s="29" t="s">
         <v>345</v>
       </c>
@@ -11154,7 +11411,7 @@
         <f>IF(LEN(C162)=0,"",COUNTA($C$62:C162))</f>
         <v>96</v>
       </c>
-      <c r="B162" s="172"/>
+      <c r="B162" s="205"/>
       <c r="C162" s="29" t="s">
         <v>346</v>
       </c>
@@ -11175,7 +11432,7 @@
         <f>IF(LEN(C163)=0,"",COUNTA($C$62:C163))</f>
         <v>97</v>
       </c>
-      <c r="B163" s="172"/>
+      <c r="B163" s="205"/>
       <c r="C163" s="29" t="s">
         <v>347</v>
       </c>
@@ -11196,7 +11453,7 @@
         <f>IF(LEN(C164)=0,"",COUNTA($C$62:C164))</f>
         <v>98</v>
       </c>
-      <c r="B164" s="172"/>
+      <c r="B164" s="205"/>
       <c r="C164" s="29" t="s">
         <v>348</v>
       </c>
@@ -11217,7 +11474,7 @@
         <f>IF(LEN(C165)=0,"",COUNTA($C$62:C165))</f>
         <v>99</v>
       </c>
-      <c r="B165" s="172"/>
+      <c r="B165" s="205"/>
       <c r="C165" s="29" t="s">
         <v>349</v>
       </c>
@@ -11238,7 +11495,7 @@
         <f>IF(LEN(C166)=0,"",COUNTA($C$62:C166))</f>
         <v>100</v>
       </c>
-      <c r="B166" s="172"/>
+      <c r="B166" s="205"/>
       <c r="C166" s="29" t="s">
         <v>350</v>
       </c>
@@ -11259,7 +11516,7 @@
         <f>IF(LEN(C167)=0,"",COUNTA($C$62:C167))</f>
         <v>101</v>
       </c>
-      <c r="B167" s="172"/>
+      <c r="B167" s="205"/>
       <c r="C167" s="29" t="s">
         <v>351</v>
       </c>
@@ -11280,7 +11537,7 @@
         <f>IF(LEN(C168)=0,"",COUNTA($C$62:C168))</f>
         <v>102</v>
       </c>
-      <c r="B168" s="172"/>
+      <c r="B168" s="205"/>
       <c r="C168" s="29" t="s">
         <v>352</v>
       </c>
@@ -11301,7 +11558,7 @@
         <f>IF(LEN(C169)=0,"",COUNTA($C$62:C169))</f>
         <v>103</v>
       </c>
-      <c r="B169" s="172"/>
+      <c r="B169" s="205"/>
       <c r="C169" s="29" t="s">
         <v>353</v>
       </c>
@@ -11322,7 +11579,7 @@
         <f>IF(LEN(C170)=0,"",COUNTA($C$62:C170))</f>
         <v>104</v>
       </c>
-      <c r="B170" s="172"/>
+      <c r="B170" s="205"/>
       <c r="C170" s="29" t="s">
         <v>354</v>
       </c>
@@ -11343,7 +11600,7 @@
         <f>IF(LEN(C171)=0,"",COUNTA($C$62:C171))</f>
         <v>105</v>
       </c>
-      <c r="B171" s="172"/>
+      <c r="B171" s="205"/>
       <c r="C171" s="29" t="s">
         <v>355</v>
       </c>
@@ -11364,7 +11621,7 @@
         <f>IF(LEN(C172)=0,"",COUNTA($C$62:C172))</f>
         <v>106</v>
       </c>
-      <c r="B172" s="172"/>
+      <c r="B172" s="205"/>
       <c r="C172" s="29" t="s">
         <v>356</v>
       </c>
@@ -11383,7 +11640,7 @@
         <f>IF(LEN(C173)=0,"",COUNTA($C$62:C173))</f>
         <v>107</v>
       </c>
-      <c r="B173" s="172"/>
+      <c r="B173" s="205"/>
       <c r="C173" s="29" t="s">
         <v>357</v>
       </c>
@@ -11402,7 +11659,7 @@
         <f>IF(LEN(C174)=0,"",COUNTA($C$62:C174))</f>
         <v>108</v>
       </c>
-      <c r="B174" s="172"/>
+      <c r="B174" s="205"/>
       <c r="C174" s="29" t="s">
         <v>358</v>
       </c>
@@ -11423,7 +11680,7 @@
         <f>IF(LEN(C175)=0,"",COUNTA($C$62:C175))</f>
         <v>109</v>
       </c>
-      <c r="B175" s="172"/>
+      <c r="B175" s="205"/>
       <c r="C175" s="29" t="s">
         <v>359</v>
       </c>
@@ -11444,7 +11701,7 @@
         <f>IF(LEN(C176)=0,"",COUNTA($C$62:C176))</f>
         <v>110</v>
       </c>
-      <c r="B176" s="172"/>
+      <c r="B176" s="205"/>
       <c r="C176" s="29" t="s">
         <v>360</v>
       </c>
@@ -11465,7 +11722,7 @@
         <f>IF(LEN(C177)=0,"",COUNTA($C$62:C177))</f>
         <v>111</v>
       </c>
-      <c r="B177" s="172"/>
+      <c r="B177" s="205"/>
       <c r="C177" s="29" t="s">
         <v>361</v>
       </c>
@@ -11482,12 +11739,12 @@
       <c r="G177" s="34"/>
     </row>
     <row r="178" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A178" s="156" t="s">
+      <c r="A178" s="203" t="s">
         <v>201</v>
       </c>
-      <c r="B178" s="156"/>
-      <c r="C178" s="156"/>
-      <c r="D178" s="156"/>
+      <c r="B178" s="203"/>
+      <c r="C178" s="203"/>
+      <c r="D178" s="203"/>
       <c r="E178" s="69"/>
       <c r="F178" s="69"/>
       <c r="G178" s="59"/>
@@ -11540,7 +11797,7 @@
         <f>IF(LEN(C181)=0,"",COUNTA($C$62:C181))</f>
         <v>114</v>
       </c>
-      <c r="B181" s="169" t="s">
+      <c r="B181" s="185" t="s">
         <v>199</v>
       </c>
       <c r="C181" s="29" t="s">
@@ -11563,7 +11820,7 @@
         <f>IF(LEN(C182)=0,"",COUNTA($C$62:C182))</f>
         <v>115</v>
       </c>
-      <c r="B182" s="171"/>
+      <c r="B182" s="187"/>
       <c r="C182" s="29" t="s">
         <v>219</v>
       </c>
@@ -11580,12 +11837,12 @@
       <c r="G182" s="34"/>
     </row>
     <row r="183" spans="1:8" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A183" s="159" t="s">
+      <c r="A183" s="191" t="s">
         <v>159</v>
       </c>
-      <c r="B183" s="160"/>
-      <c r="C183" s="160"/>
-      <c r="D183" s="161"/>
+      <c r="B183" s="192"/>
+      <c r="C183" s="192"/>
+      <c r="D183" s="193"/>
       <c r="E183" s="108"/>
       <c r="F183" s="108"/>
       <c r="G183" s="54"/>
@@ -11609,7 +11866,7 @@
         <f t="shared" si="2"/>
         <v>63900</v>
       </c>
-      <c r="G184" s="154" t="s">
+      <c r="G184" s="201" t="s">
         <v>374</v>
       </c>
     </row>
@@ -11632,15 +11889,15 @@
         <f t="shared" si="2"/>
         <v>77400</v>
       </c>
-      <c r="G185" s="155"/>
+      <c r="G185" s="202"/>
     </row>
     <row r="186" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A186" s="156" t="s">
+      <c r="A186" s="203" t="s">
         <v>164</v>
       </c>
-      <c r="B186" s="156"/>
-      <c r="C186" s="156"/>
-      <c r="D186" s="156"/>
+      <c r="B186" s="203"/>
+      <c r="C186" s="203"/>
+      <c r="D186" s="203"/>
       <c r="E186" s="69"/>
       <c r="F186" s="69"/>
       <c r="G186" s="59"/>
@@ -11685,7 +11942,7 @@
         <f t="shared" si="2"/>
         <v>2656800</v>
       </c>
-      <c r="G188" s="157"/>
+      <c r="G188" s="180"/>
     </row>
     <row r="189" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A189" s="31">
@@ -11706,7 +11963,7 @@
         <f t="shared" si="2"/>
         <v>3690000</v>
       </c>
-      <c r="G189" s="158"/>
+      <c r="G189" s="181"/>
     </row>
     <row r="190" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A190" s="31">
@@ -11793,12 +12050,12 @@
       <c r="G193" s="34"/>
     </row>
     <row r="194" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A194" s="156" t="s">
+      <c r="A194" s="203" t="s">
         <v>258</v>
       </c>
-      <c r="B194" s="156"/>
-      <c r="C194" s="156"/>
-      <c r="D194" s="156"/>
+      <c r="B194" s="203"/>
+      <c r="C194" s="203"/>
+      <c r="D194" s="203"/>
       <c r="E194" s="69"/>
       <c r="F194" s="69"/>
       <c r="G194" s="59"/>
@@ -11825,12 +12082,12 @@
       <c r="G195" s="34"/>
     </row>
     <row r="196" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A196" s="156" t="s">
+      <c r="A196" s="203" t="s">
         <v>228</v>
       </c>
-      <c r="B196" s="156"/>
-      <c r="C196" s="156"/>
-      <c r="D196" s="156"/>
+      <c r="B196" s="203"/>
+      <c r="C196" s="203"/>
+      <c r="D196" s="203"/>
       <c r="E196" s="69"/>
       <c r="F196" s="69"/>
       <c r="G196" s="59"/>
@@ -11983,12 +12240,12 @@
       <c r="G203" s="34"/>
     </row>
     <row r="204" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A204" s="159" t="s">
+      <c r="A204" s="191" t="s">
         <v>317</v>
       </c>
-      <c r="B204" s="160"/>
-      <c r="C204" s="160"/>
-      <c r="D204" s="161"/>
+      <c r="B204" s="192"/>
+      <c r="C204" s="192"/>
+      <c r="D204" s="193"/>
       <c r="E204" s="58"/>
       <c r="F204" s="58"/>
       <c r="G204" s="59"/>
@@ -12097,12 +12354,12 @@
       <c r="G209" s="34"/>
     </row>
     <row r="210" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A210" s="159" t="s">
+      <c r="A210" s="191" t="s">
         <v>216</v>
       </c>
-      <c r="B210" s="160"/>
-      <c r="C210" s="160"/>
-      <c r="D210" s="161"/>
+      <c r="B210" s="192"/>
+      <c r="C210" s="192"/>
+      <c r="D210" s="193"/>
       <c r="E210" s="58"/>
       <c r="F210" s="58"/>
       <c r="G210" s="59"/>
@@ -12171,12 +12428,12 @@
       <c r="G213" s="34"/>
     </row>
     <row r="214" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A214" s="159" t="s">
+      <c r="A214" s="191" t="s">
         <v>205</v>
       </c>
-      <c r="B214" s="160"/>
-      <c r="C214" s="160"/>
-      <c r="D214" s="161"/>
+      <c r="B214" s="192"/>
+      <c r="C214" s="192"/>
+      <c r="D214" s="193"/>
       <c r="E214" s="58"/>
       <c r="F214" s="58"/>
       <c r="G214" s="59"/>
@@ -12191,10 +12448,10 @@
         <v>206</v>
       </c>
       <c r="D215" s="29"/>
-      <c r="E215" s="162">
+      <c r="E215" s="207">
         <v>183000</v>
       </c>
-      <c r="F215" s="200">
+      <c r="F215" s="210">
         <f>E215*90%</f>
         <v>164700</v>
       </c>
@@ -12210,8 +12467,8 @@
         <v>207</v>
       </c>
       <c r="D216" s="29"/>
-      <c r="E216" s="163"/>
-      <c r="F216" s="201"/>
+      <c r="E216" s="208"/>
+      <c r="F216" s="211"/>
       <c r="G216" s="34"/>
     </row>
     <row r="217" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -12224,8 +12481,8 @@
         <v>208</v>
       </c>
       <c r="D217" s="29"/>
-      <c r="E217" s="163"/>
-      <c r="F217" s="201"/>
+      <c r="E217" s="208"/>
+      <c r="F217" s="211"/>
       <c r="G217" s="34"/>
     </row>
     <row r="218" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -12238,17 +12495,17 @@
         <v>209</v>
       </c>
       <c r="D218" s="29"/>
-      <c r="E218" s="164"/>
-      <c r="F218" s="202"/>
+      <c r="E218" s="209"/>
+      <c r="F218" s="212"/>
       <c r="G218" s="34"/>
     </row>
     <row r="219" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A219" s="159" t="s">
+      <c r="A219" s="191" t="s">
         <v>403</v>
       </c>
-      <c r="B219" s="160"/>
-      <c r="C219" s="160"/>
-      <c r="D219" s="161"/>
+      <c r="B219" s="192"/>
+      <c r="C219" s="192"/>
+      <c r="D219" s="193"/>
       <c r="E219" s="58"/>
       <c r="F219" s="58"/>
       <c r="G219" s="59"/>
@@ -12330,7 +12587,7 @@
       <c r="G223" s="34"/>
     </row>
     <row r="224" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="219" t="s">
+      <c r="A224" s="151" t="s">
         <v>423</v>
       </c>
       <c r="B224" s="82"/>
@@ -12354,22 +12611,22 @@
       <c r="B226" s="82"/>
       <c r="C226" s="81"/>
       <c r="D226" s="81"/>
-      <c r="E226" s="203" t="s">
+      <c r="E226" s="213" t="s">
         <v>422</v>
       </c>
-      <c r="F226" s="204"/>
-      <c r="G226" s="205"/>
+      <c r="F226" s="214"/>
+      <c r="G226" s="215"/>
     </row>
     <row r="227" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A227" s="81"/>
       <c r="B227" s="82"/>
       <c r="C227" s="81"/>
       <c r="D227" s="81"/>
-      <c r="E227" s="206" t="s">
+      <c r="E227" s="216" t="s">
         <v>421</v>
       </c>
-      <c r="F227" s="207"/>
-      <c r="G227" s="208"/>
+      <c r="F227" s="217"/>
+      <c r="G227" s="218"/>
     </row>
     <row r="228" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A228" s="81"/>
@@ -12462,70 +12719,70 @@
       <c r="G237" s="84"/>
     </row>
     <row r="238" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A238" s="153" t="s">
+      <c r="A238" s="219" t="s">
         <v>26</v>
       </c>
-      <c r="B238" s="153"/>
-      <c r="C238" s="153"/>
-      <c r="D238" s="153"/>
+      <c r="B238" s="219"/>
+      <c r="C238" s="219"/>
+      <c r="D238" s="219"/>
       <c r="E238" s="24"/>
       <c r="F238" s="24"/>
       <c r="G238" s="85"/>
     </row>
     <row r="239" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A239" s="86"/>
-      <c r="B239" s="151" t="s">
+      <c r="B239" s="206" t="s">
         <v>261</v>
       </c>
-      <c r="C239" s="151"/>
-      <c r="D239" s="151"/>
-      <c r="E239" s="151"/>
-      <c r="F239" s="151"/>
-      <c r="G239" s="151"/>
+      <c r="C239" s="206"/>
+      <c r="D239" s="206"/>
+      <c r="E239" s="206"/>
+      <c r="F239" s="206"/>
+      <c r="G239" s="206"/>
     </row>
     <row r="240" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A240" s="86"/>
-      <c r="B240" s="151" t="s">
+      <c r="B240" s="206" t="s">
         <v>408</v>
       </c>
-      <c r="C240" s="151"/>
-      <c r="D240" s="151"/>
-      <c r="E240" s="151"/>
-      <c r="F240" s="151"/>
-      <c r="G240" s="151"/>
+      <c r="C240" s="206"/>
+      <c r="D240" s="206"/>
+      <c r="E240" s="206"/>
+      <c r="F240" s="206"/>
+      <c r="G240" s="206"/>
     </row>
     <row r="241" spans="1:7" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="87"/>
-      <c r="B241" s="151" t="s">
+      <c r="B241" s="206" t="s">
         <v>27</v>
       </c>
-      <c r="C241" s="151"/>
-      <c r="D241" s="151"/>
-      <c r="E241" s="151"/>
-      <c r="F241" s="151"/>
-      <c r="G241" s="151"/>
+      <c r="C241" s="206"/>
+      <c r="D241" s="206"/>
+      <c r="E241" s="206"/>
+      <c r="F241" s="206"/>
+      <c r="G241" s="206"/>
     </row>
     <row r="242" spans="1:7" s="15" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="88"/>
-      <c r="B242" s="152" t="s">
+      <c r="B242" s="220" t="s">
         <v>28</v>
       </c>
-      <c r="C242" s="152"/>
-      <c r="D242" s="152"/>
-      <c r="E242" s="152"/>
-      <c r="F242" s="152"/>
-      <c r="G242" s="152"/>
+      <c r="C242" s="220"/>
+      <c r="D242" s="220"/>
+      <c r="E242" s="220"/>
+      <c r="F242" s="220"/>
+      <c r="G242" s="220"/>
     </row>
     <row r="243" spans="1:7" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="85"/>
-      <c r="B243" s="151" t="s">
+      <c r="B243" s="206" t="s">
         <v>29</v>
       </c>
-      <c r="C243" s="151"/>
-      <c r="D243" s="151"/>
-      <c r="E243" s="151"/>
-      <c r="F243" s="151"/>
-      <c r="G243" s="151"/>
+      <c r="C243" s="206"/>
+      <c r="D243" s="206"/>
+      <c r="E243" s="206"/>
+      <c r="F243" s="206"/>
+      <c r="G243" s="206"/>
     </row>
     <row r="244" spans="1:7" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A244" s="85"/>
@@ -12668,11 +12925,11 @@
     <mergeCell ref="B243:G243"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="55" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>